--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5325,31 +5325,113 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>28997.75</v>
+      </c>
+      <c r="C58" t="n">
+        <v>29604.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>29107.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>29489.75</v>
+      </c>
+      <c r="F58" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="H58" t="n">
+        <v>497.25</v>
+      </c>
+      <c r="I58" t="n">
+        <v>28316.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>28654.94</v>
+      </c>
+      <c r="K58" t="n">
+        <v>29024.88</v>
+      </c>
+      <c r="L58" t="n">
+        <v>29394.81</v>
+      </c>
+      <c r="M58" t="n">
+        <v>29749.12</v>
+      </c>
+      <c r="N58" t="n">
+        <v>30103.44</v>
+      </c>
+      <c r="O58" t="n">
+        <v>30489</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>28316.25</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>28654.94</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>29024.88</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>29394.81</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>29749.12</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>30103.44</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>30489</v>
+      <c r="I59" s="13" t="n">
+        <v>28610</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>29059.44</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>29241.12</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>29422.81</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>29738.38</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>30053.94</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>30101.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -666,25 +669,25 @@
         <v>846.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23106.5</v>
+        <v>23123.5</v>
       </c>
       <c r="J2" t="n">
-        <v>23311</v>
+        <v>23317.38</v>
       </c>
       <c r="K2" t="n">
-        <v>23563.5</v>
+        <v>23567.75</v>
       </c>
       <c r="L2" t="n">
-        <v>23816</v>
+        <v>23818.12</v>
       </c>
       <c r="M2" t="n">
-        <v>24044.5</v>
+        <v>24040.25</v>
       </c>
       <c r="N2" t="n">
-        <v>24273</v>
+        <v>24262.38</v>
       </c>
       <c r="O2" t="n">
-        <v>24549.5</v>
+        <v>24541</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5331,25 +5334,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28997.75</v>
+        <v>29488.5</v>
       </c>
       <c r="C58" t="n">
-        <v>29604.5</v>
+        <v>29495.25</v>
       </c>
       <c r="D58" t="n">
-        <v>29107.25</v>
+        <v>29426.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29489.75</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>102.75</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0035</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>497.25</v>
+        <v>68.5</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5372,8 +5375,10 @@
       <c r="O58" t="n">
         <v>30489</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5381,9 +5386,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5402,36 +5407,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>28610</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>29059.44</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>29241.12</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>29422.81</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>29738.38</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>30053.94</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>30101.75</v>
+      <c r="I59" s="14" t="n">
+        <v>29358.25</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>29563.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5334,25 +5331,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29488.5</v>
+        <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29495.25</v>
+        <v>29303</v>
       </c>
       <c r="D58" t="n">
-        <v>29426.75</v>
+        <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>29152.25</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-234.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.008</v>
       </c>
       <c r="H58" t="n">
-        <v>68.5</v>
+        <v>486.75</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5375,20 +5372,20 @@
       <c r="O58" t="n">
         <v>30489</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5405,38 +5402,34 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>29358.25</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>29563.75</v>
+      <c r="I59" s="13" t="n">
+        <v>28329.5</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>28711.81</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>28908.88</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>29105.94</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>29395.62</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>29685.31</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>29789.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29303</v>
+        <v>29495.25</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29152.25</v>
+        <v>29277</v>
       </c>
       <c r="F58" t="n">
-        <v>-234.75</v>
+        <v>-110</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0037</v>
       </c>
       <c r="H58" t="n">
-        <v>486.75</v>
+        <v>679</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5411,25 +5411,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28329.5</v>
+        <v>28137.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28711.81</v>
+        <v>28658.62</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>28908.88</v>
+        <v>28937.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29105.94</v>
+        <v>29216.38</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29395.62</v>
+        <v>29616.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>29685.31</v>
+        <v>30016.62</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>29789.75</v>
+        <v>30174.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>846.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23123.5</v>
+        <v>23400.5</v>
       </c>
       <c r="J2" t="n">
-        <v>23317.38</v>
+        <v>23421.25</v>
       </c>
       <c r="K2" t="n">
-        <v>23567.75</v>
+        <v>23637</v>
       </c>
       <c r="L2" t="n">
-        <v>23818.12</v>
+        <v>23852.75</v>
       </c>
       <c r="M2" t="n">
-        <v>24040.25</v>
+        <v>23971</v>
       </c>
       <c r="N2" t="n">
-        <v>24262.38</v>
+        <v>24089.25</v>
       </c>
       <c r="O2" t="n">
-        <v>24541</v>
+        <v>24402.5</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29495.25</v>
+        <v>29303</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29277</v>
+        <v>29254.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-110</v>
+        <v>-132.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0045</v>
       </c>
       <c r="H58" t="n">
-        <v>679</v>
+        <v>486.75</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5411,25 +5411,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28137.25</v>
+        <v>28329.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28658.62</v>
+        <v>28864.81</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>28937.5</v>
+        <v>29010.88</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29216.38</v>
+        <v>29156.94</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29616.5</v>
+        <v>29497.62</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>30016.62</v>
+        <v>29838.31</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>30174.25</v>
+        <v>29789.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29303</v>
+        <v>29358.5</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29254.25</v>
+        <v>29320.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-132.75</v>
+        <v>-66.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0045</v>
+        <v>-0.0023</v>
       </c>
       <c r="H58" t="n">
-        <v>486.75</v>
+        <v>542.25</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5411,25 +5411,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28329.5</v>
+        <v>28274</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28864.81</v>
+        <v>28894.81</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29010.88</v>
+        <v>29049.38</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29156.94</v>
+        <v>29203.94</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29497.62</v>
+        <v>29591.62</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>29838.31</v>
+        <v>29979.31</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>29789.75</v>
+        <v>29900.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29358.5</v>
+        <v>29419.25</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29320.5</v>
+        <v>29382</v>
       </c>
       <c r="F58" t="n">
-        <v>-66.5</v>
+        <v>-5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0002</v>
       </c>
       <c r="H58" t="n">
-        <v>542.25</v>
+        <v>603</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5411,25 +5411,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28274</v>
+        <v>28213.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28894.81</v>
+        <v>28911.12</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29049.38</v>
+        <v>29080.5</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29203.94</v>
+        <v>29249.88</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29591.62</v>
+        <v>29683.5</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>29979.31</v>
+        <v>30117.12</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>29900.75</v>
+        <v>30022.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5340,13 +5340,13 @@
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29382</v>
+        <v>29413.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-5</v>
+        <v>26.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0009</v>
       </c>
       <c r="H58" t="n">
         <v>603</v>
@@ -5383,9 +5383,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5402,7 +5402,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5414,19 +5418,19 @@
         <v>28213.25</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28911.12</v>
+        <v>28958</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29080.5</v>
+        <v>29111.75</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29249.88</v>
+        <v>29265.5</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29683.5</v>
+        <v>29714.75</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>30117.12</v>
+        <v>30164</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>30022.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29419.25</v>
+        <v>29439</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29413.25</v>
+        <v>29432.75</v>
       </c>
       <c r="F58" t="n">
-        <v>26.25</v>
+        <v>45.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0016</v>
       </c>
       <c r="H58" t="n">
-        <v>603</v>
+        <v>622.75</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5415,25 +5415,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28213.25</v>
+        <v>28193.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28958</v>
+        <v>28962.56</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29111.75</v>
+        <v>29121.38</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29265.5</v>
+        <v>29280.19</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29714.75</v>
+        <v>29744.12</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>30164</v>
+        <v>30208.06</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>30022.25</v>
+        <v>30061.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29439</v>
+        <v>29303</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29432.75</v>
+        <v>29260.25</v>
       </c>
       <c r="F58" t="n">
-        <v>45.75</v>
+        <v>-126.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.0043</v>
       </c>
       <c r="H58" t="n">
-        <v>622.75</v>
+        <v>486.75</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5383,9 +5383,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5402,11 +5402,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5415,25 +5411,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28193.5</v>
+        <v>28329.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28962.56</v>
+        <v>28873.81</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29121.38</v>
+        <v>29016.88</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29280.19</v>
+        <v>29159.94</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29744.12</v>
+        <v>29503.62</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>30208.06</v>
+        <v>29847.31</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>30061.75</v>
+        <v>29789.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -666,25 +666,25 @@
         <v>846.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23400.5</v>
+        <v>23461.25</v>
       </c>
       <c r="J2" t="n">
-        <v>23421.25</v>
+        <v>23497.19</v>
       </c>
       <c r="K2" t="n">
-        <v>23637</v>
+        <v>23667.38</v>
       </c>
       <c r="L2" t="n">
-        <v>23852.75</v>
+        <v>23837.56</v>
       </c>
       <c r="M2" t="n">
-        <v>23971</v>
+        <v>23940.62</v>
       </c>
       <c r="N2" t="n">
-        <v>24089.25</v>
+        <v>24043.69</v>
       </c>
       <c r="O2" t="n">
-        <v>24402.5</v>
+        <v>24281</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -693,12 +693,12 @@
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29303</v>
+        <v>29478</v>
       </c>
       <c r="D58" t="n">
         <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29260.25</v>
+        <v>29443.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-126.75</v>
+        <v>56.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0019</v>
       </c>
       <c r="H58" t="n">
-        <v>486.75</v>
+        <v>661.75</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5383,9 +5383,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5402,7 +5402,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
@@ -5411,25 +5415,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28329.5</v>
+        <v>28154.5</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28873.81</v>
+        <v>28929.56</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29016.88</v>
+        <v>29112.38</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29159.94</v>
+        <v>29295.19</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29503.62</v>
+        <v>29774.12</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>29847.31</v>
+        <v>30253.06</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>29789.75</v>
+        <v>30139.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5334,22 +5334,22 @@
         <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29478</v>
+        <v>29728.5</v>
       </c>
       <c r="D58" t="n">
-        <v>28816.25</v>
+        <v>28763.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29443.25</v>
+        <v>29707</v>
       </c>
       <c r="F58" t="n">
-        <v>56.25</v>
+        <v>320</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0109</v>
       </c>
       <c r="H58" t="n">
-        <v>661.75</v>
+        <v>964.75</v>
       </c>
       <c r="I58" t="n">
         <v>28316.25</v>
@@ -5385,11 +5385,13 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5415,25 +5417,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>28154.5</v>
+        <v>27799</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28929.56</v>
+        <v>28972.69</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29112.38</v>
+        <v>29224.62</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29295.19</v>
+        <v>29476.56</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>29774.12</v>
+        <v>30189.38</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>30253.06</v>
+        <v>30902.19</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>30139.75</v>
+        <v>30693.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5340,13 +5340,13 @@
         <v>28763.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29707</v>
+        <v>29694.25</v>
       </c>
       <c r="F58" t="n">
-        <v>320</v>
+        <v>307.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0105</v>
       </c>
       <c r="H58" t="n">
         <v>964.75</v>
@@ -5420,19 +5420,19 @@
         <v>27799</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>28972.69</v>
+        <v>28953.56</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>29224.62</v>
+        <v>29211.88</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>29476.56</v>
+        <v>29470.19</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>30189.38</v>
+        <v>30176.62</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>30902.19</v>
+        <v>30883.06</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>30693.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>846.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23461.25</v>
+        <v>23506</v>
       </c>
       <c r="J2" t="n">
-        <v>23497.19</v>
+        <v>23553.12</v>
       </c>
       <c r="K2" t="n">
-        <v>23667.38</v>
+        <v>23689.75</v>
       </c>
       <c r="L2" t="n">
-        <v>23837.56</v>
+        <v>23826.38</v>
       </c>
       <c r="M2" t="n">
-        <v>23940.62</v>
+        <v>23918.25</v>
       </c>
       <c r="N2" t="n">
-        <v>24043.69</v>
+        <v>24010.12</v>
       </c>
       <c r="O2" t="n">
-        <v>24281</v>
+        <v>24191.5</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -5340,13 +5333,13 @@
         <v>28763.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29694.25</v>
+        <v>29685.25</v>
       </c>
       <c r="F58" t="n">
-        <v>307.25</v>
+        <v>298.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0101</v>
       </c>
       <c r="H58" t="n">
         <v>964.75</v>
@@ -5408,34 +5401,6 @@
         <is>
           <t>弱警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>27799</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>28953.56</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>29211.88</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>29470.19</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>30176.62</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>30883.06</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>30693.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5333,13 +5333,13 @@
         <v>28763.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29685.25</v>
+        <v>29679.75</v>
       </c>
       <c r="F58" t="n">
-        <v>298.25</v>
+        <v>292.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.01</v>
       </c>
       <c r="H58" t="n">
         <v>964.75</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23795</v>
+        <v>23602</v>
       </c>
       <c r="C2" t="n">
-        <v>23881.75</v>
+        <v>23803.75</v>
       </c>
       <c r="D2" t="n">
-        <v>23035</v>
+        <v>23371.5</v>
       </c>
       <c r="E2" t="n">
-        <v>23569.75</v>
+        <v>23461.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-234.25</v>
+        <v>-108</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0098</v>
+        <v>-0.0046</v>
       </c>
       <c r="H2" t="n">
-        <v>846.75</v>
+        <v>432.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23506</v>
+        <v>22188.25</v>
       </c>
       <c r="J2" t="n">
-        <v>23553.12</v>
+        <v>22778.69</v>
       </c>
       <c r="K2" t="n">
-        <v>23689.75</v>
+        <v>23146.38</v>
       </c>
       <c r="L2" t="n">
-        <v>23826.38</v>
+        <v>23514.06</v>
       </c>
       <c r="M2" t="n">
-        <v>23918.25</v>
+        <v>23993.12</v>
       </c>
       <c r="N2" t="n">
-        <v>24010.12</v>
+        <v>24472.19</v>
       </c>
       <c r="O2" t="n">
-        <v>24191.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>24728.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -715,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23602</v>
+        <v>23479</v>
       </c>
       <c r="C3" t="n">
-        <v>23803.75</v>
+        <v>23902</v>
       </c>
       <c r="D3" t="n">
-        <v>23371.5</v>
+        <v>23025.25</v>
       </c>
       <c r="E3" t="n">
-        <v>23461.75</v>
+        <v>23684</v>
       </c>
       <c r="F3" t="n">
-        <v>-108</v>
+        <v>222.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0046</v>
+        <v>0.0095</v>
       </c>
       <c r="H3" t="n">
-        <v>432.25</v>
+        <v>876.75</v>
       </c>
       <c r="I3" t="n">
-        <v>22188.25</v>
+        <v>22939.25</v>
       </c>
       <c r="J3" t="n">
-        <v>22778.69</v>
+        <v>22966.56</v>
       </c>
       <c r="K3" t="n">
-        <v>23146.38</v>
+        <v>23245.62</v>
       </c>
       <c r="L3" t="n">
-        <v>23514.06</v>
+        <v>23524.69</v>
       </c>
       <c r="M3" t="n">
-        <v>23993.12</v>
+        <v>23677.88</v>
       </c>
       <c r="N3" t="n">
-        <v>24472.19</v>
+        <v>23831.06</v>
       </c>
       <c r="O3" t="n">
-        <v>24728.5</v>
+        <v>24236</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,19 +767,25 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -797,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23479</v>
+        <v>23673.5</v>
       </c>
       <c r="C4" t="n">
-        <v>23902</v>
+        <v>24159</v>
       </c>
       <c r="D4" t="n">
-        <v>23025.25</v>
+        <v>23650.25</v>
       </c>
       <c r="E4" t="n">
-        <v>23684</v>
+        <v>24113.25</v>
       </c>
       <c r="F4" t="n">
-        <v>222.25</v>
+        <v>429.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0181</v>
       </c>
       <c r="H4" t="n">
-        <v>876.75</v>
+        <v>508.75</v>
       </c>
       <c r="I4" t="n">
-        <v>22939.25</v>
+        <v>22148.5</v>
       </c>
       <c r="J4" t="n">
-        <v>22966.56</v>
+        <v>22917.44</v>
       </c>
       <c r="K4" t="n">
         <v>23245.62</v>
       </c>
       <c r="L4" t="n">
-        <v>23524.69</v>
+        <v>23573.81</v>
       </c>
       <c r="M4" t="n">
-        <v>23677.88</v>
+        <v>24122.38</v>
       </c>
       <c r="N4" t="n">
-        <v>23831.06</v>
+        <v>24670.94</v>
       </c>
       <c r="O4" t="n">
-        <v>24236</v>
+        <v>24778.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,10 +855,8 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
@@ -870,10 +868,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -883,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23673.5</v>
+        <v>24115.25</v>
       </c>
       <c r="C5" t="n">
-        <v>24159</v>
+        <v>24575</v>
       </c>
       <c r="D5" t="n">
-        <v>23650.25</v>
+        <v>24003.75</v>
       </c>
       <c r="E5" t="n">
-        <v>24113.25</v>
+        <v>24568.07</v>
       </c>
       <c r="F5" t="n">
-        <v>429.25</v>
+        <v>454.82</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0181</v>
+        <v>0.0189</v>
       </c>
       <c r="H5" t="n">
-        <v>508.75</v>
+        <v>571.25</v>
       </c>
       <c r="I5" t="n">
-        <v>22148.5</v>
+        <v>23141.5</v>
       </c>
       <c r="J5" t="n">
-        <v>22917.44</v>
+        <v>23708.81</v>
       </c>
       <c r="K5" t="n">
-        <v>23245.62</v>
+        <v>23858.88</v>
       </c>
       <c r="L5" t="n">
-        <v>23573.81</v>
+        <v>24008.94</v>
       </c>
       <c r="M5" t="n">
-        <v>24122.38</v>
+        <v>24367.62</v>
       </c>
       <c r="N5" t="n">
-        <v>24670.94</v>
+        <v>24726.31</v>
       </c>
       <c r="O5" t="n">
-        <v>24778.75</v>
+        <v>24667.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -953,14 +945,16 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -972,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24115.25</v>
+        <v>24850</v>
       </c>
       <c r="C6" t="n">
-        <v>24575</v>
+        <v>25027.25</v>
       </c>
       <c r="D6" t="n">
-        <v>24003.75</v>
+        <v>24422.5</v>
       </c>
       <c r="E6" t="n">
-        <v>24568.07</v>
+        <v>24726.75</v>
       </c>
       <c r="F6" t="n">
-        <v>454.82</v>
+        <v>158.68</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0065</v>
       </c>
       <c r="H6" t="n">
-        <v>571.25</v>
+        <v>604.75</v>
       </c>
       <c r="I6" t="n">
-        <v>23141.5</v>
+        <v>23432.5</v>
       </c>
       <c r="J6" t="n">
-        <v>23708.81</v>
+        <v>24136.17</v>
       </c>
       <c r="K6" t="n">
-        <v>23858.88</v>
+        <v>24282.45</v>
       </c>
       <c r="L6" t="n">
-        <v>24008.94</v>
+        <v>24428.72</v>
       </c>
       <c r="M6" t="n">
-        <v>24367.62</v>
+        <v>24853.7</v>
       </c>
       <c r="N6" t="n">
-        <v>24726.31</v>
+        <v>25278.67</v>
       </c>
       <c r="O6" t="n">
-        <v>24667.75</v>
+        <v>25146.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1033,16 +1027,14 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1054,50 +1046,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24850</v>
+        <v>24726.5</v>
       </c>
       <c r="C7" t="n">
-        <v>25027.25</v>
+        <v>25196.5</v>
       </c>
       <c r="D7" t="n">
-        <v>24422.5</v>
+        <v>24633.25</v>
       </c>
       <c r="E7" t="n">
-        <v>24726.75</v>
+        <v>24992</v>
       </c>
       <c r="F7" t="n">
-        <v>158.68</v>
+        <v>265.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.0107</v>
       </c>
       <c r="H7" t="n">
-        <v>604.75</v>
+        <v>563.25</v>
       </c>
       <c r="I7" t="n">
-        <v>23432.5</v>
+        <v>23817.75</v>
       </c>
       <c r="J7" t="n">
-        <v>24136.17</v>
+        <v>24122.94</v>
       </c>
       <c r="K7" t="n">
-        <v>24282.45</v>
+        <v>24424.38</v>
       </c>
       <c r="L7" t="n">
-        <v>24428.72</v>
+        <v>24725.81</v>
       </c>
       <c r="M7" t="n">
-        <v>24853.7</v>
+        <v>25029.12</v>
       </c>
       <c r="N7" t="n">
-        <v>25278.67</v>
+        <v>25332.44</v>
       </c>
       <c r="O7" t="n">
-        <v>25146.25</v>
+        <v>25632</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1134,68 +1126,72 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C8" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D8" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E8" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F8" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H8" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I8" t="n">
-        <v>23817.75</v>
+        <v>24070</v>
       </c>
       <c r="J8" t="n">
-        <v>24122.94</v>
+        <v>24467.31</v>
       </c>
       <c r="K8" t="n">
-        <v>24424.38</v>
+        <v>24710.38</v>
       </c>
       <c r="L8" t="n">
-        <v>24725.81</v>
+        <v>24953.44</v>
       </c>
       <c r="M8" t="n">
-        <v>25029.12</v>
+        <v>25273.62</v>
       </c>
       <c r="N8" t="n">
-        <v>25332.44</v>
+        <v>25593.81</v>
       </c>
       <c r="O8" t="n">
-        <v>25632</v>
+        <v>25759.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1204,84 +1200,84 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C9" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D9" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E9" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H9" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I9" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J9" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K9" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L9" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M9" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N9" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O9" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1295,57 +1291,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C10" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D10" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E10" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F10" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H10" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I10" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J10" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K10" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L10" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M10" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N10" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O10" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1379,57 +1375,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C11" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D11" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E11" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F11" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H11" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I11" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J11" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K11" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L11" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M11" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N11" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O11" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1453,8 +1449,10 @@
       <c r="U11" s="8" t="n">
         <v/>
       </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
@@ -1470,155 +1468,147 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C12" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D12" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E12" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F12" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H12" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I12" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J12" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K12" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L12" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M12" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N12" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O12" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>27098</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C13" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D13" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E13" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F13" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H13" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I13" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J13" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K13" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L13" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M13" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N13" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O13" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>27822.75</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1640,50 +1630,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C14" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D14" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E14" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H14" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I14" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J14" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K14" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L14" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M14" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N14" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O14" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,12 +1681,14 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1718,50 +1710,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C15" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D15" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E15" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F15" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H15" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I15" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J15" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K15" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L15" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M15" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N15" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O15" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,22 +1761,24 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1793,55 +1787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C16" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D16" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E16" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F16" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H16" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I16" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J16" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K16" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L16" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M16" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N16" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O16" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,13 +1857,11 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1884,70 +1880,72 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C17" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D17" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E17" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F17" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H17" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I17" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J17" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K17" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L17" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M17" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N17" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O17" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1961,65 +1959,63 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C18" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D18" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E18" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F18" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H18" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I18" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J18" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K18" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L18" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M18" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N18" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O18" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q18" s="6" t="n">
+        <v/>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
@@ -2028,7 +2024,7 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2045,59 +2041,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C19" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D19" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E19" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H19" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I19" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J19" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K19" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L19" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M19" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N19" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O19" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2105,21 +2097,23 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2129,79 +2123,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C20" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D20" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E20" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F20" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H20" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I20" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J20" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K20" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L20" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M20" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N20" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O20" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>26262.25</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2211,92 +2211,86 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C21" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D21" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E21" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H21" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I21" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J21" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K21" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L21" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M21" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N21" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O21" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2304,75 +2298,75 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C22" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D22" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E22" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F22" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I22" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J22" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K22" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L22" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M22" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N22" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O22" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2381,55 +2375,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C23" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D23" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E23" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H23" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I23" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J23" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K23" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L23" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M23" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N23" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O23" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,12 +2439,12 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2465,79 +2463,77 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C24" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D24" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E24" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F24" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H24" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I24" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J24" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K24" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L24" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M24" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N24" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O24" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2551,77 +2547,81 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C25" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D25" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E25" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H25" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I25" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J25" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K25" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L25" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M25" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N25" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O25" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+        <v>27332.75</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2635,76 +2635,70 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C26" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D26" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E26" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H26" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I26" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J26" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K26" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L26" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M26" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N26" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O26" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27815.75</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2723,57 +2717,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C27" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D27" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E27" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H27" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I27" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J27" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K27" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L27" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M27" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N27" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O27" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,9 +2778,9 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2812,50 +2806,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C28" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D28" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E28" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F28" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H28" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I28" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J28" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K28" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L28" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M28" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N28" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O28" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2863,16 +2857,20 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2887,57 +2885,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C29" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D29" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E29" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H29" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I29" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J29" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K29" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L29" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M29" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N29" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O29" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,18 +2945,16 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2973,57 +2969,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C30" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D30" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E30" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F30" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H30" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I30" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J30" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K30" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L30" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M30" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N30" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O30" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,8 +3037,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3064,50 +3062,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C31" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D31" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E31" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F31" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H31" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I31" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J31" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K31" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L31" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M31" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N31" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O31" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3115,20 +3113,16 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3143,74 +3137,80 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C32" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D32" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E32" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H32" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I32" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J32" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K32" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L32" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M32" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N32" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O32" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3225,81 +3225,77 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C33" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D33" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E33" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H33" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I33" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J33" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K33" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L33" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M33" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N33" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O33" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3313,57 +3309,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C34" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D34" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E34" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F34" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H34" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I34" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J34" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K34" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L34" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M34" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N34" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O34" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3381,73 +3377,71 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C35" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D35" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E35" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H35" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I35" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J35" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K35" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L35" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M35" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N35" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O35" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3486,50 +3480,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C36" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D36" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E36" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F36" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H36" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I36" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J36" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K36" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L36" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M36" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N36" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O36" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3547,16 +3541,14 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3568,50 +3560,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C37" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D37" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E37" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F37" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H37" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I37" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J37" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K37" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L37" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M37" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N37" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O37" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3648,50 +3640,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C38" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D38" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E38" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F38" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H38" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I38" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J38" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K38" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L38" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M38" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N38" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O38" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3709,14 +3701,18 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3728,50 +3724,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C39" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D39" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E39" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F39" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H39" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I39" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J39" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K39" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L39" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M39" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N39" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O39" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3784,78 +3780,76 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C40" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D40" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E40" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H40" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I40" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J40" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K40" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L40" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M40" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N40" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O40" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3863,16 +3857,20 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3887,57 +3885,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C41" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D41" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E41" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F41" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H41" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I41" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J41" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K41" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L41" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M41" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N41" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O41" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3945,10 +3943,8 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
@@ -3971,158 +3967,156 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C42" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D42" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E42" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F42" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H42" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I42" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J42" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K42" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L42" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M42" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N42" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O42" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>31395.75</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C43" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D43" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F43" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H43" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I43" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J43" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K43" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L43" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M43" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N43" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O43" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>32834.25</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4148,50 +4142,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C44" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D44" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E44" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F44" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H44" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I44" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J44" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K44" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L44" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M44" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N44" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O44" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4204,11 +4198,13 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4223,77 +4219,79 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C45" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D45" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E45" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F45" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H45" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I45" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J45" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K45" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L45" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M45" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N45" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O45" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4307,79 +4305,77 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C46" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D46" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E46" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H46" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I46" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J46" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K46" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L46" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M46" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N46" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O46" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4393,57 +4389,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C47" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D47" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E47" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F47" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H47" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I47" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J47" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K47" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L47" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M47" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N47" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O47" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4451,18 +4447,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4477,72 +4473,74 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C48" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D48" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E48" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F48" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H48" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I48" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J48" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K48" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L48" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M48" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N48" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O48" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4559,71 +4557,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C49" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D49" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E49" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F49" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H49" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I49" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J49" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K49" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L49" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M49" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N49" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O49" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
@@ -4650,50 +4642,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C50" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D50" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E50" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F50" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H50" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I50" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J50" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K50" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L50" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M50" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N50" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O50" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4703,12 +4695,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4725,55 +4717,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C51" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D51" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E51" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F51" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H51" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I51" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J51" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K51" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L51" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M51" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N51" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O51" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4781,21 +4777,23 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4807,57 +4805,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C52" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D52" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E52" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F52" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H52" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I52" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J52" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K52" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L52" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M52" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N52" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O52" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4875,13 +4873,11 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4900,70 +4896,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C53" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D53" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E53" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F53" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H53" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I53" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J53" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K53" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L53" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M53" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N53" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O53" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4977,74 +4975,70 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C54" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D54" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E54" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H54" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I54" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J54" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K54" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L54" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M54" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N54" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O54" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5070,50 +5064,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C55" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D55" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E55" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F55" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H55" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I55" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J55" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K55" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L55" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M55" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N55" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O55" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5121,12 +5115,14 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5152,50 +5148,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C56" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D56" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E56" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F56" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H56" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I56" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J56" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K56" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L56" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M56" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N56" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O56" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5208,9 +5204,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5229,57 +5225,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C57" t="n">
-        <v>29764.75</v>
+        <v>29944.5</v>
       </c>
       <c r="D57" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29387</v>
+        <v>29917.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-178.25</v>
+        <v>530.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.018</v>
       </c>
       <c r="H57" t="n">
-        <v>724.25</v>
+        <v>1180.75</v>
       </c>
       <c r="I57" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J57" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K57" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L57" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M57" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N57" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O57" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5292,13 +5288,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5314,92 +5312,6 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>28997.75</v>
-      </c>
-      <c r="C58" t="n">
-        <v>29728.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>28763.75</v>
-      </c>
-      <c r="E58" t="n">
-        <v>29679.75</v>
-      </c>
-      <c r="F58" t="n">
-        <v>292.75</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H58" t="n">
-        <v>964.75</v>
-      </c>
-      <c r="I58" t="n">
-        <v>28316.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>28654.94</v>
-      </c>
-      <c r="K58" t="n">
-        <v>29024.88</v>
-      </c>
-      <c r="L58" t="n">
-        <v>29394.81</v>
-      </c>
-      <c r="M58" t="n">
-        <v>29749.12</v>
-      </c>
-      <c r="N58" t="n">
-        <v>30103.44</v>
-      </c>
-      <c r="O58" t="n">
-        <v>30489</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5239,22 +5239,22 @@
         <v>28997.75</v>
       </c>
       <c r="C57" t="n">
-        <v>29944.5</v>
+        <v>29665.25</v>
       </c>
       <c r="D57" t="n">
         <v>28763.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29917.25</v>
+        <v>29613.68</v>
       </c>
       <c r="F57" t="n">
-        <v>530.25</v>
+        <v>226.68</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.018</v>
+        <v>0.0077</v>
       </c>
       <c r="H57" t="n">
-        <v>1180.75</v>
+        <v>901.5</v>
       </c>
       <c r="I57" t="n">
         <v>28316.25</v>
@@ -5311,9 +5311,93 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>30780</v>
+      </c>
+      <c r="C58" t="n">
+        <v>30821.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30778.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>30816.75</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1203.07</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="H58" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>27862.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>28911.77</v>
+      </c>
+      <c r="K58" t="n">
+        <v>29162.93</v>
+      </c>
+      <c r="L58" t="n">
+        <v>29414.09</v>
+      </c>
+      <c r="M58" t="n">
+        <v>30064.43</v>
+      </c>
+      <c r="N58" t="n">
+        <v>30714.77</v>
+      </c>
+      <c r="O58" t="n">
+        <v>30566.75</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>432.25</v>
       </c>
       <c r="I2" t="n">
-        <v>22188.25</v>
+        <v>22232</v>
       </c>
       <c r="J2" t="n">
-        <v>22778.69</v>
+        <v>22833.38</v>
       </c>
       <c r="K2" t="n">
-        <v>23146.38</v>
+        <v>23168.25</v>
       </c>
       <c r="L2" t="n">
-        <v>23514.06</v>
+        <v>23503.12</v>
       </c>
       <c r="M2" t="n">
-        <v>23993.12</v>
+        <v>23971.25</v>
       </c>
       <c r="N2" t="n">
-        <v>24472.19</v>
+        <v>24439.38</v>
       </c>
       <c r="O2" t="n">
-        <v>24728.5</v>
+        <v>24641</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5322,25 +5322,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30780</v>
+        <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>30821.25</v>
+        <v>30945</v>
       </c>
       <c r="D58" t="n">
-        <v>30778.5</v>
+        <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>30816.75</v>
+        <v>30923.25</v>
       </c>
       <c r="F58" t="n">
-        <v>1203.07</v>
+        <v>1309.57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0406</v>
+        <v>0.0442</v>
       </c>
       <c r="H58" t="n">
-        <v>42.75</v>
+        <v>1041</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>30945</v>
+        <v>30997.5</v>
       </c>
       <c r="D58" t="n">
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>30923.25</v>
+        <v>30910</v>
       </c>
       <c r="F58" t="n">
-        <v>1309.57</v>
+        <v>1296.32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0442</v>
+        <v>0.0438</v>
       </c>
       <c r="H58" t="n">
-        <v>1041</v>
+        <v>1093.5</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>30997.5</v>
+        <v>31033</v>
       </c>
       <c r="D58" t="n">
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>30910</v>
+        <v>31020.25</v>
       </c>
       <c r="F58" t="n">
-        <v>1296.32</v>
+        <v>1406.57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0438</v>
+        <v>0.0475</v>
       </c>
       <c r="H58" t="n">
-        <v>1093.5</v>
+        <v>1129</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,25 +659,25 @@
         <v>432.25</v>
       </c>
       <c r="I2" t="n">
-        <v>22232</v>
+        <v>22420</v>
       </c>
       <c r="J2" t="n">
-        <v>22833.38</v>
+        <v>23068.38</v>
       </c>
       <c r="K2" t="n">
-        <v>23168.25</v>
+        <v>23262.25</v>
       </c>
       <c r="L2" t="n">
-        <v>23503.12</v>
+        <v>23456.12</v>
       </c>
       <c r="M2" t="n">
-        <v>23971.25</v>
+        <v>23877.25</v>
       </c>
       <c r="N2" t="n">
-        <v>24439.38</v>
+        <v>24298.38</v>
       </c>
       <c r="O2" t="n">
-        <v>24641</v>
+        <v>24265</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -858,7 +858,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -938,7 +938,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1020,7 +1020,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1100,7 +1100,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1184,7 +1184,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1268,7 +1268,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1352,7 +1352,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1436,7 +1436,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1528,7 +1528,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1606,7 +1606,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1686,7 +1686,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1764,7 +1764,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1850,7 +1850,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1938,7 +1938,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2022,7 +2022,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2100,7 +2100,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2192,7 +2192,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2270,7 +2270,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2356,7 +2356,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2442,7 +2442,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2524,7 +2524,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2614,7 +2614,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2696,7 +2696,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2778,7 +2778,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2862,7 +2862,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2948,7 +2948,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3032,7 +3032,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3116,7 +3116,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3202,7 +3202,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3286,7 +3286,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3370,7 +3370,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3452,7 +3452,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3534,7 +3534,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3614,7 +3614,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3694,7 +3694,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3778,7 +3778,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3862,7 +3862,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3946,7 +3946,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4032,7 +4032,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4114,7 +4114,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4196,7 +4196,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4284,7 +4284,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4366,7 +4366,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4452,7 +4452,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4538,7 +4538,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4618,7 +4618,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4698,7 +4698,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4780,7 +4780,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4866,7 +4866,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4954,7 +4954,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5036,7 +5036,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5120,7 +5120,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5204,7 +5204,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5288,7 +5288,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5325,22 +5325,22 @@
         <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>31033</v>
+        <v>31070.5</v>
       </c>
       <c r="D58" t="n">
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>31020.25</v>
+        <v>31047.75</v>
       </c>
       <c r="F58" t="n">
-        <v>1406.57</v>
+        <v>1434.07</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0475</v>
+        <v>0.0484</v>
       </c>
       <c r="H58" t="n">
-        <v>1129</v>
+        <v>1166.5</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>
@@ -5372,7 +5372,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5331,13 +5331,13 @@
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>31047.75</v>
+        <v>31014</v>
       </c>
       <c r="F58" t="n">
-        <v>1434.07</v>
+        <v>1400.32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0473</v>
       </c>
       <c r="H58" t="n">
         <v>1166.5</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5331,13 +5331,13 @@
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>31014</v>
+        <v>31002</v>
       </c>
       <c r="F58" t="n">
-        <v>1400.32</v>
+        <v>1388.32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0473</v>
+        <v>0.0469</v>
       </c>
       <c r="H58" t="n">
         <v>1166.5</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5331,10 +5331,10 @@
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>31002</v>
+        <v>31001.25</v>
       </c>
       <c r="F58" t="n">
-        <v>1388.32</v>
+        <v>1387.57</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0.0469</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>31070.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D58" t="n">
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>31001.25</v>
+        <v>30956.75</v>
       </c>
       <c r="F58" t="n">
-        <v>1387.57</v>
+        <v>1343.07</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0469</v>
+        <v>0.0454</v>
       </c>
       <c r="H58" t="n">
-        <v>1166.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,22 +5325,22 @@
         <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>31094.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D58" t="n">
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>30956.75</v>
+        <v>30792</v>
       </c>
       <c r="F58" t="n">
-        <v>1343.07</v>
+        <v>1178.32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0454</v>
+        <v>0.0398</v>
       </c>
       <c r="H58" t="n">
-        <v>1190.75</v>
+        <v>1161.5</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,25 +659,25 @@
         <v>432.25</v>
       </c>
       <c r="I2" t="n">
-        <v>22420</v>
+        <v>22503.5</v>
       </c>
       <c r="J2" t="n">
-        <v>23068.38</v>
+        <v>23099.69</v>
       </c>
       <c r="K2" t="n">
-        <v>23262.25</v>
+        <v>23283.12</v>
       </c>
       <c r="L2" t="n">
-        <v>23456.12</v>
+        <v>23466.56</v>
       </c>
       <c r="M2" t="n">
-        <v>23877.25</v>
+        <v>23856.38</v>
       </c>
       <c r="N2" t="n">
-        <v>24298.38</v>
+        <v>24246.19</v>
       </c>
       <c r="O2" t="n">
-        <v>24265</v>
+        <v>24223.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,7 +690,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -772,7 +772,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -858,7 +858,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -938,7 +938,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1020,7 +1020,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1100,7 +1100,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1184,7 +1184,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1268,7 +1268,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1352,7 +1352,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1436,7 +1436,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1528,7 +1528,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1606,7 +1606,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1686,7 +1686,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1764,7 +1764,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1850,7 +1850,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1938,7 +1938,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2022,7 +2022,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2100,7 +2100,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2192,7 +2192,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2270,7 +2270,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2356,7 +2356,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2442,7 +2442,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2524,7 +2524,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2614,7 +2614,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2696,7 +2696,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2778,7 +2778,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2862,7 +2862,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2948,7 +2948,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3032,7 +3032,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3116,7 +3116,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3202,7 +3202,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3286,7 +3286,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3370,7 +3370,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3452,7 +3452,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3534,7 +3534,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3614,7 +3614,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3694,7 +3694,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3778,7 +3778,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -3862,7 +3862,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3946,7 +3946,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4032,7 +4032,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4114,7 +4114,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4196,7 +4196,7 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4284,7 +4284,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4366,7 +4366,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4452,7 +4452,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -4538,7 +4538,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4618,7 +4618,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4698,7 +4698,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -4780,7 +4780,7 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4866,7 +4866,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4954,7 +4954,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5036,7 +5036,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5120,7 +5120,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -5204,7 +5204,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -5288,7 +5288,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5325,22 +5325,22 @@
         <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D58" t="n">
         <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>30792</v>
+        <v>30730.25</v>
       </c>
       <c r="F58" t="n">
-        <v>1178.32</v>
+        <v>1116.57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0398</v>
+        <v>0.0377</v>
       </c>
       <c r="H58" t="n">
-        <v>1161.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I58" t="n">
         <v>27862.25</v>
@@ -5372,7 +5372,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23602</v>
+        <v>23479</v>
       </c>
       <c r="C2" t="n">
-        <v>23803.75</v>
+        <v>23902</v>
       </c>
       <c r="D2" t="n">
-        <v>23371.5</v>
+        <v>23025.25</v>
       </c>
       <c r="E2" t="n">
-        <v>23461.75</v>
+        <v>23684</v>
       </c>
       <c r="F2" t="n">
-        <v>-108</v>
+        <v>222.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0046</v>
+        <v>0.0095</v>
       </c>
       <c r="H2" t="n">
-        <v>432.25</v>
+        <v>876.75</v>
       </c>
       <c r="I2" t="n">
-        <v>22503.5</v>
+        <v>22939.25</v>
       </c>
       <c r="J2" t="n">
-        <v>23099.69</v>
+        <v>22966.56</v>
       </c>
       <c r="K2" t="n">
-        <v>23283.12</v>
+        <v>23245.62</v>
       </c>
       <c r="L2" t="n">
-        <v>23466.56</v>
+        <v>23524.69</v>
       </c>
       <c r="M2" t="n">
-        <v>23856.38</v>
+        <v>23677.88</v>
       </c>
       <c r="N2" t="n">
-        <v>24246.19</v>
+        <v>23831.06</v>
       </c>
       <c r="O2" t="n">
-        <v>24223.25</v>
+        <v>24236</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,19 +685,25 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -716,50 +722,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23479</v>
+        <v>23673.5</v>
       </c>
       <c r="C3" t="n">
-        <v>23902</v>
+        <v>24159</v>
       </c>
       <c r="D3" t="n">
-        <v>23025.25</v>
+        <v>23650.25</v>
       </c>
       <c r="E3" t="n">
-        <v>23684</v>
+        <v>24113.25</v>
       </c>
       <c r="F3" t="n">
-        <v>222.25</v>
+        <v>429.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0181</v>
       </c>
       <c r="H3" t="n">
-        <v>876.75</v>
+        <v>508.75</v>
       </c>
       <c r="I3" t="n">
-        <v>22939.25</v>
+        <v>22148.5</v>
       </c>
       <c r="J3" t="n">
-        <v>22966.56</v>
+        <v>22917.44</v>
       </c>
       <c r="K3" t="n">
         <v>23245.62</v>
       </c>
       <c r="L3" t="n">
-        <v>23524.69</v>
+        <v>23573.81</v>
       </c>
       <c r="M3" t="n">
-        <v>23677.88</v>
+        <v>24122.38</v>
       </c>
       <c r="N3" t="n">
-        <v>23831.06</v>
+        <v>24670.94</v>
       </c>
       <c r="O3" t="n">
-        <v>24236</v>
+        <v>24778.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,12 +773,10 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -782,10 +786,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -795,59 +797,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23673.5</v>
+        <v>24115.25</v>
       </c>
       <c r="C4" t="n">
-        <v>24159</v>
+        <v>24575</v>
       </c>
       <c r="D4" t="n">
-        <v>23650.25</v>
+        <v>24003.75</v>
       </c>
       <c r="E4" t="n">
-        <v>24113.25</v>
+        <v>24568.07</v>
       </c>
       <c r="F4" t="n">
-        <v>429.25</v>
+        <v>454.82</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0181</v>
+        <v>0.0189</v>
       </c>
       <c r="H4" t="n">
-        <v>508.75</v>
+        <v>571.25</v>
       </c>
       <c r="I4" t="n">
-        <v>22148.5</v>
+        <v>23141.5</v>
       </c>
       <c r="J4" t="n">
-        <v>22917.44</v>
+        <v>23708.81</v>
       </c>
       <c r="K4" t="n">
-        <v>23245.62</v>
+        <v>23858.88</v>
       </c>
       <c r="L4" t="n">
-        <v>23573.81</v>
+        <v>24008.94</v>
       </c>
       <c r="M4" t="n">
-        <v>24122.38</v>
+        <v>24367.62</v>
       </c>
       <c r="N4" t="n">
-        <v>24670.94</v>
+        <v>24726.31</v>
       </c>
       <c r="O4" t="n">
-        <v>24778.75</v>
+        <v>24667.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,21 +856,23 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -884,50 +884,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24115.25</v>
+        <v>24850</v>
       </c>
       <c r="C5" t="n">
-        <v>24575</v>
+        <v>25027.25</v>
       </c>
       <c r="D5" t="n">
-        <v>24003.75</v>
+        <v>24422.5</v>
       </c>
       <c r="E5" t="n">
-        <v>24568.07</v>
+        <v>24726.75</v>
       </c>
       <c r="F5" t="n">
-        <v>454.82</v>
+        <v>158.68</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0065</v>
       </c>
       <c r="H5" t="n">
-        <v>571.25</v>
+        <v>604.75</v>
       </c>
       <c r="I5" t="n">
-        <v>23141.5</v>
+        <v>23432.5</v>
       </c>
       <c r="J5" t="n">
-        <v>23708.81</v>
+        <v>24136.17</v>
       </c>
       <c r="K5" t="n">
-        <v>23858.88</v>
+        <v>24282.45</v>
       </c>
       <c r="L5" t="n">
-        <v>24008.94</v>
+        <v>24428.72</v>
       </c>
       <c r="M5" t="n">
-        <v>24367.62</v>
+        <v>24853.7</v>
       </c>
       <c r="N5" t="n">
-        <v>24726.31</v>
+        <v>25278.67</v>
       </c>
       <c r="O5" t="n">
-        <v>24667.75</v>
+        <v>25146.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,23 +938,21 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -966,50 +964,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24850</v>
+        <v>24726.5</v>
       </c>
       <c r="C6" t="n">
-        <v>25027.25</v>
+        <v>25196.5</v>
       </c>
       <c r="D6" t="n">
-        <v>24422.5</v>
+        <v>24633.25</v>
       </c>
       <c r="E6" t="n">
-        <v>24726.75</v>
+        <v>24992</v>
       </c>
       <c r="F6" t="n">
-        <v>158.68</v>
+        <v>265.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.0107</v>
       </c>
       <c r="H6" t="n">
-        <v>604.75</v>
+        <v>563.25</v>
       </c>
       <c r="I6" t="n">
-        <v>23432.5</v>
+        <v>23817.75</v>
       </c>
       <c r="J6" t="n">
-        <v>24136.17</v>
+        <v>24122.94</v>
       </c>
       <c r="K6" t="n">
-        <v>24282.45</v>
+        <v>24424.38</v>
       </c>
       <c r="L6" t="n">
-        <v>24428.72</v>
+        <v>24725.81</v>
       </c>
       <c r="M6" t="n">
-        <v>24853.7</v>
+        <v>25029.12</v>
       </c>
       <c r="N6" t="n">
-        <v>25278.67</v>
+        <v>25332.44</v>
       </c>
       <c r="O6" t="n">
-        <v>25146.25</v>
+        <v>25632</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,7 +1018,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1046,68 +1044,72 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C7" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D7" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E7" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F7" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H7" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I7" t="n">
-        <v>23817.75</v>
+        <v>24070</v>
       </c>
       <c r="J7" t="n">
-        <v>24122.94</v>
+        <v>24467.31</v>
       </c>
       <c r="K7" t="n">
-        <v>24424.38</v>
+        <v>24710.38</v>
       </c>
       <c r="L7" t="n">
-        <v>24725.81</v>
+        <v>24953.44</v>
       </c>
       <c r="M7" t="n">
-        <v>25029.12</v>
+        <v>25273.62</v>
       </c>
       <c r="N7" t="n">
-        <v>25332.44</v>
+        <v>25593.81</v>
       </c>
       <c r="O7" t="n">
-        <v>25632</v>
+        <v>25759.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1116,84 +1118,84 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C8" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D8" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E8" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H8" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I8" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J8" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K8" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L8" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M8" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N8" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O8" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1207,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C9" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D9" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E9" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F9" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H9" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I9" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J9" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K9" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L9" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M9" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N9" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O9" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,7 +1270,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1291,57 +1293,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C10" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D10" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E10" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F10" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H10" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I10" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J10" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K10" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L10" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M10" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N10" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O10" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1352,7 +1354,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1365,8 +1367,10 @@
       <c r="U10" s="8" t="n">
         <v/>
       </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
@@ -1382,155 +1386,147 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C11" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D11" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E11" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F11" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H11" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I11" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J11" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K11" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L11" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M11" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N11" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O11" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>27098</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C12" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D12" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E12" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F12" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H12" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I12" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J12" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K12" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L12" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M12" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N12" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O12" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>27822.75</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1552,50 +1548,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C13" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D13" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E13" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H13" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I13" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J13" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K13" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L13" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M13" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N13" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O13" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,12 +1599,14 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1630,50 +1628,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C14" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D14" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E14" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F14" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H14" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I14" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J14" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K14" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L14" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M14" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N14" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O14" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,22 +1679,24 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1705,55 +1705,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C15" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D15" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E15" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F15" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H15" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I15" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J15" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K15" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L15" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M15" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N15" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O15" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,20 +1768,18 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1796,69 +1798,71 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C16" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D16" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E16" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F16" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H16" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I16" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J16" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K16" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L16" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M16" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N16" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O16" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1873,74 +1877,72 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C17" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D17" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E17" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F17" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H17" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I17" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J17" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K17" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L17" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M17" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N17" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O17" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1957,59 +1959,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C18" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D18" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E18" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H18" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I18" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J18" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K18" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L18" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M18" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N18" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O18" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,21 +2015,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2041,79 +2041,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C19" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D19" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E19" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F19" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H19" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I19" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J19" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K19" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L19" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M19" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N19" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O19" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>26262.25</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2123,92 +2129,86 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C20" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D20" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E20" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H20" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I20" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J20" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K20" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L20" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M20" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N20" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O20" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2216,74 +2216,74 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C21" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D21" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E21" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F21" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I21" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J21" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K21" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L21" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M21" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N21" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O21" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2293,55 +2293,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C22" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D22" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E22" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H22" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I22" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J22" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K22" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L22" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M22" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N22" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O22" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,12 +2357,12 @@
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2377,79 +2381,77 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C23" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D23" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E23" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F23" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H23" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I23" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J23" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K23" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L23" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M23" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N23" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O23" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2463,76 +2465,80 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C24" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D24" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E24" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H24" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I24" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J24" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K24" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L24" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M24" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N24" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O24" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>27332.75</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2547,76 +2553,70 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C25" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D25" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E25" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H25" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I25" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J25" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K25" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L25" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M25" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N25" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O25" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>27815.75</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2635,57 +2635,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C26" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D26" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E26" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H26" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I26" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J26" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K26" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L26" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M26" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N26" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O26" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2724,50 +2724,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C27" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D27" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E27" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F27" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H27" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I27" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J27" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K27" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L27" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M27" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N27" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O27" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2775,16 +2775,20 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2799,57 +2803,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C28" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D28" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E28" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F28" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H28" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I28" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J28" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K28" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L28" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M28" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N28" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O28" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,18 +2863,16 @@
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2885,57 +2887,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C29" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D29" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E29" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H29" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I29" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J29" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K29" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L29" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M29" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N29" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O29" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2948,13 +2950,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2976,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C30" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D30" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E30" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F30" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H30" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I30" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J30" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K30" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L30" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M30" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N30" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O30" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,20 +3031,16 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3055,74 +3055,80 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C31" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D31" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E31" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H31" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I31" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J31" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K31" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L31" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M31" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N31" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O31" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3137,81 +3143,77 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C32" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D32" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E32" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H32" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I32" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J32" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K32" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L32" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M32" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N32" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O32" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3225,57 +3227,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C33" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D33" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E33" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F33" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H33" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I33" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J33" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K33" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L33" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M33" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N33" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O33" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3286,80 +3288,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C34" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D34" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E34" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F34" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H34" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I34" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J34" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K34" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L34" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M34" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N34" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O34" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3370,7 +3370,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3398,50 +3398,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C35" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D35" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E35" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F35" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H35" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I35" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J35" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K35" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L35" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M35" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N35" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O35" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3452,23 +3452,21 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3480,50 +3478,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C36" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D36" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E36" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F36" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H36" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I36" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J36" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K36" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L36" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M36" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N36" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O36" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3534,7 +3532,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3560,50 +3558,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C37" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D37" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E37" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F37" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H37" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I37" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J37" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K37" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L37" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M37" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N37" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O37" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3614,21 +3612,25 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3640,50 +3642,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C38" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D38" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E38" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F38" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H38" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I38" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J38" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K38" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L38" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M38" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N38" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O38" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3694,80 +3696,78 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C39" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D39" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E39" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F39" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H39" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I39" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J39" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K39" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L39" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M39" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N39" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O39" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,16 +3775,20 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3799,57 +3803,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C40" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D40" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E40" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F40" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H40" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I40" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J40" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K40" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L40" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M40" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N40" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O40" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3857,12 +3861,10 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3883,78 +3885,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C41" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D41" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E41" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F41" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H41" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I41" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J41" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K41" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L41" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M41" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N41" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O41" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>31395.75</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3962,79 +3964,77 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C42" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D42" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F42" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H42" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I42" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J42" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K42" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L42" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M42" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N42" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O42" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32834.25</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4060,50 +4060,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C43" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D43" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E43" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F43" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H43" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I43" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J43" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K43" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L43" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M43" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N43" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O43" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4114,13 +4114,15 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4135,76 +4137,78 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C44" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D44" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E44" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F44" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H44" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I44" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J44" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K44" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L44" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M44" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N44" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O44" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4219,79 +4223,77 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C45" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D45" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H45" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I45" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J45" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K45" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L45" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M45" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N45" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O45" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4305,57 +4307,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C46" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D46" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E46" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F46" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H46" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I46" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J46" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K46" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L46" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M46" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N46" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O46" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4363,18 +4365,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4389,63 +4391,65 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C47" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D47" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E47" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F47" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H47" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I47" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J47" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K47" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L47" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M47" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N47" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O47" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4454,7 +4458,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4471,74 +4475,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C48" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D48" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E48" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F48" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H48" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I48" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J48" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K48" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L48" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M48" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N48" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O48" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4562,50 +4560,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C49" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D49" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E49" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F49" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H49" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I49" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J49" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K49" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L49" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M49" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N49" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O49" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,12 +4613,12 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4637,55 +4635,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C50" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D50" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E50" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F50" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H50" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I50" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J50" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K50" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L50" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M50" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N50" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O50" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4693,21 +4695,23 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4719,57 +4723,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C51" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D51" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E51" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F51" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H51" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I51" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J51" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K51" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L51" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M51" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N51" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O51" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4780,20 +4784,18 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4812,69 +4814,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C52" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D52" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E52" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F52" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H52" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I52" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J52" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K52" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L52" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M52" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N52" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O52" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4889,74 +4893,70 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C53" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D53" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E53" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F53" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H53" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I53" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J53" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K53" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L53" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M53" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N53" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O53" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4982,50 +4982,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C54" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D54" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E54" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F54" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H54" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I54" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J54" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K54" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L54" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M54" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N54" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O54" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5033,12 +5033,14 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5064,50 +5066,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C55" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D55" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E55" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F55" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H55" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I55" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J55" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K55" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L55" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M55" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N55" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O55" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5122,7 +5124,7 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5141,57 +5143,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C56" t="n">
-        <v>29764.75</v>
+        <v>29665.25</v>
       </c>
       <c r="D56" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E56" t="n">
-        <v>29387</v>
+        <v>29613.68</v>
       </c>
       <c r="F56" t="n">
-        <v>-178.25</v>
+        <v>226.68</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0077</v>
       </c>
       <c r="H56" t="n">
-        <v>724.25</v>
+        <v>901.5</v>
       </c>
       <c r="I56" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J56" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K56" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L56" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M56" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N56" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O56" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5206,11 +5208,13 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5225,57 +5229,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28997.75</v>
+        <v>29938</v>
       </c>
       <c r="C57" t="n">
-        <v>29665.25</v>
+        <v>31094.75</v>
       </c>
       <c r="D57" t="n">
-        <v>28763.75</v>
+        <v>29904</v>
       </c>
       <c r="E57" t="n">
-        <v>29613.68</v>
+        <v>30889.25</v>
       </c>
       <c r="F57" t="n">
-        <v>226.68</v>
+        <v>1275.57</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0431</v>
       </c>
       <c r="H57" t="n">
-        <v>901.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I57" t="n">
-        <v>28316.25</v>
+        <v>27862.25</v>
       </c>
       <c r="J57" t="n">
-        <v>28654.94</v>
+        <v>28911.77</v>
       </c>
       <c r="K57" t="n">
-        <v>29024.88</v>
+        <v>29162.93</v>
       </c>
       <c r="L57" t="n">
-        <v>29394.81</v>
+        <v>29414.09</v>
       </c>
       <c r="M57" t="n">
-        <v>29749.12</v>
+        <v>30064.43</v>
       </c>
       <c r="N57" t="n">
-        <v>30103.44</v>
+        <v>30714.77</v>
       </c>
       <c r="O57" t="n">
-        <v>30489</v>
+        <v>30566.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5283,121 +5287,35 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>29938</v>
-      </c>
-      <c r="C58" t="n">
-        <v>31094.75</v>
-      </c>
-      <c r="D58" t="n">
-        <v>29904</v>
-      </c>
-      <c r="E58" t="n">
-        <v>30730.25</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1116.57</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0377</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1190.75</v>
-      </c>
-      <c r="I58" t="n">
-        <v>27862.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>28911.77</v>
-      </c>
-      <c r="K58" t="n">
-        <v>29162.93</v>
-      </c>
-      <c r="L58" t="n">
-        <v>29414.09</v>
-      </c>
-      <c r="M58" t="n">
-        <v>30064.43</v>
-      </c>
-      <c r="N58" t="n">
-        <v>30714.77</v>
-      </c>
-      <c r="O58" t="n">
-        <v>30566.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="V57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5317,6 +5317,88 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>30560.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>30589</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30536.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>30548.5</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-340.75</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="H58" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>28713.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>29893.44</v>
+      </c>
+      <c r="K58" t="n">
+        <v>30293.88</v>
+      </c>
+      <c r="L58" t="n">
+        <v>30694.31</v>
+      </c>
+      <c r="M58" t="n">
+        <v>31484.62</v>
+      </c>
+      <c r="N58" t="n">
+        <v>32274.94</v>
+      </c>
+      <c r="O58" t="n">
+        <v>32285.5</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30560.5</v>
+        <v>30870</v>
       </c>
       <c r="C58" t="n">
-        <v>30589</v>
+        <v>30920.75</v>
       </c>
       <c r="D58" t="n">
-        <v>30536.25</v>
+        <v>30356.75</v>
       </c>
       <c r="E58" t="n">
-        <v>30548.5</v>
+        <v>30693.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-340.75</v>
+        <v>-195.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.011</v>
+        <v>-0.0063</v>
       </c>
       <c r="H58" t="n">
-        <v>52.75</v>
+        <v>564</v>
       </c>
       <c r="I58" t="n">
         <v>28713.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>876.75</v>
       </c>
       <c r="I2" t="n">
-        <v>22939.25</v>
+        <v>22991.25</v>
       </c>
       <c r="J2" t="n">
-        <v>22966.56</v>
+        <v>22986.06</v>
       </c>
       <c r="K2" t="n">
-        <v>23245.62</v>
+        <v>23258.62</v>
       </c>
       <c r="L2" t="n">
-        <v>23524.69</v>
+        <v>23531.19</v>
       </c>
       <c r="M2" t="n">
-        <v>23677.88</v>
+        <v>23664.88</v>
       </c>
       <c r="N2" t="n">
-        <v>23831.06</v>
+        <v>23798.56</v>
       </c>
       <c r="O2" t="n">
-        <v>24236</v>
+        <v>24210</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5333,13 +5333,13 @@
         <v>30356.75</v>
       </c>
       <c r="E58" t="n">
-        <v>30693.75</v>
+        <v>30729.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-195.5</v>
+        <v>-160</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0063</v>
+        <v>-0.0052</v>
       </c>
       <c r="H58" t="n">
         <v>564</v>
@@ -5374,9 +5374,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5333,13 +5333,13 @@
         <v>30356.75</v>
       </c>
       <c r="E58" t="n">
-        <v>30729.25</v>
+        <v>30786.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-160</v>
+        <v>-102.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0052</v>
+        <v>-0.0033</v>
       </c>
       <c r="H58" t="n">
         <v>564</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23479</v>
+        <v>23673.5</v>
       </c>
       <c r="C2" t="n">
-        <v>23902</v>
+        <v>24159</v>
       </c>
       <c r="D2" t="n">
-        <v>23025.25</v>
+        <v>23650.25</v>
       </c>
       <c r="E2" t="n">
-        <v>23684</v>
+        <v>24113.25</v>
       </c>
       <c r="F2" t="n">
-        <v>222.25</v>
+        <v>429.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0181</v>
       </c>
       <c r="H2" t="n">
-        <v>876.75</v>
+        <v>508.75</v>
       </c>
       <c r="I2" t="n">
-        <v>22991.25</v>
+        <v>22148.5</v>
       </c>
       <c r="J2" t="n">
-        <v>22986.06</v>
+        <v>22917.44</v>
       </c>
       <c r="K2" t="n">
-        <v>23258.62</v>
+        <v>23245.62</v>
       </c>
       <c r="L2" t="n">
-        <v>23531.19</v>
+        <v>23573.81</v>
       </c>
       <c r="M2" t="n">
-        <v>23664.88</v>
+        <v>24122.38</v>
       </c>
       <c r="N2" t="n">
-        <v>23798.56</v>
+        <v>24670.94</v>
       </c>
       <c r="O2" t="n">
-        <v>24210</v>
+        <v>24778.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -700,10 +698,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -713,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23673.5</v>
+        <v>24115.25</v>
       </c>
       <c r="C3" t="n">
-        <v>24159</v>
+        <v>24575</v>
       </c>
       <c r="D3" t="n">
-        <v>23650.25</v>
+        <v>24003.75</v>
       </c>
       <c r="E3" t="n">
-        <v>24113.25</v>
+        <v>24568.07</v>
       </c>
       <c r="F3" t="n">
-        <v>429.25</v>
+        <v>454.82</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0181</v>
+        <v>0.0189</v>
       </c>
       <c r="H3" t="n">
-        <v>508.75</v>
+        <v>571.25</v>
       </c>
       <c r="I3" t="n">
-        <v>22148.5</v>
+        <v>23141.5</v>
       </c>
       <c r="J3" t="n">
-        <v>22917.44</v>
+        <v>23708.81</v>
       </c>
       <c r="K3" t="n">
-        <v>23245.62</v>
+        <v>23858.88</v>
       </c>
       <c r="L3" t="n">
-        <v>23573.81</v>
+        <v>24008.94</v>
       </c>
       <c r="M3" t="n">
-        <v>24122.38</v>
+        <v>24367.62</v>
       </c>
       <c r="N3" t="n">
-        <v>24670.94</v>
+        <v>24726.31</v>
       </c>
       <c r="O3" t="n">
-        <v>24778.75</v>
+        <v>24667.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -783,14 +775,16 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -802,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24115.25</v>
+        <v>24850</v>
       </c>
       <c r="C4" t="n">
-        <v>24575</v>
+        <v>25027.25</v>
       </c>
       <c r="D4" t="n">
-        <v>24003.75</v>
+        <v>24422.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24568.07</v>
+        <v>24726.75</v>
       </c>
       <c r="F4" t="n">
-        <v>454.82</v>
+        <v>158.68</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0065</v>
       </c>
       <c r="H4" t="n">
-        <v>571.25</v>
+        <v>604.75</v>
       </c>
       <c r="I4" t="n">
-        <v>23141.5</v>
+        <v>23432.5</v>
       </c>
       <c r="J4" t="n">
-        <v>23708.81</v>
+        <v>24136.17</v>
       </c>
       <c r="K4" t="n">
-        <v>23858.88</v>
+        <v>24282.45</v>
       </c>
       <c r="L4" t="n">
-        <v>24008.94</v>
+        <v>24428.72</v>
       </c>
       <c r="M4" t="n">
-        <v>24367.62</v>
+        <v>24853.7</v>
       </c>
       <c r="N4" t="n">
-        <v>24726.31</v>
+        <v>25278.67</v>
       </c>
       <c r="O4" t="n">
-        <v>24667.75</v>
+        <v>25146.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,16 +857,14 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -884,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24850</v>
+        <v>24726.5</v>
       </c>
       <c r="C5" t="n">
-        <v>25027.25</v>
+        <v>25196.5</v>
       </c>
       <c r="D5" t="n">
-        <v>24422.5</v>
+        <v>24633.25</v>
       </c>
       <c r="E5" t="n">
-        <v>24726.75</v>
+        <v>24992</v>
       </c>
       <c r="F5" t="n">
-        <v>158.68</v>
+        <v>265.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.0107</v>
       </c>
       <c r="H5" t="n">
-        <v>604.75</v>
+        <v>563.25</v>
       </c>
       <c r="I5" t="n">
-        <v>23432.5</v>
+        <v>23817.75</v>
       </c>
       <c r="J5" t="n">
-        <v>24136.17</v>
+        <v>24122.94</v>
       </c>
       <c r="K5" t="n">
-        <v>24282.45</v>
+        <v>24424.38</v>
       </c>
       <c r="L5" t="n">
-        <v>24428.72</v>
+        <v>24725.81</v>
       </c>
       <c r="M5" t="n">
-        <v>24853.7</v>
+        <v>25029.12</v>
       </c>
       <c r="N5" t="n">
-        <v>25278.67</v>
+        <v>25332.44</v>
       </c>
       <c r="O5" t="n">
-        <v>25146.25</v>
+        <v>25632</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -964,68 +956,72 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C6" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D6" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E6" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F6" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H6" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I6" t="n">
-        <v>23817.75</v>
+        <v>24070</v>
       </c>
       <c r="J6" t="n">
-        <v>24122.94</v>
+        <v>24467.31</v>
       </c>
       <c r="K6" t="n">
-        <v>24424.38</v>
+        <v>24710.38</v>
       </c>
       <c r="L6" t="n">
-        <v>24725.81</v>
+        <v>24953.44</v>
       </c>
       <c r="M6" t="n">
-        <v>25029.12</v>
+        <v>25273.62</v>
       </c>
       <c r="N6" t="n">
-        <v>25332.44</v>
+        <v>25593.81</v>
       </c>
       <c r="O6" t="n">
-        <v>25632</v>
+        <v>25759.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1034,84 +1030,84 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C7" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D7" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E7" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H7" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I7" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J7" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K7" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L7" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M7" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N7" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O7" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1125,57 +1121,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C8" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D8" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E8" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F8" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H8" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I8" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J8" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K8" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L8" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M8" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N8" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O8" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1209,57 +1205,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C9" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D9" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E9" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F9" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H9" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I9" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J9" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K9" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L9" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M9" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N9" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O9" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,8 +1279,10 @@
       <c r="U9" s="8" t="n">
         <v/>
       </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
@@ -1300,155 +1298,147 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C10" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D10" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E10" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F10" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H10" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I10" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J10" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K10" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L10" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M10" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N10" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O10" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>27098</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C11" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D11" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E11" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F11" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H11" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I11" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J11" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K11" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L11" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M11" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N11" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O11" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>27822.75</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1470,50 +1460,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C12" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D12" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E12" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H12" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I12" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J12" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K12" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L12" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M12" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N12" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O12" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,12 +1511,14 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1548,50 +1540,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C13" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D13" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E13" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F13" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H13" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I13" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J13" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K13" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L13" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M13" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N13" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O13" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1599,22 +1591,24 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1623,55 +1617,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C14" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D14" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E14" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F14" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H14" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I14" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J14" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K14" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L14" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M14" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N14" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O14" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,13 +1687,11 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1714,70 +1710,72 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C15" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D15" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E15" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F15" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H15" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I15" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J15" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K15" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L15" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M15" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N15" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O15" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1791,65 +1789,63 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C16" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D16" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E16" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F16" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H16" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I16" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J16" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K16" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L16" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M16" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N16" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O16" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q16" s="6" t="n">
+        <v/>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
@@ -1858,7 +1854,7 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1875,59 +1871,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C17" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D17" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E17" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H17" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I17" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J17" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K17" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L17" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M17" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N17" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O17" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,21 +1927,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1959,79 +1953,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C18" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D18" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E18" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F18" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H18" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I18" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J18" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K18" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L18" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M18" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N18" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O18" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>26262.25</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2041,92 +2041,86 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C19" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D19" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E19" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H19" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I19" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J19" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K19" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L19" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M19" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N19" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O19" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2134,75 +2128,75 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C20" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D20" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E20" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F20" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I20" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J20" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K20" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L20" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M20" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N20" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O20" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2211,55 +2205,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C21" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D21" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E21" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H21" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I21" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J21" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K21" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L21" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M21" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N21" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O21" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2271,12 +2269,12 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2295,79 +2293,77 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C22" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D22" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E22" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F22" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H22" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I22" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J22" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K22" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L22" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M22" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N22" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O22" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2381,77 +2377,81 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C23" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D23" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E23" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H23" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I23" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J23" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K23" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L23" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M23" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N23" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O23" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+        <v>27332.75</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2465,76 +2465,70 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C24" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D24" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E24" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H24" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I24" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J24" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K24" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L24" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M24" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N24" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O24" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27815.75</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2553,57 +2547,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C25" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D25" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E25" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F25" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H25" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I25" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J25" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K25" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L25" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M25" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N25" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O25" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,9 +2608,9 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2642,50 +2636,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C26" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D26" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E26" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F26" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H26" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I26" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J26" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K26" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L26" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M26" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N26" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O26" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2693,16 +2687,20 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2717,57 +2715,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C27" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D27" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E27" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H27" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I27" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J27" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K27" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L27" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M27" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N27" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O27" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2777,18 +2775,16 @@
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2803,57 +2799,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C28" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D28" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E28" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F28" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H28" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I28" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J28" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K28" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L28" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M28" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N28" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O28" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2871,8 +2867,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2894,50 +2892,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C29" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D29" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E29" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F29" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H29" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I29" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J29" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K29" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L29" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M29" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N29" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O29" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2945,20 +2943,16 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2973,74 +2967,80 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C30" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D30" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E30" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F30" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H30" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J30" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K30" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L30" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M30" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N30" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O30" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3055,81 +3055,77 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C31" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D31" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E31" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H31" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I31" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J31" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K31" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L31" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M31" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N31" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O31" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3143,57 +3139,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C32" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D32" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E32" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F32" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H32" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I32" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J32" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K32" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L32" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M32" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N32" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O32" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3211,73 +3207,71 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C33" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D33" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E33" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F33" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H33" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I33" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J33" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K33" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L33" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M33" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N33" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O33" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3316,50 +3310,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C34" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D34" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E34" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F34" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H34" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I34" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J34" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K34" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L34" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M34" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N34" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O34" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3377,16 +3371,14 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3398,50 +3390,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C35" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D35" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E35" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F35" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H35" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I35" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J35" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K35" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L35" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M35" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N35" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O35" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3478,50 +3470,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C36" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D36" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E36" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F36" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H36" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I36" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J36" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K36" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L36" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M36" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N36" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O36" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,14 +3531,18 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3558,50 +3554,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C37" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D37" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E37" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F37" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H37" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I37" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J37" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K37" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L37" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M37" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N37" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O37" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3614,78 +3610,76 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C38" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D38" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E38" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H38" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I38" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J38" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K38" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L38" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M38" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N38" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O38" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,16 +3687,20 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3717,57 +3715,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C39" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D39" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E39" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F39" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H39" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I39" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J39" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K39" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L39" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M39" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N39" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O39" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,10 +3773,8 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
@@ -3801,158 +3797,156 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C40" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D40" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E40" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F40" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H40" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I40" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J40" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K40" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L40" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M40" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N40" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O40" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+        <v>31395.75</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C41" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D41" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F41" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H41" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I41" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J41" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K41" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L41" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M41" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N41" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O41" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>32834.25</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3978,50 +3972,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C42" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D42" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E42" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F42" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H42" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I42" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J42" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K42" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L42" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M42" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N42" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O42" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4034,11 +4028,13 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4053,77 +4049,79 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C43" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D43" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E43" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F43" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H43" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I43" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J43" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K43" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L43" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M43" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N43" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O43" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4137,79 +4135,77 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C44" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D44" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E44" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F44" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H44" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I44" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J44" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K44" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L44" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M44" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N44" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O44" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4223,57 +4219,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C45" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D45" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F45" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H45" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I45" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J45" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K45" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L45" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M45" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N45" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O45" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4281,18 +4277,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4307,72 +4303,74 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C46" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D46" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E46" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F46" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H46" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I46" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J46" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K46" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L46" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M46" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N46" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O46" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4389,71 +4387,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C47" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D47" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E47" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H47" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I47" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J47" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K47" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L47" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M47" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N47" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O47" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4480,50 +4472,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C48" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D48" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E48" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F48" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H48" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I48" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J48" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K48" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L48" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M48" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N48" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O48" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4533,12 +4525,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4555,55 +4547,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C49" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D49" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E49" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F49" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H49" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I49" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J49" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K49" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L49" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M49" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N49" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O49" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4611,21 +4607,23 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4637,57 +4635,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C50" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D50" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E50" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F50" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H50" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I50" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J50" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K50" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L50" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M50" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N50" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O50" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4705,13 +4703,11 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4730,70 +4726,72 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C51" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D51" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E51" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F51" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H51" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I51" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J51" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K51" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L51" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M51" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N51" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O51" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4807,74 +4805,70 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C52" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D52" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E52" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F52" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H52" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I52" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J52" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K52" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L52" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M52" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N52" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O52" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4900,50 +4894,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C53" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D53" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E53" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F53" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H53" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I53" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J53" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K53" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L53" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M53" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N53" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O53" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4951,12 +4945,14 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4982,50 +4978,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C54" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D54" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E54" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F54" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H54" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I54" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J54" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K54" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L54" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M54" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N54" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O54" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5038,9 +5034,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5059,57 +5055,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C55" t="n">
-        <v>29764.75</v>
+        <v>29665.25</v>
       </c>
       <c r="D55" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E55" t="n">
-        <v>29387</v>
+        <v>29613.68</v>
       </c>
       <c r="F55" t="n">
-        <v>-178.25</v>
+        <v>226.68</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0077</v>
       </c>
       <c r="H55" t="n">
-        <v>724.25</v>
+        <v>901.5</v>
       </c>
       <c r="I55" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J55" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K55" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L55" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M55" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N55" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O55" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5122,13 +5118,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5143,57 +5141,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28997.75</v>
+        <v>29938</v>
       </c>
       <c r="C56" t="n">
-        <v>29665.25</v>
+        <v>31094.75</v>
       </c>
       <c r="D56" t="n">
-        <v>28763.75</v>
+        <v>29904</v>
       </c>
       <c r="E56" t="n">
-        <v>29613.68</v>
+        <v>30889.25</v>
       </c>
       <c r="F56" t="n">
-        <v>226.68</v>
+        <v>1275.57</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0431</v>
       </c>
       <c r="H56" t="n">
-        <v>901.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I56" t="n">
-        <v>28316.25</v>
+        <v>27862.25</v>
       </c>
       <c r="J56" t="n">
-        <v>28654.94</v>
+        <v>28911.77</v>
       </c>
       <c r="K56" t="n">
-        <v>29024.88</v>
+        <v>29162.93</v>
       </c>
       <c r="L56" t="n">
-        <v>29394.81</v>
+        <v>29414.09</v>
       </c>
       <c r="M56" t="n">
-        <v>29749.12</v>
+        <v>30064.43</v>
       </c>
       <c r="N56" t="n">
-        <v>30103.44</v>
+        <v>30714.77</v>
       </c>
       <c r="O56" t="n">
-        <v>30489</v>
+        <v>30566.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5201,85 +5199,83 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29938</v>
+        <v>30870</v>
       </c>
       <c r="C57" t="n">
-        <v>31094.75</v>
+        <v>31282.5</v>
       </c>
       <c r="D57" t="n">
-        <v>29904</v>
+        <v>30356.75</v>
       </c>
       <c r="E57" t="n">
-        <v>30889.25</v>
+        <v>31061.75</v>
       </c>
       <c r="F57" t="n">
-        <v>1275.57</v>
+        <v>172.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0056</v>
       </c>
       <c r="H57" t="n">
-        <v>1190.75</v>
+        <v>925.75</v>
       </c>
       <c r="I57" t="n">
-        <v>27862.25</v>
+        <v>28713.25</v>
       </c>
       <c r="J57" t="n">
-        <v>28911.77</v>
+        <v>29893.44</v>
       </c>
       <c r="K57" t="n">
-        <v>29162.93</v>
+        <v>30293.88</v>
       </c>
       <c r="L57" t="n">
-        <v>29414.09</v>
+        <v>30694.31</v>
       </c>
       <c r="M57" t="n">
-        <v>30064.43</v>
+        <v>31484.62</v>
       </c>
       <c r="N57" t="n">
-        <v>30714.77</v>
+        <v>32274.94</v>
       </c>
       <c r="O57" t="n">
-        <v>30566.75</v>
+        <v>32285.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5292,23 +5288,17 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5316,88 +5306,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>30870</v>
-      </c>
-      <c r="C58" t="n">
-        <v>30920.75</v>
-      </c>
-      <c r="D58" t="n">
-        <v>30356.75</v>
-      </c>
-      <c r="E58" t="n">
-        <v>30786.75</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-102.5</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0033</v>
-      </c>
-      <c r="H58" t="n">
-        <v>564</v>
-      </c>
-      <c r="I58" t="n">
-        <v>28713.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>29893.44</v>
-      </c>
-      <c r="K58" t="n">
-        <v>30293.88</v>
-      </c>
-      <c r="L58" t="n">
-        <v>30694.31</v>
-      </c>
-      <c r="M58" t="n">
-        <v>31484.62</v>
-      </c>
-      <c r="N58" t="n">
-        <v>32274.94</v>
-      </c>
-      <c r="O58" t="n">
-        <v>32285.5</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5307,6 +5307,86 @@
       </c>
       <c r="X57" t="inlineStr"/>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>31346.75</v>
+      </c>
+      <c r="C58" t="n">
+        <v>31385.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>31344.5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>31368.25</v>
+      </c>
+      <c r="F58" t="n">
+        <v>306.5</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="H58" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>29431</v>
+      </c>
+      <c r="J58" t="n">
+        <v>30257.06</v>
+      </c>
+      <c r="K58" t="n">
+        <v>30598.88</v>
+      </c>
+      <c r="L58" t="n">
+        <v>30940.69</v>
+      </c>
+      <c r="M58" t="n">
+        <v>31524.62</v>
+      </c>
+      <c r="N58" t="n">
+        <v>32108.56</v>
+      </c>
+      <c r="O58" t="n">
+        <v>32208.25</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>508.75</v>
       </c>
       <c r="I2" t="n">
-        <v>22148.5</v>
+        <v>22694.5</v>
       </c>
       <c r="J2" t="n">
-        <v>22917.44</v>
+        <v>23122.19</v>
       </c>
       <c r="K2" t="n">
-        <v>23245.62</v>
+        <v>23382.12</v>
       </c>
       <c r="L2" t="n">
-        <v>23573.81</v>
+        <v>23642.06</v>
       </c>
       <c r="M2" t="n">
-        <v>24122.38</v>
+        <v>23985.88</v>
       </c>
       <c r="N2" t="n">
-        <v>24670.94</v>
+        <v>24329.69</v>
       </c>
       <c r="O2" t="n">
-        <v>24778.75</v>
+        <v>24505.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5314,25 +5314,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31346.75</v>
+        <v>31059</v>
       </c>
       <c r="C58" t="n">
-        <v>31385.25</v>
+        <v>31521</v>
       </c>
       <c r="D58" t="n">
-        <v>31344.5</v>
+        <v>30957.5</v>
       </c>
       <c r="E58" t="n">
-        <v>31368.25</v>
+        <v>31487.5</v>
       </c>
       <c r="F58" t="n">
-        <v>306.5</v>
+        <v>425.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0137</v>
       </c>
       <c r="H58" t="n">
-        <v>40.75</v>
+        <v>563.5</v>
       </c>
       <c r="I58" t="n">
         <v>29431</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>508.75</v>
       </c>
       <c r="I2" t="n">
-        <v>22694.5</v>
+        <v>22918</v>
       </c>
       <c r="J2" t="n">
-        <v>23122.19</v>
+        <v>23206</v>
       </c>
       <c r="K2" t="n">
-        <v>23382.12</v>
+        <v>23438</v>
       </c>
       <c r="L2" t="n">
-        <v>23642.06</v>
+        <v>23670</v>
       </c>
       <c r="M2" t="n">
-        <v>23985.88</v>
+        <v>23930</v>
       </c>
       <c r="N2" t="n">
-        <v>24329.69</v>
+        <v>24190</v>
       </c>
       <c r="O2" t="n">
-        <v>24505.75</v>
+        <v>24394</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -5317,22 +5319,22 @@
         <v>31059</v>
       </c>
       <c r="C58" t="n">
-        <v>31521</v>
+        <v>31616.5</v>
       </c>
       <c r="D58" t="n">
         <v>30957.5</v>
       </c>
       <c r="E58" t="n">
-        <v>31487.5</v>
+        <v>31406.75</v>
       </c>
       <c r="F58" t="n">
-        <v>425.75</v>
+        <v>345</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0137</v>
+        <v>0.0111</v>
       </c>
       <c r="H58" t="n">
-        <v>563.5</v>
+        <v>659</v>
       </c>
       <c r="I58" t="n">
         <v>29431</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,13 +5325,13 @@
         <v>30957.5</v>
       </c>
       <c r="E58" t="n">
-        <v>31406.75</v>
+        <v>31416</v>
       </c>
       <c r="F58" t="n">
-        <v>345</v>
+        <v>354.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0111</v>
+        <v>0.0114</v>
       </c>
       <c r="H58" t="n">
         <v>659</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>508.75</v>
       </c>
       <c r="I2" t="n">
-        <v>22918</v>
+        <v>23108</v>
       </c>
       <c r="J2" t="n">
-        <v>23206</v>
+        <v>23277.25</v>
       </c>
       <c r="K2" t="n">
-        <v>23438</v>
+        <v>23485.5</v>
       </c>
       <c r="L2" t="n">
-        <v>23670</v>
+        <v>23693.75</v>
       </c>
       <c r="M2" t="n">
-        <v>23930</v>
+        <v>23882.5</v>
       </c>
       <c r="N2" t="n">
-        <v>24190</v>
+        <v>24071.25</v>
       </c>
       <c r="O2" t="n">
-        <v>24394</v>
+        <v>24299</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5322,19 +5322,19 @@
         <v>31616.5</v>
       </c>
       <c r="D58" t="n">
-        <v>30957.5</v>
+        <v>30953</v>
       </c>
       <c r="E58" t="n">
-        <v>31416</v>
+        <v>31047.5</v>
       </c>
       <c r="F58" t="n">
-        <v>354.25</v>
+        <v>-14.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0114</v>
+        <v>-0.0005</v>
       </c>
       <c r="H58" t="n">
-        <v>659</v>
+        <v>663.5</v>
       </c>
       <c r="I58" t="n">
         <v>29431</v>
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5387,7 +5387,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23673.5</v>
+        <v>24115.25</v>
       </c>
       <c r="C2" t="n">
-        <v>24159</v>
+        <v>24575</v>
       </c>
       <c r="D2" t="n">
-        <v>23650.25</v>
+        <v>24003.75</v>
       </c>
       <c r="E2" t="n">
-        <v>24113.25</v>
+        <v>24568.07</v>
       </c>
       <c r="F2" t="n">
-        <v>429.25</v>
+        <v>454.82</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0181</v>
+        <v>0.0189</v>
       </c>
       <c r="H2" t="n">
-        <v>508.75</v>
+        <v>571.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23108</v>
+        <v>23141.5</v>
       </c>
       <c r="J2" t="n">
-        <v>23277.25</v>
+        <v>23708.81</v>
       </c>
       <c r="K2" t="n">
-        <v>23485.5</v>
+        <v>23858.88</v>
       </c>
       <c r="L2" t="n">
-        <v>23693.75</v>
+        <v>24008.94</v>
       </c>
       <c r="M2" t="n">
-        <v>23882.5</v>
+        <v>24367.62</v>
       </c>
       <c r="N2" t="n">
-        <v>24071.25</v>
+        <v>24726.31</v>
       </c>
       <c r="O2" t="n">
-        <v>24299</v>
+        <v>24667.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,13 +698,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -716,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24115.25</v>
+        <v>24850</v>
       </c>
       <c r="C3" t="n">
-        <v>24575</v>
+        <v>25027.25</v>
       </c>
       <c r="D3" t="n">
-        <v>24003.75</v>
+        <v>24422.5</v>
       </c>
       <c r="E3" t="n">
-        <v>24568.07</v>
+        <v>24726.75</v>
       </c>
       <c r="F3" t="n">
-        <v>454.82</v>
+        <v>158.68</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0065</v>
       </c>
       <c r="H3" t="n">
-        <v>571.25</v>
+        <v>604.75</v>
       </c>
       <c r="I3" t="n">
-        <v>23141.5</v>
+        <v>23432.5</v>
       </c>
       <c r="J3" t="n">
-        <v>23708.81</v>
+        <v>24136.17</v>
       </c>
       <c r="K3" t="n">
-        <v>23858.88</v>
+        <v>24282.45</v>
       </c>
       <c r="L3" t="n">
-        <v>24008.94</v>
+        <v>24428.72</v>
       </c>
       <c r="M3" t="n">
-        <v>24367.62</v>
+        <v>24853.7</v>
       </c>
       <c r="N3" t="n">
-        <v>24726.31</v>
+        <v>25278.67</v>
       </c>
       <c r="O3" t="n">
-        <v>24667.75</v>
+        <v>25146.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -777,16 +777,14 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -798,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24850</v>
+        <v>24726.5</v>
       </c>
       <c r="C4" t="n">
-        <v>25027.25</v>
+        <v>25196.5</v>
       </c>
       <c r="D4" t="n">
-        <v>24422.5</v>
+        <v>24633.25</v>
       </c>
       <c r="E4" t="n">
-        <v>24726.75</v>
+        <v>24992</v>
       </c>
       <c r="F4" t="n">
-        <v>158.68</v>
+        <v>265.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.0107</v>
       </c>
       <c r="H4" t="n">
-        <v>604.75</v>
+        <v>563.25</v>
       </c>
       <c r="I4" t="n">
-        <v>23432.5</v>
+        <v>23817.75</v>
       </c>
       <c r="J4" t="n">
-        <v>24136.17</v>
+        <v>24122.94</v>
       </c>
       <c r="K4" t="n">
-        <v>24282.45</v>
+        <v>24424.38</v>
       </c>
       <c r="L4" t="n">
-        <v>24428.72</v>
+        <v>24725.81</v>
       </c>
       <c r="M4" t="n">
-        <v>24853.7</v>
+        <v>25029.12</v>
       </c>
       <c r="N4" t="n">
-        <v>25278.67</v>
+        <v>25332.44</v>
       </c>
       <c r="O4" t="n">
-        <v>25146.25</v>
+        <v>25632</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -878,68 +876,72 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C5" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D5" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E5" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F5" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H5" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I5" t="n">
-        <v>23817.75</v>
+        <v>24070</v>
       </c>
       <c r="J5" t="n">
-        <v>24122.94</v>
+        <v>24467.31</v>
       </c>
       <c r="K5" t="n">
-        <v>24424.38</v>
+        <v>24710.38</v>
       </c>
       <c r="L5" t="n">
-        <v>24725.81</v>
+        <v>24953.44</v>
       </c>
       <c r="M5" t="n">
-        <v>25029.12</v>
+        <v>25273.62</v>
       </c>
       <c r="N5" t="n">
-        <v>25332.44</v>
+        <v>25593.81</v>
       </c>
       <c r="O5" t="n">
-        <v>25632</v>
+        <v>25759.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -948,84 +950,84 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C6" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D6" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E6" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H6" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I6" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J6" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K6" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L6" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M6" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N6" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O6" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1039,57 +1041,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C7" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D7" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E7" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F7" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H7" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I7" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J7" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K7" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L7" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M7" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N7" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O7" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1123,57 +1125,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C8" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D8" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E8" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F8" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H8" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I8" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J8" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K8" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L8" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M8" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N8" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O8" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1197,8 +1199,10 @@
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
@@ -1214,155 +1218,147 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C9" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D9" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E9" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F9" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H9" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I9" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J9" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K9" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L9" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M9" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N9" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O9" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+        <v>27098</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C10" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D10" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E10" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F10" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H10" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I10" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J10" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K10" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L10" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M10" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N10" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O10" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>27822.75</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1384,50 +1380,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C11" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D11" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E11" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H11" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I11" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J11" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K11" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L11" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M11" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N11" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O11" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,12 +1431,14 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1462,50 +1460,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C12" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D12" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E12" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F12" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H12" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I12" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J12" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K12" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L12" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M12" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N12" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O12" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1513,22 +1511,24 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1537,55 +1537,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C13" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D13" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E13" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F13" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H13" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I13" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J13" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K13" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L13" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M13" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N13" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O13" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,13 +1607,11 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1628,70 +1630,72 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C14" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D14" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E14" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F14" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H14" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I14" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J14" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K14" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L14" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M14" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N14" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O14" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1705,65 +1709,63 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C15" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D15" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E15" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F15" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H15" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I15" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J15" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K15" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L15" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M15" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N15" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O15" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q15" s="6" t="n">
+        <v/>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1772,7 +1774,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1789,59 +1791,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C16" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D16" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E16" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H16" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I16" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J16" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K16" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L16" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M16" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N16" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O16" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,21 +1847,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1873,79 +1873,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C17" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D17" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E17" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F17" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H17" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I17" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J17" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K17" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L17" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M17" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N17" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O17" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+        <v>26262.25</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1955,92 +1961,86 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C18" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D18" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E18" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H18" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I18" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J18" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K18" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L18" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M18" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N18" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O18" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2048,75 +2048,75 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C19" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D19" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E19" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F19" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I19" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J19" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K19" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L19" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M19" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N19" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O19" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2125,55 +2125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C20" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D20" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E20" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H20" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I20" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J20" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K20" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L20" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M20" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N20" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O20" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2185,12 +2189,12 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2209,79 +2213,77 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C21" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D21" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E21" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F21" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H21" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I21" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J21" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K21" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L21" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M21" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N21" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O21" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2295,77 +2297,81 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C22" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D22" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E22" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H22" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I22" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J22" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K22" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L22" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M22" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N22" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O22" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+        <v>27332.75</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2379,76 +2385,70 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C23" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D23" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E23" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H23" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I23" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J23" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K23" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L23" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M23" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N23" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O23" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27815.75</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2467,57 +2467,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C24" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D24" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E24" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F24" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H24" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I24" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J24" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K24" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L24" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M24" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N24" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O24" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2528,9 +2528,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2556,50 +2556,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C25" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D25" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E25" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F25" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H25" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I25" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J25" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K25" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L25" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M25" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N25" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O25" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,16 +2607,20 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2631,57 +2635,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C26" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D26" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E26" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H26" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I26" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J26" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K26" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L26" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M26" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N26" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O26" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,18 +2695,16 @@
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2717,57 +2719,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C27" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D27" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E27" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H27" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J27" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K27" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L27" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M27" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N27" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O27" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2785,8 +2787,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2808,50 +2812,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C28" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D28" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E28" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F28" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H28" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I28" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J28" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K28" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L28" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M28" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N28" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O28" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,20 +2863,16 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2887,74 +2887,80 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C29" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D29" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E29" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H29" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I29" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J29" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K29" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L29" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M29" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N29" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O29" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2969,81 +2975,77 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C30" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D30" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E30" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H30" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I30" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J30" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K30" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L30" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M30" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N30" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O30" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3057,57 +3059,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C31" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D31" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E31" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F31" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H31" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I31" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J31" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K31" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L31" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M31" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N31" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O31" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,73 +3127,71 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C32" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D32" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E32" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H32" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I32" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J32" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K32" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L32" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M32" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N32" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O32" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3230,50 +3230,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C33" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D33" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E33" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F33" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H33" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I33" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J33" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K33" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L33" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M33" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N33" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O33" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,16 +3291,14 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3312,50 +3310,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C34" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D34" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E34" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F34" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H34" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I34" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J34" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K34" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L34" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M34" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N34" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O34" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3392,50 +3390,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C35" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D35" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E35" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F35" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H35" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I35" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J35" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K35" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L35" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M35" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N35" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O35" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3453,14 +3451,18 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3472,50 +3474,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C36" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D36" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E36" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F36" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H36" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I36" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J36" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K36" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L36" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M36" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N36" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O36" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3528,78 +3530,76 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C37" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D37" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E37" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H37" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I37" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J37" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K37" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L37" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M37" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N37" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O37" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,16 +3607,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3631,57 +3635,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C38" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D38" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E38" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F38" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H38" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I38" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J38" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K38" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L38" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M38" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N38" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O38" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3689,10 +3693,8 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
@@ -3715,158 +3717,156 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C39" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D39" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E39" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F39" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H39" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I39" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J39" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K39" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L39" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M39" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N39" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O39" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>31395.75</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C40" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D40" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E40" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F40" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H40" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I40" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J40" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K40" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L40" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M40" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N40" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O40" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>32834.25</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3892,50 +3892,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C41" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D41" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E41" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F41" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H41" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I41" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J41" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K41" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L41" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M41" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N41" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O41" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,11 +3948,13 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3967,77 +3969,79 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C42" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D42" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E42" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F42" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H42" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I42" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J42" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K42" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L42" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M42" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N42" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O42" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4051,79 +4055,77 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C43" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D43" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F43" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H43" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I43" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J43" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K43" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L43" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M43" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N43" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O43" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4137,57 +4139,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C44" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D44" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E44" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F44" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H44" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I44" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J44" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K44" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L44" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M44" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N44" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O44" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4195,18 +4197,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4221,72 +4223,74 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C45" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D45" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E45" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F45" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H45" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I45" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J45" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K45" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L45" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M45" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N45" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O45" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4303,71 +4307,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C46" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D46" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E46" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F46" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H46" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I46" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J46" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K46" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L46" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M46" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N46" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O46" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
@@ -4394,50 +4392,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C47" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D47" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E47" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H47" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I47" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J47" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K47" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L47" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M47" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N47" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O47" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,12 +4445,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4469,55 +4467,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C48" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D48" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E48" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F48" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H48" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I48" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J48" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K48" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L48" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M48" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N48" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O48" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4525,21 +4527,23 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4551,57 +4555,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C49" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D49" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E49" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F49" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H49" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I49" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J49" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K49" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L49" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M49" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N49" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O49" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4619,13 +4623,11 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4644,70 +4646,72 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C50" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D50" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E50" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F50" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H50" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I50" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J50" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K50" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L50" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M50" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N50" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O50" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4721,74 +4725,70 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C51" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D51" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E51" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F51" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H51" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I51" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J51" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K51" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L51" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M51" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N51" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O51" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4814,50 +4814,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C52" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D52" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E52" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F52" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H52" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I52" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J52" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K52" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L52" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M52" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N52" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O52" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4865,12 +4865,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4896,50 +4898,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C53" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D53" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E53" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F53" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H53" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I53" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J53" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K53" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L53" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M53" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N53" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O53" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4952,9 +4954,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4973,57 +4975,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C54" t="n">
-        <v>29764.75</v>
+        <v>29665.25</v>
       </c>
       <c r="D54" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E54" t="n">
-        <v>29387</v>
+        <v>29613.68</v>
       </c>
       <c r="F54" t="n">
-        <v>-178.25</v>
+        <v>226.68</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0077</v>
       </c>
       <c r="H54" t="n">
-        <v>724.25</v>
+        <v>901.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J54" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K54" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L54" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M54" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N54" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O54" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5036,13 +5038,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5057,57 +5061,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28997.75</v>
+        <v>29938</v>
       </c>
       <c r="C55" t="n">
-        <v>29665.25</v>
+        <v>31094.75</v>
       </c>
       <c r="D55" t="n">
-        <v>28763.75</v>
+        <v>29904</v>
       </c>
       <c r="E55" t="n">
-        <v>29613.68</v>
+        <v>30889.25</v>
       </c>
       <c r="F55" t="n">
-        <v>226.68</v>
+        <v>1275.57</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0431</v>
       </c>
       <c r="H55" t="n">
-        <v>901.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I55" t="n">
-        <v>28316.25</v>
+        <v>27862.25</v>
       </c>
       <c r="J55" t="n">
-        <v>28654.94</v>
+        <v>28911.77</v>
       </c>
       <c r="K55" t="n">
-        <v>29024.88</v>
+        <v>29162.93</v>
       </c>
       <c r="L55" t="n">
-        <v>29394.81</v>
+        <v>29414.09</v>
       </c>
       <c r="M55" t="n">
-        <v>29749.12</v>
+        <v>30064.43</v>
       </c>
       <c r="N55" t="n">
-        <v>30103.44</v>
+        <v>30714.77</v>
       </c>
       <c r="O55" t="n">
-        <v>30489</v>
+        <v>30566.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5115,85 +5119,83 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29938</v>
+        <v>30870</v>
       </c>
       <c r="C56" t="n">
-        <v>31094.75</v>
+        <v>31282.5</v>
       </c>
       <c r="D56" t="n">
-        <v>29904</v>
+        <v>30356.75</v>
       </c>
       <c r="E56" t="n">
-        <v>30889.25</v>
+        <v>31061.75</v>
       </c>
       <c r="F56" t="n">
-        <v>1275.57</v>
+        <v>172.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0056</v>
       </c>
       <c r="H56" t="n">
-        <v>1190.75</v>
+        <v>925.75</v>
       </c>
       <c r="I56" t="n">
-        <v>27862.25</v>
+        <v>28713.25</v>
       </c>
       <c r="J56" t="n">
-        <v>28911.77</v>
+        <v>29893.44</v>
       </c>
       <c r="K56" t="n">
-        <v>29162.93</v>
+        <v>30293.88</v>
       </c>
       <c r="L56" t="n">
-        <v>29414.09</v>
+        <v>30694.31</v>
       </c>
       <c r="M56" t="n">
-        <v>30064.43</v>
+        <v>31484.62</v>
       </c>
       <c r="N56" t="n">
-        <v>30714.77</v>
+        <v>32274.94</v>
       </c>
       <c r="O56" t="n">
-        <v>30566.75</v>
+        <v>32285.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5206,23 +5208,17 @@
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5234,50 +5230,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>30870</v>
+        <v>31059</v>
       </c>
       <c r="C57" t="n">
-        <v>31282.5</v>
+        <v>31616.5</v>
       </c>
       <c r="D57" t="n">
-        <v>30356.75</v>
+        <v>30792</v>
       </c>
       <c r="E57" t="n">
-        <v>31061.75</v>
+        <v>31108.75</v>
       </c>
       <c r="F57" t="n">
-        <v>172.5</v>
+        <v>47</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0056</v>
+        <v>0.0015</v>
       </c>
       <c r="H57" t="n">
-        <v>925.75</v>
+        <v>824.5</v>
       </c>
       <c r="I57" t="n">
-        <v>28713.25</v>
+        <v>29431</v>
       </c>
       <c r="J57" t="n">
-        <v>29893.44</v>
+        <v>30257.06</v>
       </c>
       <c r="K57" t="n">
-        <v>30293.88</v>
+        <v>30598.88</v>
       </c>
       <c r="L57" t="n">
-        <v>30694.31</v>
+        <v>30940.69</v>
       </c>
       <c r="M57" t="n">
-        <v>31484.62</v>
+        <v>31524.62</v>
       </c>
       <c r="N57" t="n">
-        <v>32274.94</v>
+        <v>32108.56</v>
       </c>
       <c r="O57" t="n">
-        <v>32285.5</v>
+        <v>32208.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,8 +5289,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5308,90 +5306,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>31059</v>
-      </c>
-      <c r="C58" t="n">
-        <v>31616.5</v>
-      </c>
-      <c r="D58" t="n">
-        <v>30953</v>
-      </c>
-      <c r="E58" t="n">
-        <v>31047.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-14.25</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0005</v>
-      </c>
-      <c r="H58" t="n">
-        <v>663.5</v>
-      </c>
-      <c r="I58" t="n">
-        <v>29431</v>
-      </c>
-      <c r="J58" t="n">
-        <v>30257.06</v>
-      </c>
-      <c r="K58" t="n">
-        <v>30598.88</v>
-      </c>
-      <c r="L58" t="n">
-        <v>30940.69</v>
-      </c>
-      <c r="M58" t="n">
-        <v>31524.62</v>
-      </c>
-      <c r="N58" t="n">
-        <v>32108.56</v>
-      </c>
-      <c r="O58" t="n">
-        <v>32208.25</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5243,13 +5243,13 @@
         <v>30792</v>
       </c>
       <c r="E57" t="n">
-        <v>31108.75</v>
+        <v>31205.25</v>
       </c>
       <c r="F57" t="n">
-        <v>47</v>
+        <v>143.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0046</v>
       </c>
       <c r="H57" t="n">
         <v>824.5</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5243,13 +5243,13 @@
         <v>30792</v>
       </c>
       <c r="E57" t="n">
-        <v>31205.25</v>
+        <v>31171.25</v>
       </c>
       <c r="F57" t="n">
-        <v>143.5</v>
+        <v>109.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0035</v>
       </c>
       <c r="H57" t="n">
         <v>824.5</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +659,25 @@
         <v>571.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23141.5</v>
+        <v>23293</v>
       </c>
       <c r="J2" t="n">
-        <v>23708.81</v>
+        <v>23765.62</v>
       </c>
       <c r="K2" t="n">
-        <v>23858.88</v>
+        <v>23896.75</v>
       </c>
       <c r="L2" t="n">
-        <v>24008.94</v>
+        <v>24027.88</v>
       </c>
       <c r="M2" t="n">
-        <v>24367.62</v>
+        <v>24329.75</v>
       </c>
       <c r="N2" t="n">
-        <v>24726.31</v>
+        <v>24631.62</v>
       </c>
       <c r="O2" t="n">
-        <v>24667.75</v>
+        <v>24592</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5243,13 +5243,13 @@
         <v>30792</v>
       </c>
       <c r="E57" t="n">
-        <v>31171.25</v>
+        <v>31108.75</v>
       </c>
       <c r="F57" t="n">
-        <v>109.5</v>
+        <v>47</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0015</v>
       </c>
       <c r="H57" t="n">
         <v>824.5</v>
@@ -5306,6 +5306,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>31145.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>31289.25</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30844.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v>30898.25</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-210.5</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="H58" t="n">
+        <v>445</v>
+      </c>
+      <c r="I58" t="n">
+        <v>29967.5</v>
+      </c>
+      <c r="J58" t="n">
+        <v>30236.5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>30696.5</v>
+      </c>
+      <c r="L58" t="n">
+        <v>31156.5</v>
+      </c>
+      <c r="M58" t="n">
+        <v>31521</v>
+      </c>
+      <c r="N58" t="n">
+        <v>31885.5</v>
+      </c>
+      <c r="O58" t="n">
+        <v>32441</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>571.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23293</v>
+        <v>23411</v>
       </c>
       <c r="J2" t="n">
-        <v>23765.62</v>
+        <v>23809.88</v>
       </c>
       <c r="K2" t="n">
-        <v>23896.75</v>
+        <v>23926.25</v>
       </c>
       <c r="L2" t="n">
-        <v>24027.88</v>
+        <v>24042.62</v>
       </c>
       <c r="M2" t="n">
-        <v>24329.75</v>
+        <v>24300.25</v>
       </c>
       <c r="N2" t="n">
-        <v>24631.62</v>
+        <v>24557.88</v>
       </c>
       <c r="O2" t="n">
-        <v>24592</v>
+        <v>24533</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,12 +698,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5320,19 +5322,19 @@
         <v>31289.25</v>
       </c>
       <c r="D58" t="n">
-        <v>30844.25</v>
+        <v>30744.5</v>
       </c>
       <c r="E58" t="n">
-        <v>30898.25</v>
+        <v>30827.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-210.5</v>
+        <v>-281</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0068</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>445</v>
+        <v>544.75</v>
       </c>
       <c r="I58" t="n">
         <v>29967.5</v>
@@ -5387,7 +5389,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>571.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23411</v>
+        <v>23517</v>
       </c>
       <c r="J2" t="n">
-        <v>23809.88</v>
+        <v>23849.62</v>
       </c>
       <c r="K2" t="n">
-        <v>23926.25</v>
+        <v>23952.75</v>
       </c>
       <c r="L2" t="n">
-        <v>24042.62</v>
+        <v>24055.88</v>
       </c>
       <c r="M2" t="n">
-        <v>24300.25</v>
+        <v>24273.75</v>
       </c>
       <c r="N2" t="n">
-        <v>24557.88</v>
+        <v>24491.62</v>
       </c>
       <c r="O2" t="n">
-        <v>24533</v>
+        <v>24480</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5322,19 +5322,19 @@
         <v>31289.25</v>
       </c>
       <c r="D58" t="n">
-        <v>30744.5</v>
+        <v>29880</v>
       </c>
       <c r="E58" t="n">
-        <v>30827.75</v>
+        <v>29953.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-281</v>
+        <v>-1155.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.0371</v>
       </c>
       <c r="H58" t="n">
-        <v>544.75</v>
+        <v>1409.25</v>
       </c>
       <c r="I58" t="n">
         <v>29967.5</v>
@@ -5357,15 +5357,19 @@
       <c r="O58" t="n">
         <v>32441</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5382,16 +5386,12 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,13 +5325,13 @@
         <v>29880</v>
       </c>
       <c r="E58" t="n">
-        <v>29953.25</v>
+        <v>29942</v>
       </c>
       <c r="F58" t="n">
-        <v>-1155.5</v>
+        <v>-1166.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0371</v>
+        <v>-0.0375</v>
       </c>
       <c r="H58" t="n">
         <v>1409.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,13 +5325,13 @@
         <v>29880</v>
       </c>
       <c r="E58" t="n">
-        <v>29942</v>
+        <v>29948.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-1166.75</v>
+        <v>-1160.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0375</v>
+        <v>-0.0373</v>
       </c>
       <c r="H58" t="n">
         <v>1409.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>571.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23517</v>
+        <v>23779</v>
       </c>
       <c r="J2" t="n">
-        <v>23849.62</v>
+        <v>23947.88</v>
       </c>
       <c r="K2" t="n">
-        <v>23952.75</v>
+        <v>24018.25</v>
       </c>
       <c r="L2" t="n">
-        <v>24055.88</v>
+        <v>24088.62</v>
       </c>
       <c r="M2" t="n">
-        <v>24273.75</v>
+        <v>24208.25</v>
       </c>
       <c r="N2" t="n">
-        <v>24491.62</v>
+        <v>24327.88</v>
       </c>
       <c r="O2" t="n">
-        <v>24480</v>
+        <v>24349</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -700,12 +702,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5322,19 +5324,19 @@
         <v>31289.25</v>
       </c>
       <c r="D58" t="n">
-        <v>29880</v>
+        <v>29959.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29948.25</v>
+        <v>30060.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-1160.5</v>
+        <v>-1048.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0373</v>
+        <v>-0.0337</v>
       </c>
       <c r="H58" t="n">
-        <v>1409.25</v>
+        <v>1330</v>
       </c>
       <c r="I58" t="n">
         <v>29967.5</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24115.25</v>
+        <v>24850</v>
       </c>
       <c r="C2" t="n">
-        <v>24575</v>
+        <v>25027.25</v>
       </c>
       <c r="D2" t="n">
-        <v>24003.75</v>
+        <v>24422.5</v>
       </c>
       <c r="E2" t="n">
-        <v>24568.07</v>
+        <v>24726.75</v>
       </c>
       <c r="F2" t="n">
-        <v>454.82</v>
+        <v>158.68</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0189</v>
+        <v>0.0065</v>
       </c>
       <c r="H2" t="n">
-        <v>571.25</v>
+        <v>604.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23779</v>
+        <v>23432.5</v>
       </c>
       <c r="J2" t="n">
-        <v>23947.88</v>
+        <v>24136.17</v>
       </c>
       <c r="K2" t="n">
-        <v>24018.25</v>
+        <v>24282.45</v>
       </c>
       <c r="L2" t="n">
-        <v>24088.62</v>
+        <v>24428.72</v>
       </c>
       <c r="M2" t="n">
-        <v>24208.25</v>
+        <v>24853.7</v>
       </c>
       <c r="N2" t="n">
-        <v>24327.88</v>
+        <v>25278.67</v>
       </c>
       <c r="O2" t="n">
-        <v>24349</v>
+        <v>25146.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -697,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -720,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24850</v>
+        <v>24726.5</v>
       </c>
       <c r="C3" t="n">
-        <v>25027.25</v>
+        <v>25196.5</v>
       </c>
       <c r="D3" t="n">
-        <v>24422.5</v>
+        <v>24633.25</v>
       </c>
       <c r="E3" t="n">
-        <v>24726.75</v>
+        <v>24992</v>
       </c>
       <c r="F3" t="n">
-        <v>158.68</v>
+        <v>265.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.0107</v>
       </c>
       <c r="H3" t="n">
-        <v>604.75</v>
+        <v>563.25</v>
       </c>
       <c r="I3" t="n">
-        <v>23432.5</v>
+        <v>23817.75</v>
       </c>
       <c r="J3" t="n">
-        <v>24136.17</v>
+        <v>24122.94</v>
       </c>
       <c r="K3" t="n">
-        <v>24282.45</v>
+        <v>24424.38</v>
       </c>
       <c r="L3" t="n">
-        <v>24428.72</v>
+        <v>24725.81</v>
       </c>
       <c r="M3" t="n">
-        <v>24853.7</v>
+        <v>25029.12</v>
       </c>
       <c r="N3" t="n">
-        <v>25278.67</v>
+        <v>25332.44</v>
       </c>
       <c r="O3" t="n">
-        <v>25146.25</v>
+        <v>25632</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -800,68 +794,72 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C4" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D4" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E4" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F4" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H4" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I4" t="n">
-        <v>23817.75</v>
+        <v>24070</v>
       </c>
       <c r="J4" t="n">
-        <v>24122.94</v>
+        <v>24467.31</v>
       </c>
       <c r="K4" t="n">
-        <v>24424.38</v>
+        <v>24710.38</v>
       </c>
       <c r="L4" t="n">
-        <v>24725.81</v>
+        <v>24953.44</v>
       </c>
       <c r="M4" t="n">
-        <v>25029.12</v>
+        <v>25273.62</v>
       </c>
       <c r="N4" t="n">
-        <v>25332.44</v>
+        <v>25593.81</v>
       </c>
       <c r="O4" t="n">
-        <v>25632</v>
+        <v>25759.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -870,84 +868,84 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C5" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D5" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E5" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H5" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I5" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J5" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K5" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L5" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M5" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N5" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O5" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C6" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D6" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E6" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F6" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H6" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I6" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J6" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K6" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L6" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M6" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N6" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O6" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1045,57 +1043,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C7" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D7" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E7" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F7" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H7" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I7" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J7" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K7" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L7" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M7" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N7" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O7" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1119,8 +1117,10 @@
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
@@ -1136,155 +1136,147 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C8" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D8" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E8" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F8" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H8" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I8" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J8" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K8" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L8" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M8" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N8" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O8" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>27098</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C9" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D9" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E9" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F9" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H9" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I9" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J9" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K9" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L9" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M9" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N9" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O9" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>27822.75</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1306,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C10" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D10" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E10" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H10" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I10" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J10" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K10" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L10" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M10" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N10" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O10" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,12 +1349,14 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1384,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C11" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D11" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E11" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F11" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H11" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I11" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J11" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K11" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L11" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M11" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N11" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O11" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,22 +1429,24 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1459,55 +1455,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C12" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D12" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E12" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F12" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H12" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I12" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J12" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K12" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L12" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M12" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N12" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O12" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,13 +1525,11 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1550,70 +1548,72 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C13" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D13" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E13" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F13" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H13" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I13" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J13" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K13" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L13" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M13" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N13" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O13" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1627,65 +1627,63 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C14" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D14" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E14" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F14" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H14" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I14" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J14" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K14" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L14" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M14" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N14" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O14" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
@@ -1694,7 +1692,7 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1711,59 +1709,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C15" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D15" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E15" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H15" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I15" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J15" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K15" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L15" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M15" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N15" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O15" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,21 +1765,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1795,79 +1791,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C16" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D16" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E16" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F16" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H16" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I16" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J16" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K16" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L16" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M16" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N16" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O16" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>26262.25</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1877,92 +1879,86 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C17" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D17" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E17" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H17" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I17" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J17" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K17" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L17" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M17" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N17" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O17" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1970,75 +1966,75 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C18" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D18" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E18" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F18" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I18" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J18" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K18" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L18" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M18" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N18" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O18" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2047,55 +2043,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C19" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D19" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E19" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H19" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I19" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J19" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K19" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L19" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M19" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N19" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O19" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2131,79 +2131,77 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C20" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D20" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E20" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F20" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H20" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I20" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J20" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K20" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L20" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M20" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N20" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O20" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2217,77 +2215,81 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C21" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D21" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E21" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H21" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I21" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J21" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K21" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L21" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M21" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N21" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O21" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+        <v>27332.75</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2301,76 +2303,70 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C22" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D22" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E22" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H22" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I22" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J22" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K22" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L22" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M22" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N22" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O22" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27815.75</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2389,57 +2385,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C23" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D23" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E23" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H23" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I23" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J23" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K23" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L23" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M23" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N23" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O23" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2450,9 +2446,9 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2478,50 +2474,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C24" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D24" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E24" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F24" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H24" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I24" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J24" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K24" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L24" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M24" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N24" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O24" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2529,16 +2525,20 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2553,57 +2553,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C25" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D25" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E25" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H25" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I25" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J25" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K25" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L25" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M25" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N25" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O25" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2613,18 +2613,16 @@
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2639,57 +2637,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C26" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D26" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E26" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H26" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I26" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J26" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K26" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L26" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M26" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N26" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O26" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2707,8 +2705,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2730,50 +2730,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C27" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D27" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E27" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F27" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H27" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I27" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J27" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K27" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L27" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M27" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N27" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O27" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2781,20 +2781,16 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2809,74 +2805,80 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C28" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D28" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F28" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H28" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I28" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J28" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K28" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L28" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M28" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N28" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O28" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2891,81 +2893,77 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C29" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D29" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E29" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H29" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I29" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J29" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K29" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L29" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M29" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N29" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O29" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2979,57 +2977,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C30" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D30" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E30" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F30" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H30" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I30" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J30" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K30" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L30" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M30" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N30" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O30" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3047,73 +3045,71 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C31" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D31" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E31" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H31" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I31" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J31" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K31" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L31" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M31" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N31" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O31" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3152,50 +3148,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C32" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D32" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E32" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F32" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H32" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I32" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J32" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K32" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L32" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M32" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N32" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O32" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3213,16 +3209,14 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3234,50 +3228,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C33" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D33" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E33" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F33" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H33" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I33" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J33" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K33" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L33" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M33" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N33" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O33" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3314,50 +3308,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C34" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D34" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E34" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F34" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H34" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I34" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J34" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K34" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L34" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M34" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N34" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O34" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3375,14 +3369,18 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3394,50 +3392,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C35" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D35" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E35" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F35" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H35" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I35" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J35" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K35" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L35" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M35" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N35" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O35" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,78 +3448,76 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C36" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D36" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E36" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H36" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I36" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J36" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K36" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L36" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M36" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N36" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O36" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,16 +3525,20 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3553,57 +3553,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C37" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D37" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E37" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F37" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H37" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I37" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J37" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K37" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L37" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M37" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N37" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O37" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3611,10 +3611,8 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
@@ -3637,158 +3635,156 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C38" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D38" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E38" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F38" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H38" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I38" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J38" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K38" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L38" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M38" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N38" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O38" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+        <v>31395.75</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C39" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D39" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E39" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F39" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H39" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I39" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J39" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K39" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L39" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M39" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N39" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O39" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>32834.25</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3814,50 +3810,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C40" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D40" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E40" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F40" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H40" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I40" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J40" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K40" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L40" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M40" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N40" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O40" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,11 +3866,13 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3889,77 +3887,79 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C41" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D41" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E41" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F41" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H41" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I41" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J41" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K41" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L41" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M41" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N41" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O41" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3973,79 +3973,77 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C42" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D42" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F42" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H42" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I42" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J42" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K42" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L42" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M42" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N42" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O42" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4059,57 +4057,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C43" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D43" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F43" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H43" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I43" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J43" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K43" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L43" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M43" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N43" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O43" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4117,18 +4115,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4143,72 +4141,74 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C44" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D44" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E44" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F44" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H44" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I44" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J44" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K44" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L44" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M44" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N44" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O44" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4225,71 +4225,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C45" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D45" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E45" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F45" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H45" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I45" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J45" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K45" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L45" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M45" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N45" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O45" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
@@ -4316,50 +4310,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C46" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D46" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E46" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F46" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H46" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I46" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J46" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K46" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L46" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M46" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N46" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O46" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4369,12 +4363,12 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4391,55 +4385,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C47" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D47" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E47" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F47" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H47" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I47" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J47" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K47" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L47" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M47" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N47" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O47" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,21 +4445,23 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4473,57 +4473,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C48" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D48" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E48" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F48" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H48" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J48" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K48" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L48" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M48" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N48" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O48" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,13 +4541,11 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4566,70 +4564,72 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C49" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D49" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E49" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F49" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H49" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I49" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J49" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K49" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L49" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M49" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N49" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O49" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4643,74 +4643,70 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C50" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D50" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E50" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F50" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H50" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I50" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J50" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K50" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L50" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M50" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N50" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O50" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4736,50 +4732,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C51" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D51" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E51" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F51" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H51" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I51" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J51" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K51" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L51" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M51" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N51" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O51" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4787,12 +4783,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4818,50 +4816,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C52" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D52" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E52" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F52" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H52" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I52" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J52" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K52" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L52" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M52" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N52" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O52" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4874,9 +4872,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4895,57 +4893,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C53" t="n">
-        <v>29764.75</v>
+        <v>29665.25</v>
       </c>
       <c r="D53" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E53" t="n">
-        <v>29387</v>
+        <v>29613.68</v>
       </c>
       <c r="F53" t="n">
-        <v>-178.25</v>
+        <v>226.68</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0077</v>
       </c>
       <c r="H53" t="n">
-        <v>724.25</v>
+        <v>901.5</v>
       </c>
       <c r="I53" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J53" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K53" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L53" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M53" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N53" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O53" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4958,13 +4956,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4979,57 +4979,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28997.75</v>
+        <v>29938</v>
       </c>
       <c r="C54" t="n">
-        <v>29665.25</v>
+        <v>31094.75</v>
       </c>
       <c r="D54" t="n">
-        <v>28763.75</v>
+        <v>29904</v>
       </c>
       <c r="E54" t="n">
-        <v>29613.68</v>
+        <v>30889.25</v>
       </c>
       <c r="F54" t="n">
-        <v>226.68</v>
+        <v>1275.57</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0431</v>
       </c>
       <c r="H54" t="n">
-        <v>901.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I54" t="n">
-        <v>28316.25</v>
+        <v>27862.25</v>
       </c>
       <c r="J54" t="n">
-        <v>28654.94</v>
+        <v>28911.77</v>
       </c>
       <c r="K54" t="n">
-        <v>29024.88</v>
+        <v>29162.93</v>
       </c>
       <c r="L54" t="n">
-        <v>29394.81</v>
+        <v>29414.09</v>
       </c>
       <c r="M54" t="n">
-        <v>29749.12</v>
+        <v>30064.43</v>
       </c>
       <c r="N54" t="n">
-        <v>30103.44</v>
+        <v>30714.77</v>
       </c>
       <c r="O54" t="n">
-        <v>30489</v>
+        <v>30566.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5037,85 +5037,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29938</v>
+        <v>30870</v>
       </c>
       <c r="C55" t="n">
-        <v>31094.75</v>
+        <v>31282.5</v>
       </c>
       <c r="D55" t="n">
-        <v>29904</v>
+        <v>30356.75</v>
       </c>
       <c r="E55" t="n">
-        <v>30889.25</v>
+        <v>31061.75</v>
       </c>
       <c r="F55" t="n">
-        <v>1275.57</v>
+        <v>172.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0056</v>
       </c>
       <c r="H55" t="n">
-        <v>1190.75</v>
+        <v>925.75</v>
       </c>
       <c r="I55" t="n">
-        <v>27862.25</v>
+        <v>28713.25</v>
       </c>
       <c r="J55" t="n">
-        <v>28911.77</v>
+        <v>29893.44</v>
       </c>
       <c r="K55" t="n">
-        <v>29162.93</v>
+        <v>30293.88</v>
       </c>
       <c r="L55" t="n">
-        <v>29414.09</v>
+        <v>30694.31</v>
       </c>
       <c r="M55" t="n">
-        <v>30064.43</v>
+        <v>31484.62</v>
       </c>
       <c r="N55" t="n">
-        <v>30714.77</v>
+        <v>32274.94</v>
       </c>
       <c r="O55" t="n">
-        <v>30566.75</v>
+        <v>32285.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5128,23 +5126,17 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5156,50 +5148,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>30870</v>
+        <v>31059</v>
       </c>
       <c r="C56" t="n">
-        <v>31282.5</v>
+        <v>31616.5</v>
       </c>
       <c r="D56" t="n">
-        <v>30356.75</v>
+        <v>30792</v>
       </c>
       <c r="E56" t="n">
-        <v>31061.75</v>
+        <v>31108.75</v>
       </c>
       <c r="F56" t="n">
-        <v>172.5</v>
+        <v>47</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0056</v>
+        <v>0.0015</v>
       </c>
       <c r="H56" t="n">
-        <v>925.75</v>
+        <v>824.5</v>
       </c>
       <c r="I56" t="n">
-        <v>28713.25</v>
+        <v>29431</v>
       </c>
       <c r="J56" t="n">
-        <v>29893.44</v>
+        <v>30257.06</v>
       </c>
       <c r="K56" t="n">
-        <v>30293.88</v>
+        <v>30598.88</v>
       </c>
       <c r="L56" t="n">
-        <v>30694.31</v>
+        <v>30940.69</v>
       </c>
       <c r="M56" t="n">
-        <v>31484.62</v>
+        <v>31524.62</v>
       </c>
       <c r="N56" t="n">
-        <v>32274.94</v>
+        <v>32108.56</v>
       </c>
       <c r="O56" t="n">
-        <v>32285.5</v>
+        <v>32208.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5215,8 +5207,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5234,166 +5228,86 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31059</v>
+        <v>31145.5</v>
       </c>
       <c r="C57" t="n">
-        <v>31616.5</v>
+        <v>31289.25</v>
       </c>
       <c r="D57" t="n">
-        <v>30792</v>
+        <v>29268.75</v>
       </c>
       <c r="E57" t="n">
-        <v>31108.75</v>
+        <v>29391.25</v>
       </c>
       <c r="F57" t="n">
-        <v>47</v>
+        <v>-1717.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0552</v>
       </c>
       <c r="H57" t="n">
-        <v>824.5</v>
+        <v>2020.5</v>
       </c>
       <c r="I57" t="n">
-        <v>29431</v>
+        <v>29967.5</v>
       </c>
       <c r="J57" t="n">
-        <v>30257.06</v>
+        <v>30236.5</v>
       </c>
       <c r="K57" t="n">
-        <v>30598.88</v>
+        <v>30696.5</v>
       </c>
       <c r="L57" t="n">
-        <v>30940.69</v>
+        <v>31156.5</v>
       </c>
       <c r="M57" t="n">
-        <v>31524.62</v>
+        <v>31521</v>
       </c>
       <c r="N57" t="n">
-        <v>32108.56</v>
+        <v>31885.5</v>
       </c>
       <c r="O57" t="n">
-        <v>32208.25</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+        <v>32441</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>31145.5</v>
-      </c>
-      <c r="C58" t="n">
-        <v>31289.25</v>
-      </c>
-      <c r="D58" t="n">
-        <v>29959.25</v>
-      </c>
-      <c r="E58" t="n">
-        <v>30060.25</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-1048.5</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0337</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1330</v>
-      </c>
-      <c r="I58" t="n">
-        <v>29967.5</v>
-      </c>
-      <c r="J58" t="n">
-        <v>30236.5</v>
-      </c>
-      <c r="K58" t="n">
-        <v>30696.5</v>
-      </c>
-      <c r="L58" t="n">
-        <v>31156.5</v>
-      </c>
-      <c r="M58" t="n">
-        <v>31521</v>
-      </c>
-      <c r="N58" t="n">
-        <v>31885.5</v>
-      </c>
-      <c r="O58" t="n">
-        <v>32441</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5241,10 +5241,10 @@
         <v>29268.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29391.25</v>
+        <v>29391.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-1717.5</v>
+        <v>-1717.25</v>
       </c>
       <c r="G57" s="5" t="n">
         <v>-0.0552</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5238,19 +5238,19 @@
         <v>31289.25</v>
       </c>
       <c r="D57" t="n">
-        <v>29268.75</v>
+        <v>29227</v>
       </c>
       <c r="E57" t="n">
-        <v>29391.5</v>
+        <v>29593.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-1717.25</v>
+        <v>-1515.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0552</v>
+        <v>-0.0487</v>
       </c>
       <c r="H57" t="n">
-        <v>2020.5</v>
+        <v>2062.25</v>
       </c>
       <c r="I57" t="n">
         <v>29967.5</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5241,13 +5241,13 @@
         <v>29227</v>
       </c>
       <c r="E57" t="n">
-        <v>29593.5</v>
+        <v>29652.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-1515.25</v>
+        <v>-1456.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0487</v>
+        <v>-0.0468</v>
       </c>
       <c r="H57" t="n">
         <v>2062.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5238,19 +5241,19 @@
         <v>31289.25</v>
       </c>
       <c r="D57" t="n">
-        <v>29227</v>
+        <v>29268.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29652.5</v>
+        <v>29391.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-1456.25</v>
+        <v>-1717.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0468</v>
+        <v>-0.0552</v>
       </c>
       <c r="H57" t="n">
-        <v>2062.25</v>
+        <v>2020.5</v>
       </c>
       <c r="I57" t="n">
         <v>29967.5</v>
@@ -5308,6 +5311,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>29745.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>29803.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>29605.75</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>197.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>27248.25</v>
+      </c>
+      <c r="J58" t="n">
+        <v>26927.25</v>
+      </c>
+      <c r="K58" t="n">
+        <v>28381.25</v>
+      </c>
+      <c r="L58" t="n">
+        <v>29835.25</v>
+      </c>
+      <c r="M58" t="n">
+        <v>30401.75</v>
+      </c>
+      <c r="N58" t="n">
+        <v>30968.25</v>
+      </c>
+      <c r="O58" t="n">
+        <v>33309.75</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5325,7 +5325,7 @@
         <v>29803.5</v>
       </c>
       <c r="D58" t="n">
-        <v>29605.75</v>
+        <v>29576</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5337,7 +5337,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>197.75</v>
+        <v>227.5</v>
       </c>
       <c r="I58" t="n">
         <v>27248.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5319,25 +5316,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29745.5</v>
+        <v>29227</v>
       </c>
       <c r="C58" t="n">
-        <v>29803.5</v>
+        <v>30010.25</v>
       </c>
       <c r="D58" t="n">
-        <v>29576</v>
+        <v>29226</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>29851.25</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>459.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0156</v>
       </c>
       <c r="H58" t="n">
-        <v>227.5</v>
+        <v>784.25</v>
       </c>
       <c r="I58" t="n">
         <v>27248.25</v>
@@ -5360,10 +5357,8 @@
       <c r="O58" t="n">
         <v>33309.75</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5371,9 +5366,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>604.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23432.5</v>
+        <v>23922</v>
       </c>
       <c r="J2" t="n">
-        <v>24136.17</v>
+        <v>24319.73</v>
       </c>
       <c r="K2" t="n">
-        <v>24282.45</v>
+        <v>24404.82</v>
       </c>
       <c r="L2" t="n">
-        <v>24428.72</v>
+        <v>24489.91</v>
       </c>
       <c r="M2" t="n">
-        <v>24853.7</v>
+        <v>24731.32</v>
       </c>
       <c r="N2" t="n">
-        <v>25278.67</v>
+        <v>24972.73</v>
       </c>
       <c r="O2" t="n">
-        <v>25146.25</v>
+        <v>24901.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,11 +698,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5319,22 +5323,22 @@
         <v>29227</v>
       </c>
       <c r="C58" t="n">
-        <v>30010.25</v>
+        <v>29993.25</v>
       </c>
       <c r="D58" t="n">
         <v>29226</v>
       </c>
       <c r="E58" t="n">
-        <v>29851.25</v>
+        <v>29797.75</v>
       </c>
       <c r="F58" t="n">
-        <v>459.75</v>
+        <v>406.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0156</v>
+        <v>0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>784.25</v>
+        <v>767.25</v>
       </c>
       <c r="I58" t="n">
         <v>27248.25</v>
@@ -5366,9 +5370,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5323,22 +5323,22 @@
         <v>29227</v>
       </c>
       <c r="C58" t="n">
-        <v>29993.25</v>
+        <v>30113</v>
       </c>
       <c r="D58" t="n">
         <v>29226</v>
       </c>
       <c r="E58" t="n">
-        <v>29797.75</v>
+        <v>29656.75</v>
       </c>
       <c r="F58" t="n">
-        <v>406.25</v>
+        <v>265.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0138</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>767.25</v>
+        <v>887</v>
       </c>
       <c r="I58" t="n">
         <v>27248.25</v>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,34 +659,38 @@
         <v>604.75</v>
       </c>
       <c r="I2" t="n">
-        <v>23922</v>
+        <v>24250</v>
       </c>
       <c r="J2" t="n">
-        <v>24319.73</v>
+        <v>24442.73</v>
       </c>
       <c r="K2" t="n">
-        <v>24404.82</v>
+        <v>24486.82</v>
       </c>
       <c r="L2" t="n">
-        <v>24489.91</v>
+        <v>24530.91</v>
       </c>
       <c r="M2" t="n">
-        <v>24731.32</v>
+        <v>24649.32</v>
       </c>
       <c r="N2" t="n">
-        <v>24972.73</v>
+        <v>24767.73</v>
       </c>
       <c r="O2" t="n">
-        <v>24901.5</v>
+        <v>24737.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,17 +699,17 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5326,19 +5330,19 @@
         <v>30113</v>
       </c>
       <c r="D58" t="n">
-        <v>29226</v>
+        <v>29022.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29656.75</v>
+        <v>29143</v>
       </c>
       <c r="F58" t="n">
-        <v>265.25</v>
+        <v>-248.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>887</v>
+        <v>1090.25</v>
       </c>
       <c r="I58" t="n">
         <v>27248.25</v>
@@ -5389,11 +5393,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24850</v>
+        <v>24726.5</v>
       </c>
       <c r="C2" t="n">
-        <v>25027.25</v>
+        <v>25196.5</v>
       </c>
       <c r="D2" t="n">
-        <v>24422.5</v>
+        <v>24633.25</v>
       </c>
       <c r="E2" t="n">
-        <v>24726.75</v>
+        <v>24992</v>
       </c>
       <c r="F2" t="n">
-        <v>158.68</v>
+        <v>265.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0065</v>
+        <v>0.0107</v>
       </c>
       <c r="H2" t="n">
-        <v>604.75</v>
+        <v>563.25</v>
       </c>
       <c r="I2" t="n">
-        <v>24250</v>
+        <v>23817.75</v>
       </c>
       <c r="J2" t="n">
-        <v>24442.73</v>
+        <v>24122.94</v>
       </c>
       <c r="K2" t="n">
-        <v>24486.82</v>
+        <v>24424.38</v>
       </c>
       <c r="L2" t="n">
-        <v>24530.91</v>
+        <v>24725.81</v>
       </c>
       <c r="M2" t="n">
-        <v>24649.32</v>
+        <v>25029.12</v>
       </c>
       <c r="N2" t="n">
-        <v>24767.73</v>
+        <v>25332.44</v>
       </c>
       <c r="O2" t="n">
-        <v>24737.5</v>
+        <v>25632</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -699,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -722,68 +714,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C3" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D3" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E3" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F3" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H3" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I3" t="n">
-        <v>23817.75</v>
+        <v>24070</v>
       </c>
       <c r="J3" t="n">
-        <v>24122.94</v>
+        <v>24467.31</v>
       </c>
       <c r="K3" t="n">
-        <v>24424.38</v>
+        <v>24710.38</v>
       </c>
       <c r="L3" t="n">
-        <v>24725.81</v>
+        <v>24953.44</v>
       </c>
       <c r="M3" t="n">
-        <v>25029.12</v>
+        <v>25273.62</v>
       </c>
       <c r="N3" t="n">
-        <v>25332.44</v>
+        <v>25593.81</v>
       </c>
       <c r="O3" t="n">
-        <v>25632</v>
+        <v>25759.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -792,84 +788,84 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C4" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D4" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E4" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H4" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I4" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J4" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K4" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L4" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M4" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N4" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O4" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -883,57 +879,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C5" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D5" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E5" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F5" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H5" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I5" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J5" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K5" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L5" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M5" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N5" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O5" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -967,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C6" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D6" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E6" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F6" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H6" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I6" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J6" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K6" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L6" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M6" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N6" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O6" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1041,8 +1037,10 @@
       <c r="U6" s="8" t="n">
         <v/>
       </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="11" t="inlineStr">
         <is>
@@ -1058,155 +1056,147 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C7" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D7" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E7" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F7" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H7" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I7" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J7" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K7" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L7" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M7" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N7" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O7" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+        <v>27098</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C8" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D8" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E8" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F8" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H8" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I8" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J8" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K8" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L8" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M8" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N8" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O8" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>27822.75</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1228,50 +1218,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C9" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D9" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E9" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H9" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I9" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J9" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K9" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L9" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M9" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N9" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O9" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,12 +1269,14 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1306,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C10" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D10" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E10" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F10" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H10" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I10" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J10" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K10" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L10" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M10" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N10" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O10" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,22 +1349,24 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1381,55 +1375,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C11" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D11" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E11" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F11" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H11" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I11" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J11" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K11" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L11" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M11" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N11" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O11" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1447,13 +1445,11 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1472,70 +1468,72 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C12" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D12" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E12" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F12" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H12" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I12" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J12" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K12" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L12" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M12" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N12" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O12" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1549,65 +1547,63 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C13" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D13" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E13" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F13" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H13" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I13" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J13" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K13" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L13" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M13" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N13" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O13" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
@@ -1616,7 +1612,7 @@
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1633,59 +1629,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C14" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D14" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E14" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H14" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I14" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J14" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K14" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L14" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M14" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N14" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O14" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,21 +1685,23 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1717,79 +1711,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C15" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D15" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E15" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F15" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H15" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I15" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J15" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K15" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L15" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M15" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N15" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O15" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>26262.25</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1799,92 +1799,86 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C16" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D16" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E16" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H16" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I16" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J16" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K16" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L16" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M16" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N16" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O16" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1892,75 +1886,75 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C17" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D17" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E17" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F17" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I17" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J17" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K17" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L17" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M17" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N17" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O17" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1969,55 +1963,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C18" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D18" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E18" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H18" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I18" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J18" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K18" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L18" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M18" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N18" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O18" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,12 +2027,12 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2053,79 +2051,77 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C19" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D19" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E19" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F19" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H19" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I19" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J19" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K19" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L19" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M19" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N19" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O19" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2139,77 +2135,81 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C20" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D20" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E20" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H20" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I20" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J20" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K20" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L20" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M20" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N20" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O20" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>27332.75</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2223,76 +2223,70 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C21" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D21" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E21" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H21" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I21" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J21" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K21" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L21" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M21" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N21" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O21" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>27815.75</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2311,57 +2305,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C22" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D22" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E22" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H22" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I22" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J22" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K22" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L22" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M22" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N22" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O22" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2372,9 +2366,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2400,50 +2394,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C23" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D23" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E23" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F23" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H23" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I23" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J23" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K23" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L23" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M23" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N23" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O23" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,16 +2445,20 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2475,57 +2473,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C24" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D24" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E24" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H24" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I24" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J24" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K24" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L24" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M24" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N24" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O24" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,18 +2533,16 @@
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2561,57 +2557,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C25" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D25" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E25" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H25" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I25" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J25" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K25" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L25" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M25" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N25" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O25" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2629,8 +2625,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2652,50 +2650,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C26" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D26" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E26" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F26" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H26" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I26" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J26" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K26" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L26" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M26" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N26" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O26" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2703,20 +2701,16 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2731,74 +2725,80 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C27" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D27" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E27" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F27" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H27" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I27" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J27" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K27" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L27" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M27" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N27" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O27" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2813,81 +2813,77 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C28" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D28" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E28" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H28" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I28" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J28" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K28" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L28" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M28" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N28" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O28" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2901,57 +2897,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C29" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D29" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E29" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F29" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H29" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I29" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J29" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K29" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L29" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M29" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N29" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O29" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2969,73 +2965,71 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C30" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D30" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E30" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H30" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I30" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J30" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K30" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L30" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M30" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N30" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O30" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3074,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C31" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D31" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E31" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F31" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H31" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I31" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J31" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K31" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L31" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M31" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N31" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O31" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3135,16 +3129,14 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3156,50 +3148,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C32" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D32" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E32" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F32" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H32" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I32" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J32" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K32" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L32" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M32" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N32" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O32" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3236,50 +3228,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C33" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D33" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E33" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F33" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H33" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I33" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J33" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K33" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L33" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M33" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N33" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O33" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3297,14 +3289,18 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3316,50 +3312,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C34" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D34" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E34" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F34" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H34" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I34" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J34" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K34" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L34" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M34" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N34" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O34" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,78 +3368,76 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C35" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D35" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E35" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H35" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I35" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J35" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K35" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L35" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M35" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N35" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O35" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,16 +3445,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3475,57 +3473,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C36" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D36" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E36" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F36" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H36" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I36" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J36" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K36" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L36" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M36" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N36" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O36" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3533,10 +3531,8 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
@@ -3559,158 +3555,156 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C37" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E37" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F37" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H37" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I37" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J37" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K37" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L37" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M37" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N37" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O37" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+        <v>31395.75</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C38" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D38" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E38" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F38" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H38" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I38" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J38" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K38" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L38" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M38" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N38" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O38" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>32834.25</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3736,50 +3730,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C39" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D39" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E39" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F39" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H39" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I39" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J39" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K39" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L39" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M39" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N39" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O39" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3792,11 +3786,13 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3811,77 +3807,79 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C40" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D40" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E40" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F40" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H40" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I40" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J40" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K40" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L40" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M40" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N40" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O40" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3895,79 +3893,77 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C41" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D41" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F41" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H41" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I41" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J41" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K41" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L41" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M41" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N41" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O41" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3981,57 +3977,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C42" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D42" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F42" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H42" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I42" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J42" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K42" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L42" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M42" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N42" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O42" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4039,18 +4035,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4065,72 +4061,74 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C43" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D43" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E43" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F43" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H43" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I43" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J43" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K43" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L43" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M43" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N43" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O43" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4147,71 +4145,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C44" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D44" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E44" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H44" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I44" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J44" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K44" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L44" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M44" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N44" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O44" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4238,50 +4230,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C45" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D45" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E45" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F45" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H45" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I45" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J45" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K45" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L45" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M45" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N45" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O45" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4291,12 +4283,12 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4313,55 +4305,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C46" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D46" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E46" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F46" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H46" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I46" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J46" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K46" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L46" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M46" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N46" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O46" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4369,21 +4365,23 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4395,57 +4393,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C47" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D47" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E47" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F47" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H47" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I47" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J47" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K47" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L47" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M47" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N47" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O47" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4463,13 +4461,11 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4488,70 +4484,72 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C48" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D48" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E48" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F48" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H48" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I48" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J48" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K48" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L48" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M48" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N48" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O48" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4565,74 +4563,70 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C49" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D49" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E49" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F49" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H49" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I49" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J49" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K49" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L49" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M49" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N49" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O49" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4658,50 +4652,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C50" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D50" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E50" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F50" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H50" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I50" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J50" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K50" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L50" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M50" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N50" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O50" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4709,12 +4703,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4740,50 +4736,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C51" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D51" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E51" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F51" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H51" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I51" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J51" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K51" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L51" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M51" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N51" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O51" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4796,9 +4792,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4817,57 +4813,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C52" t="n">
-        <v>29764.75</v>
+        <v>29665.25</v>
       </c>
       <c r="D52" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E52" t="n">
-        <v>29387</v>
+        <v>29613.68</v>
       </c>
       <c r="F52" t="n">
-        <v>-178.25</v>
+        <v>226.68</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0077</v>
       </c>
       <c r="H52" t="n">
-        <v>724.25</v>
+        <v>901.5</v>
       </c>
       <c r="I52" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J52" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K52" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L52" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M52" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N52" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O52" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,13 +4876,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4901,57 +4899,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28997.75</v>
+        <v>29938</v>
       </c>
       <c r="C53" t="n">
-        <v>29665.25</v>
+        <v>31094.75</v>
       </c>
       <c r="D53" t="n">
-        <v>28763.75</v>
+        <v>29904</v>
       </c>
       <c r="E53" t="n">
-        <v>29613.68</v>
+        <v>30889.25</v>
       </c>
       <c r="F53" t="n">
-        <v>226.68</v>
+        <v>1275.57</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0431</v>
       </c>
       <c r="H53" t="n">
-        <v>901.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I53" t="n">
-        <v>28316.25</v>
+        <v>27862.25</v>
       </c>
       <c r="J53" t="n">
-        <v>28654.94</v>
+        <v>28911.77</v>
       </c>
       <c r="K53" t="n">
-        <v>29024.88</v>
+        <v>29162.93</v>
       </c>
       <c r="L53" t="n">
-        <v>29394.81</v>
+        <v>29414.09</v>
       </c>
       <c r="M53" t="n">
-        <v>29749.12</v>
+        <v>30064.43</v>
       </c>
       <c r="N53" t="n">
-        <v>30103.44</v>
+        <v>30714.77</v>
       </c>
       <c r="O53" t="n">
-        <v>30489</v>
+        <v>30566.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,85 +4957,83 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29938</v>
+        <v>30870</v>
       </c>
       <c r="C54" t="n">
-        <v>31094.75</v>
+        <v>31282.5</v>
       </c>
       <c r="D54" t="n">
-        <v>29904</v>
+        <v>30356.75</v>
       </c>
       <c r="E54" t="n">
-        <v>30889.25</v>
+        <v>31061.75</v>
       </c>
       <c r="F54" t="n">
-        <v>1275.57</v>
+        <v>172.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0056</v>
       </c>
       <c r="H54" t="n">
-        <v>1190.75</v>
+        <v>925.75</v>
       </c>
       <c r="I54" t="n">
-        <v>27862.25</v>
+        <v>28713.25</v>
       </c>
       <c r="J54" t="n">
-        <v>28911.77</v>
+        <v>29893.44</v>
       </c>
       <c r="K54" t="n">
-        <v>29162.93</v>
+        <v>30293.88</v>
       </c>
       <c r="L54" t="n">
-        <v>29414.09</v>
+        <v>30694.31</v>
       </c>
       <c r="M54" t="n">
-        <v>30064.43</v>
+        <v>31484.62</v>
       </c>
       <c r="N54" t="n">
-        <v>30714.77</v>
+        <v>32274.94</v>
       </c>
       <c r="O54" t="n">
-        <v>30566.75</v>
+        <v>32285.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5050,23 +5046,17 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5078,50 +5068,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>30870</v>
+        <v>31059</v>
       </c>
       <c r="C55" t="n">
-        <v>31282.5</v>
+        <v>31616.5</v>
       </c>
       <c r="D55" t="n">
-        <v>30356.75</v>
+        <v>30792</v>
       </c>
       <c r="E55" t="n">
-        <v>31061.75</v>
+        <v>31108.75</v>
       </c>
       <c r="F55" t="n">
-        <v>172.5</v>
+        <v>47</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0056</v>
+        <v>0.0015</v>
       </c>
       <c r="H55" t="n">
-        <v>925.75</v>
+        <v>824.5</v>
       </c>
       <c r="I55" t="n">
-        <v>28713.25</v>
+        <v>29431</v>
       </c>
       <c r="J55" t="n">
-        <v>29893.44</v>
+        <v>30257.06</v>
       </c>
       <c r="K55" t="n">
-        <v>30293.88</v>
+        <v>30598.88</v>
       </c>
       <c r="L55" t="n">
-        <v>30694.31</v>
+        <v>30940.69</v>
       </c>
       <c r="M55" t="n">
-        <v>31484.62</v>
+        <v>31524.62</v>
       </c>
       <c r="N55" t="n">
-        <v>32274.94</v>
+        <v>32108.56</v>
       </c>
       <c r="O55" t="n">
-        <v>32285.5</v>
+        <v>32208.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5137,8 +5127,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5156,79 +5148,83 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31059</v>
+        <v>31145.5</v>
       </c>
       <c r="C56" t="n">
-        <v>31616.5</v>
+        <v>31289.25</v>
       </c>
       <c r="D56" t="n">
-        <v>30792</v>
+        <v>29268.75</v>
       </c>
       <c r="E56" t="n">
-        <v>31108.75</v>
+        <v>29391.5</v>
       </c>
       <c r="F56" t="n">
-        <v>47</v>
+        <v>-1717.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0552</v>
       </c>
       <c r="H56" t="n">
-        <v>824.5</v>
+        <v>2020.5</v>
       </c>
       <c r="I56" t="n">
-        <v>29431</v>
+        <v>29967.5</v>
       </c>
       <c r="J56" t="n">
-        <v>30257.06</v>
+        <v>30236.5</v>
       </c>
       <c r="K56" t="n">
-        <v>30598.88</v>
+        <v>30696.5</v>
       </c>
       <c r="L56" t="n">
-        <v>30940.69</v>
+        <v>31156.5</v>
       </c>
       <c r="M56" t="n">
-        <v>31524.62</v>
+        <v>31521</v>
       </c>
       <c r="N56" t="n">
-        <v>32108.56</v>
+        <v>31885.5</v>
       </c>
       <c r="O56" t="n">
-        <v>32208.25</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+        <v>32441</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr"/>
@@ -5236,69 +5232,63 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31145.5</v>
+        <v>29227</v>
       </c>
       <c r="C57" t="n">
-        <v>31289.25</v>
+        <v>30113</v>
       </c>
       <c r="D57" t="n">
-        <v>29268.75</v>
+        <v>28987</v>
       </c>
       <c r="E57" t="n">
-        <v>29391.5</v>
+        <v>29175</v>
       </c>
       <c r="F57" t="n">
-        <v>-1717.25</v>
+        <v>-216.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0552</v>
+        <v>-0.0074</v>
       </c>
       <c r="H57" t="n">
-        <v>2020.5</v>
+        <v>1126</v>
       </c>
       <c r="I57" t="n">
-        <v>29967.5</v>
+        <v>27248.25</v>
       </c>
       <c r="J57" t="n">
-        <v>30236.5</v>
+        <v>26927.25</v>
       </c>
       <c r="K57" t="n">
-        <v>30696.5</v>
+        <v>28381.25</v>
       </c>
       <c r="L57" t="n">
-        <v>31156.5</v>
+        <v>29835.25</v>
       </c>
       <c r="M57" t="n">
-        <v>31521</v>
+        <v>30401.75</v>
       </c>
       <c r="N57" t="n">
-        <v>31885.5</v>
+        <v>30968.25</v>
       </c>
       <c r="O57" t="n">
-        <v>32441</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>33309.75</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5316,84 +5306,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>29227</v>
-      </c>
-      <c r="C58" t="n">
-        <v>30113</v>
-      </c>
-      <c r="D58" t="n">
-        <v>29022.75</v>
-      </c>
-      <c r="E58" t="n">
-        <v>29143</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-248.5</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.008500000000000001</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1090.25</v>
-      </c>
-      <c r="I58" t="n">
-        <v>27248.25</v>
-      </c>
-      <c r="J58" t="n">
-        <v>26927.25</v>
-      </c>
-      <c r="K58" t="n">
-        <v>28381.25</v>
-      </c>
-      <c r="L58" t="n">
-        <v>29835.25</v>
-      </c>
-      <c r="M58" t="n">
-        <v>30401.75</v>
-      </c>
-      <c r="N58" t="n">
-        <v>30968.25</v>
-      </c>
-      <c r="O58" t="n">
-        <v>33309.75</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -5245,13 +5245,13 @@
         <v>28987</v>
       </c>
       <c r="E57" t="n">
-        <v>29175</v>
+        <v>29100.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-216.5</v>
+        <v>-291.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0074</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H57" t="n">
         <v>1126</v>
@@ -5283,12 +5283,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>563.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23817.75</v>
+        <v>23819</v>
       </c>
       <c r="J2" t="n">
-        <v>24122.94</v>
+        <v>24124.5</v>
       </c>
       <c r="K2" t="n">
-        <v>24424.38</v>
+        <v>24425</v>
       </c>
       <c r="L2" t="n">
-        <v>24725.81</v>
+        <v>24725.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25029.12</v>
+        <v>25028.5</v>
       </c>
       <c r="N2" t="n">
-        <v>25332.44</v>
+        <v>25331.5</v>
       </c>
       <c r="O2" t="n">
-        <v>25632</v>
+        <v>25629.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5245,13 +5248,13 @@
         <v>28987</v>
       </c>
       <c r="E57" t="n">
-        <v>29100.25</v>
+        <v>29117.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-291.25</v>
+        <v>-273.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H57" t="n">
         <v>1126</v>
@@ -5283,31 +5286,113 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>29480.5</v>
+      </c>
+      <c r="C58" t="n">
+        <v>29588.5</v>
+      </c>
+      <c r="D58" t="n">
+        <v>29412.25</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>176.25</v>
+      </c>
+      <c r="I58" t="n">
+        <v>27861</v>
+      </c>
+      <c r="J58" t="n">
+        <v>27775.62</v>
+      </c>
+      <c r="K58" t="n">
+        <v>28554.75</v>
+      </c>
+      <c r="L58" t="n">
+        <v>29333.88</v>
+      </c>
+      <c r="M58" t="n">
+        <v>29680.75</v>
+      </c>
+      <c r="N58" t="n">
+        <v>30027.62</v>
+      </c>
+      <c r="O58" t="n">
+        <v>31239</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -662,25 +659,25 @@
         <v>563.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23819</v>
+        <v>23931.5</v>
       </c>
       <c r="J2" t="n">
-        <v>24124.5</v>
+        <v>24265.12</v>
       </c>
       <c r="K2" t="n">
-        <v>24425</v>
+        <v>24481.25</v>
       </c>
       <c r="L2" t="n">
-        <v>24725.5</v>
+        <v>24697.38</v>
       </c>
       <c r="M2" t="n">
-        <v>25028.5</v>
+        <v>24972.25</v>
       </c>
       <c r="N2" t="n">
-        <v>25331.5</v>
+        <v>25247.12</v>
       </c>
       <c r="O2" t="n">
-        <v>25629.5</v>
+        <v>25404.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5317,25 +5314,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29480.5</v>
+        <v>29268</v>
       </c>
       <c r="C58" t="n">
-        <v>29588.5</v>
+        <v>29903</v>
       </c>
       <c r="D58" t="n">
-        <v>29412.25</v>
+        <v>29024.25</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>29894.5</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>776.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0267</v>
       </c>
       <c r="H58" t="n">
-        <v>176.25</v>
+        <v>878.75</v>
       </c>
       <c r="I58" t="n">
         <v>27861</v>
@@ -5358,28 +5355,30 @@
       <c r="O58" t="n">
         <v>31239</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5390,7 +5389,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>563.25</v>
       </c>
       <c r="I2" t="n">
-        <v>23931.5</v>
+        <v>24051.5</v>
       </c>
       <c r="J2" t="n">
-        <v>24265.12</v>
+        <v>24415.12</v>
       </c>
       <c r="K2" t="n">
-        <v>24481.25</v>
+        <v>24541.25</v>
       </c>
       <c r="L2" t="n">
-        <v>24697.38</v>
+        <v>24667.38</v>
       </c>
       <c r="M2" t="n">
-        <v>24972.25</v>
+        <v>24912.25</v>
       </c>
       <c r="N2" t="n">
-        <v>25247.12</v>
+        <v>25157.12</v>
       </c>
       <c r="O2" t="n">
-        <v>25404.5</v>
+        <v>25164.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -698,11 +698,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5317,22 +5321,22 @@
         <v>29268</v>
       </c>
       <c r="C58" t="n">
-        <v>29903</v>
+        <v>30178</v>
       </c>
       <c r="D58" t="n">
         <v>29024.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29894.5</v>
+        <v>29529</v>
       </c>
       <c r="F58" t="n">
-        <v>776.75</v>
+        <v>411.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0267</v>
+        <v>0.0141</v>
       </c>
       <c r="H58" t="n">
-        <v>878.75</v>
+        <v>1153.75</v>
       </c>
       <c r="I58" t="n">
         <v>27861</v>
@@ -5371,14 +5375,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5389,7 +5393,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>563.25</v>
       </c>
       <c r="I2" t="n">
-        <v>24051.5</v>
+        <v>24292.5</v>
       </c>
       <c r="J2" t="n">
-        <v>24415.12</v>
+        <v>24545.75</v>
       </c>
       <c r="K2" t="n">
-        <v>24541.25</v>
+        <v>24613</v>
       </c>
       <c r="L2" t="n">
-        <v>24667.38</v>
+        <v>24680.25</v>
       </c>
       <c r="M2" t="n">
-        <v>24912.25</v>
+        <v>24840.5</v>
       </c>
       <c r="N2" t="n">
-        <v>25157.12</v>
+        <v>25000.75</v>
       </c>
       <c r="O2" t="n">
-        <v>25164.5</v>
+        <v>24975</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,12 +695,12 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
@@ -5324,19 +5324,19 @@
         <v>30178</v>
       </c>
       <c r="D58" t="n">
-        <v>29024.25</v>
+        <v>28822.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29529</v>
+        <v>28877.5</v>
       </c>
       <c r="F58" t="n">
-        <v>411.25</v>
+        <v>-240.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0141</v>
+        <v>-0.0083</v>
       </c>
       <c r="H58" t="n">
-        <v>1153.75</v>
+        <v>1355.75</v>
       </c>
       <c r="I58" t="n">
         <v>27861</v>
@@ -5365,17 +5365,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U58" s="8" t="inlineStr">
@@ -5393,7 +5395,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_weekly.xlsx
+++ b/three_gate/analysis/NQ_weekly.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24726.5</v>
+        <v>25000</v>
       </c>
       <c r="C2" t="n">
-        <v>25196.5</v>
+        <v>25394</v>
       </c>
       <c r="D2" t="n">
-        <v>24633.25</v>
+        <v>24158.5</v>
       </c>
       <c r="E2" t="n">
-        <v>24992</v>
+        <v>24397</v>
       </c>
       <c r="F2" t="n">
-        <v>265.25</v>
+        <v>-595</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0238</v>
       </c>
       <c r="H2" t="n">
-        <v>563.25</v>
+        <v>1235.5</v>
       </c>
       <c r="I2" t="n">
-        <v>24292.5</v>
+        <v>24070</v>
       </c>
       <c r="J2" t="n">
-        <v>24545.75</v>
+        <v>24467.31</v>
       </c>
       <c r="K2" t="n">
-        <v>24613</v>
+        <v>24710.38</v>
       </c>
       <c r="L2" t="n">
-        <v>24680.25</v>
+        <v>24953.44</v>
       </c>
       <c r="M2" t="n">
-        <v>24840.5</v>
+        <v>25273.62</v>
       </c>
       <c r="N2" t="n">
-        <v>25000.75</v>
+        <v>25593.81</v>
       </c>
       <c r="O2" t="n">
-        <v>24975</v>
+        <v>25759.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -698,158 +702,154 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25000</v>
+        <v>24542</v>
       </c>
       <c r="C3" t="n">
-        <v>25394</v>
+        <v>25179.5</v>
       </c>
       <c r="D3" t="n">
-        <v>24158.5</v>
+        <v>24410</v>
       </c>
       <c r="E3" t="n">
-        <v>24397</v>
+        <v>24986.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-595</v>
+        <v>589.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0238</v>
+        <v>0.0242</v>
       </c>
       <c r="H3" t="n">
-        <v>1235.5</v>
+        <v>769.5</v>
       </c>
       <c r="I3" t="n">
-        <v>24070</v>
+        <v>22923</v>
       </c>
       <c r="J3" t="n">
-        <v>24467.31</v>
+        <v>22971.88</v>
       </c>
       <c r="K3" t="n">
-        <v>24710.38</v>
+        <v>23779.25</v>
       </c>
       <c r="L3" t="n">
-        <v>24953.44</v>
+        <v>24586.62</v>
       </c>
       <c r="M3" t="n">
-        <v>25273.62</v>
+        <v>25014.75</v>
       </c>
       <c r="N3" t="n">
-        <v>25593.81</v>
+        <v>25442.88</v>
       </c>
       <c r="O3" t="n">
-        <v>25759.75</v>
+        <v>26629.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24542</v>
+        <v>25065.75</v>
       </c>
       <c r="C4" t="n">
-        <v>25179.5</v>
+        <v>25570.75</v>
       </c>
       <c r="D4" t="n">
-        <v>24410</v>
+        <v>24804.75</v>
       </c>
       <c r="E4" t="n">
-        <v>24986.5</v>
+        <v>25509.25</v>
       </c>
       <c r="F4" t="n">
-        <v>589.5</v>
+        <v>522.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0242</v>
+        <v>0.0209</v>
       </c>
       <c r="H4" t="n">
-        <v>769.5</v>
+        <v>766</v>
       </c>
       <c r="I4" t="n">
-        <v>22923</v>
+        <v>23640.5</v>
       </c>
       <c r="J4" t="n">
-        <v>22971.88</v>
+        <v>24312.88</v>
       </c>
       <c r="K4" t="n">
-        <v>23779.25</v>
+        <v>24601.75</v>
       </c>
       <c r="L4" t="n">
-        <v>24586.62</v>
+        <v>24890.62</v>
       </c>
       <c r="M4" t="n">
-        <v>25014.75</v>
+        <v>25371.25</v>
       </c>
       <c r="N4" t="n">
-        <v>25442.88</v>
+        <v>25851.88</v>
       </c>
       <c r="O4" t="n">
-        <v>26629.5</v>
+        <v>25949</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,7 +860,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -876,64 +876,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25065.75</v>
+        <v>25723.5</v>
       </c>
       <c r="C5" t="n">
-        <v>25570.75</v>
+        <v>26399</v>
       </c>
       <c r="D5" t="n">
-        <v>24804.75</v>
+        <v>25700</v>
       </c>
       <c r="E5" t="n">
-        <v>25509.25</v>
+        <v>26004</v>
       </c>
       <c r="F5" t="n">
-        <v>522.75</v>
+        <v>494.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0209</v>
+        <v>0.0194</v>
       </c>
       <c r="H5" t="n">
-        <v>766</v>
+        <v>699</v>
       </c>
       <c r="I5" t="n">
-        <v>23640.5</v>
+        <v>24038.75</v>
       </c>
       <c r="J5" t="n">
-        <v>24312.88</v>
+        <v>24904</v>
       </c>
       <c r="K5" t="n">
-        <v>24601.75</v>
+        <v>25126.25</v>
       </c>
       <c r="L5" t="n">
-        <v>24890.62</v>
+        <v>25348.5</v>
       </c>
       <c r="M5" t="n">
-        <v>25371.25</v>
+        <v>25892.25</v>
       </c>
       <c r="N5" t="n">
-        <v>25851.88</v>
+        <v>26436</v>
       </c>
       <c r="O5" t="n">
-        <v>25949</v>
+        <v>26336.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,7 +944,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -957,10 +957,12 @@
       <c r="U5" s="8" t="n">
         <v/>
       </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -974,155 +976,147 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25723.5</v>
+        <v>26028.25</v>
       </c>
       <c r="C6" t="n">
-        <v>26399</v>
+        <v>26266</v>
       </c>
       <c r="D6" t="n">
-        <v>25700</v>
+        <v>24709.25</v>
       </c>
       <c r="E6" t="n">
-        <v>26004</v>
+        <v>25166.25</v>
       </c>
       <c r="F6" t="n">
-        <v>494.75</v>
+        <v>-837.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0194</v>
+        <v>-0.0322</v>
       </c>
       <c r="H6" t="n">
-        <v>699</v>
+        <v>1556.75</v>
       </c>
       <c r="I6" t="n">
-        <v>24038.75</v>
+        <v>25001</v>
       </c>
       <c r="J6" t="n">
-        <v>24904</v>
+        <v>25282.25</v>
       </c>
       <c r="K6" t="n">
-        <v>25126.25</v>
+        <v>25654.5</v>
       </c>
       <c r="L6" t="n">
-        <v>25348.5</v>
+        <v>26026.75</v>
       </c>
       <c r="M6" t="n">
-        <v>25892.25</v>
+        <v>26353.5</v>
       </c>
       <c r="N6" t="n">
-        <v>26436</v>
+        <v>26680.25</v>
       </c>
       <c r="O6" t="n">
-        <v>26336.75</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>27098</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26028.25</v>
+        <v>25320.75</v>
       </c>
       <c r="C7" t="n">
-        <v>26266</v>
+        <v>25830</v>
       </c>
       <c r="D7" t="n">
-        <v>24709.25</v>
+        <v>24626</v>
       </c>
       <c r="E7" t="n">
-        <v>25166.25</v>
+        <v>25094</v>
       </c>
       <c r="F7" t="n">
-        <v>-837.75</v>
+        <v>-72.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0029</v>
       </c>
       <c r="H7" t="n">
-        <v>1556.75</v>
+        <v>1204</v>
       </c>
       <c r="I7" t="n">
-        <v>25001</v>
+        <v>23152.5</v>
       </c>
       <c r="J7" t="n">
-        <v>25282.25</v>
+        <v>23448.81</v>
       </c>
       <c r="K7" t="n">
-        <v>25654.5</v>
+        <v>24387.88</v>
       </c>
       <c r="L7" t="n">
-        <v>26026.75</v>
+        <v>25326.94</v>
       </c>
       <c r="M7" t="n">
-        <v>26353.5</v>
+        <v>25944.62</v>
       </c>
       <c r="N7" t="n">
-        <v>26680.25</v>
+        <v>26562.31</v>
       </c>
       <c r="O7" t="n">
-        <v>27098</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>27822.75</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1134,7 +1128,7 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1144,50 +1138,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25320.75</v>
+        <v>25142.25</v>
       </c>
       <c r="C8" t="n">
-        <v>25830</v>
+        <v>25361.25</v>
       </c>
       <c r="D8" t="n">
-        <v>24626</v>
+        <v>23904.5</v>
       </c>
       <c r="E8" t="n">
-        <v>25094</v>
+        <v>24305.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-72.25</v>
+        <v>-788.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0314</v>
       </c>
       <c r="H8" t="n">
-        <v>1204</v>
+        <v>1456.75</v>
       </c>
       <c r="I8" t="n">
-        <v>23152.5</v>
+        <v>23422</v>
       </c>
       <c r="J8" t="n">
-        <v>23448.81</v>
+        <v>23823</v>
       </c>
       <c r="K8" t="n">
-        <v>24387.88</v>
+        <v>24492</v>
       </c>
       <c r="L8" t="n">
-        <v>25326.94</v>
+        <v>25161</v>
       </c>
       <c r="M8" t="n">
-        <v>25944.62</v>
+        <v>25696</v>
       </c>
       <c r="N8" t="n">
-        <v>26562.31</v>
+        <v>26231</v>
       </c>
       <c r="O8" t="n">
-        <v>27822.75</v>
+        <v>27034</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1195,12 +1189,14 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1212,7 +1208,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1222,50 +1218,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25142.25</v>
+        <v>24455.75</v>
       </c>
       <c r="C9" t="n">
-        <v>25361.25</v>
+        <v>25499.75</v>
       </c>
       <c r="D9" t="n">
-        <v>23904.5</v>
+        <v>24361.75</v>
       </c>
       <c r="E9" t="n">
-        <v>24305.5</v>
+        <v>25482</v>
       </c>
       <c r="F9" t="n">
-        <v>-788.5</v>
+        <v>1176.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0314</v>
+        <v>0.0484</v>
       </c>
       <c r="H9" t="n">
-        <v>1456.75</v>
+        <v>1138</v>
       </c>
       <c r="I9" t="n">
-        <v>23422</v>
+        <v>22447.75</v>
       </c>
       <c r="J9" t="n">
-        <v>23823</v>
+        <v>22685.06</v>
       </c>
       <c r="K9" t="n">
-        <v>24492</v>
+        <v>23577.12</v>
       </c>
       <c r="L9" t="n">
-        <v>25161</v>
+        <v>24469.19</v>
       </c>
       <c r="M9" t="n">
-        <v>25696</v>
+        <v>25033.88</v>
       </c>
       <c r="N9" t="n">
-        <v>26231</v>
+        <v>25598.56</v>
       </c>
       <c r="O9" t="n">
-        <v>27034</v>
+        <v>26818</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1273,79 +1269,85 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24455.75</v>
+        <v>25482.5</v>
       </c>
       <c r="C10" t="n">
-        <v>25499.75</v>
+        <v>25868</v>
       </c>
       <c r="D10" t="n">
-        <v>24361.75</v>
+        <v>25193.25</v>
       </c>
       <c r="E10" t="n">
-        <v>25482</v>
+        <v>25732</v>
       </c>
       <c r="F10" t="n">
-        <v>1176.5</v>
+        <v>250</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0484</v>
+        <v>0.0098</v>
       </c>
       <c r="H10" t="n">
-        <v>1138</v>
+        <v>674.75</v>
       </c>
       <c r="I10" t="n">
-        <v>22447.75</v>
+        <v>23223.75</v>
       </c>
       <c r="J10" t="n">
-        <v>22685.06</v>
+        <v>24619.62</v>
       </c>
       <c r="K10" t="n">
-        <v>23577.12</v>
+        <v>24913</v>
       </c>
       <c r="L10" t="n">
-        <v>24469.19</v>
+        <v>25206.38</v>
       </c>
       <c r="M10" t="n">
-        <v>25033.88</v>
+        <v>26051</v>
       </c>
       <c r="N10" t="n">
-        <v>25598.56</v>
+        <v>26895.62</v>
       </c>
       <c r="O10" t="n">
-        <v>26818</v>
+        <v>26637.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,25 +1358,23 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1388,69 +1388,71 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25482.5</v>
+        <v>25750</v>
       </c>
       <c r="C11" t="n">
-        <v>25868</v>
+        <v>25870.75</v>
       </c>
       <c r="D11" t="n">
-        <v>25193.25</v>
+        <v>25118</v>
       </c>
       <c r="E11" t="n">
-        <v>25732</v>
+        <v>25213.5</v>
       </c>
       <c r="F11" t="n">
-        <v>250</v>
+        <v>-518.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0098</v>
+        <v>-0.0202</v>
       </c>
       <c r="H11" t="n">
-        <v>674.75</v>
+        <v>752.75</v>
       </c>
       <c r="I11" t="n">
-        <v>23223.75</v>
+        <v>24518.5</v>
       </c>
       <c r="J11" t="n">
-        <v>24619.62</v>
+        <v>25157.94</v>
       </c>
       <c r="K11" t="n">
-        <v>24913</v>
+        <v>25394.62</v>
       </c>
       <c r="L11" t="n">
-        <v>25206.38</v>
+        <v>25631.31</v>
       </c>
       <c r="M11" t="n">
-        <v>26051</v>
+        <v>26069.38</v>
       </c>
       <c r="N11" t="n">
-        <v>26895.62</v>
+        <v>26507.44</v>
       </c>
       <c r="O11" t="n">
-        <v>26637.75</v>
+        <v>26542.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1458,81 +1460,79 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25750</v>
+        <v>25223.5</v>
       </c>
       <c r="C12" t="n">
-        <v>25870.75</v>
+        <v>25410</v>
       </c>
       <c r="D12" t="n">
-        <v>25118</v>
+        <v>24654.5</v>
       </c>
       <c r="E12" t="n">
-        <v>25213.5</v>
+        <v>25132.79</v>
       </c>
       <c r="F12" t="n">
-        <v>-518.5</v>
+        <v>-80.70999999999999</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0202</v>
+        <v>-0.0032</v>
       </c>
       <c r="H12" t="n">
-        <v>752.75</v>
+        <v>755.5</v>
       </c>
       <c r="I12" t="n">
-        <v>24518.5</v>
+        <v>24365.25</v>
       </c>
       <c r="J12" t="n">
-        <v>25157.94</v>
+        <v>24320.31</v>
       </c>
       <c r="K12" t="n">
-        <v>25394.62</v>
+        <v>24837.12</v>
       </c>
       <c r="L12" t="n">
-        <v>25631.31</v>
+        <v>25353.94</v>
       </c>
       <c r="M12" t="n">
-        <v>26069.38</v>
+        <v>25589.88</v>
       </c>
       <c r="N12" t="n">
-        <v>26507.44</v>
+        <v>25825.81</v>
       </c>
       <c r="O12" t="n">
-        <v>26542.75</v>
+        <v>26623.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q12" s="6" t="n">
+        <v/>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1544,64 +1544,60 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>25223.5</v>
+        <v>25635.25</v>
       </c>
       <c r="C13" t="n">
-        <v>25410</v>
+        <v>25935.25</v>
       </c>
       <c r="D13" t="n">
-        <v>24654.5</v>
+        <v>25608.25</v>
       </c>
       <c r="E13" t="n">
-        <v>25132.79</v>
+        <v>25863.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-80.70999999999999</v>
+        <v>730.46</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0032</v>
+        <v>0.0291</v>
       </c>
       <c r="H13" t="n">
-        <v>755.5</v>
+        <v>327</v>
       </c>
       <c r="I13" t="n">
-        <v>24365.25</v>
+        <v>23899</v>
       </c>
       <c r="J13" t="n">
-        <v>24320.31</v>
+        <v>24427.56</v>
       </c>
       <c r="K13" t="n">
-        <v>24837.12</v>
+        <v>24755.04</v>
       </c>
       <c r="L13" t="n">
-        <v>25353.94</v>
+        <v>25082.52</v>
       </c>
       <c r="M13" t="n">
-        <v>25589.88</v>
+        <v>25510.54</v>
       </c>
       <c r="N13" t="n">
-        <v>25825.81</v>
+        <v>25938.56</v>
       </c>
       <c r="O13" t="n">
-        <v>26623.5</v>
+        <v>26165.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,198 +1605,200 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>25635.25</v>
+        <v>25863.25</v>
       </c>
       <c r="C14" t="n">
-        <v>25935.25</v>
+        <v>25893.75</v>
       </c>
       <c r="D14" t="n">
-        <v>25608.25</v>
+        <v>25265.25</v>
       </c>
       <c r="E14" t="n">
-        <v>25863.25</v>
+        <v>25385.25</v>
       </c>
       <c r="F14" t="n">
-        <v>730.46</v>
+        <v>-478</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0291</v>
+        <v>-0.0185</v>
       </c>
       <c r="H14" t="n">
-        <v>327</v>
+        <v>628.5</v>
       </c>
       <c r="I14" t="n">
-        <v>23899</v>
+        <v>25281.25</v>
       </c>
       <c r="J14" t="n">
-        <v>24427.56</v>
+        <v>25582</v>
       </c>
       <c r="K14" t="n">
-        <v>24755.04</v>
+        <v>25699.75</v>
       </c>
       <c r="L14" t="n">
-        <v>25082.52</v>
+        <v>25817.5</v>
       </c>
       <c r="M14" t="n">
-        <v>25510.54</v>
+        <v>26026.75</v>
       </c>
       <c r="N14" t="n">
-        <v>25938.56</v>
+        <v>26236</v>
       </c>
       <c r="O14" t="n">
-        <v>26165.5</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>26262.25</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25863.25</v>
+        <v>25431.75</v>
       </c>
       <c r="C15" t="n">
-        <v>25893.75</v>
+        <v>25996.25</v>
       </c>
       <c r="D15" t="n">
-        <v>25265.25</v>
+        <v>25406.5</v>
       </c>
       <c r="E15" t="n">
-        <v>25385.25</v>
+        <v>25938.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-478</v>
+        <v>553</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0218</v>
       </c>
       <c r="H15" t="n">
-        <v>628.5</v>
+        <v>589.75</v>
       </c>
       <c r="I15" t="n">
-        <v>25281.25</v>
+        <v>24636.75</v>
       </c>
       <c r="J15" t="n">
-        <v>25582</v>
+        <v>24659.62</v>
       </c>
       <c r="K15" t="n">
-        <v>25699.75</v>
+        <v>25071</v>
       </c>
       <c r="L15" t="n">
-        <v>25817.5</v>
+        <v>25482.38</v>
       </c>
       <c r="M15" t="n">
-        <v>26026.75</v>
+        <v>25699.5</v>
       </c>
       <c r="N15" t="n">
-        <v>26236</v>
+        <v>25916.62</v>
       </c>
       <c r="O15" t="n">
-        <v>26262.25</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>26522.25</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1808,132 +1806,136 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25431.75</v>
+        <v>25949</v>
       </c>
       <c r="C16" t="n">
-        <v>25996.25</v>
+        <v>26045.5</v>
       </c>
       <c r="D16" t="n">
-        <v>25406.5</v>
+        <v>25420.75</v>
       </c>
       <c r="E16" t="n">
-        <v>25938.25</v>
+        <v>25689</v>
       </c>
       <c r="F16" t="n">
-        <v>553</v>
+        <v>-249.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0218</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>589.75</v>
+        <v>624.75</v>
       </c>
       <c r="I16" t="n">
-        <v>24636.75</v>
+        <v>24816.75</v>
       </c>
       <c r="J16" t="n">
-        <v>24659.62</v>
+        <v>25466.94</v>
       </c>
       <c r="K16" t="n">
-        <v>25071</v>
+        <v>25643.38</v>
       </c>
       <c r="L16" t="n">
-        <v>25482.38</v>
+        <v>25819.81</v>
       </c>
       <c r="M16" t="n">
-        <v>25699.5</v>
+        <v>26233.12</v>
       </c>
       <c r="N16" t="n">
-        <v>25916.62</v>
+        <v>26646.44</v>
       </c>
       <c r="O16" t="n">
-        <v>26522.25</v>
+        <v>26586</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25949</v>
+        <v>25471</v>
       </c>
       <c r="C17" t="n">
-        <v>26045.5</v>
+        <v>25845.75</v>
       </c>
       <c r="D17" t="n">
-        <v>25420.75</v>
+        <v>25025</v>
       </c>
       <c r="E17" t="n">
-        <v>25689</v>
+        <v>25738.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-249.25</v>
+        <v>49.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0019</v>
       </c>
       <c r="H17" t="n">
-        <v>624.75</v>
+        <v>820.75</v>
       </c>
       <c r="I17" t="n">
-        <v>24816.75</v>
+        <v>24796</v>
       </c>
       <c r="J17" t="n">
-        <v>25466.94</v>
+        <v>25042.19</v>
       </c>
       <c r="K17" t="n">
-        <v>25643.38</v>
+        <v>25376.62</v>
       </c>
       <c r="L17" t="n">
-        <v>25819.81</v>
+        <v>25711.06</v>
       </c>
       <c r="M17" t="n">
-        <v>26233.12</v>
+        <v>26001.38</v>
       </c>
       <c r="N17" t="n">
-        <v>26646.44</v>
+        <v>26291.69</v>
       </c>
       <c r="O17" t="n">
-        <v>26586</v>
+        <v>26670.25</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,12 +1947,12 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1962,169 +1964,171 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25471</v>
+        <v>25585.5</v>
       </c>
       <c r="C18" t="n">
-        <v>25845.75</v>
+        <v>26349</v>
       </c>
       <c r="D18" t="n">
-        <v>25025</v>
+        <v>25365.25</v>
       </c>
       <c r="E18" t="n">
-        <v>25738.25</v>
+        <v>25670</v>
       </c>
       <c r="F18" t="n">
-        <v>49.25</v>
+        <v>-68.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0027</v>
       </c>
       <c r="H18" t="n">
-        <v>820.75</v>
+        <v>983.75</v>
       </c>
       <c r="I18" t="n">
-        <v>24796</v>
+        <v>24204.25</v>
       </c>
       <c r="J18" t="n">
-        <v>25042.19</v>
+        <v>25068.94</v>
       </c>
       <c r="K18" t="n">
-        <v>25376.62</v>
+        <v>25327.88</v>
       </c>
       <c r="L18" t="n">
-        <v>25711.06</v>
+        <v>25586.81</v>
       </c>
       <c r="M18" t="n">
-        <v>26001.38</v>
+        <v>26148.62</v>
       </c>
       <c r="N18" t="n">
-        <v>26291.69</v>
+        <v>26710.44</v>
       </c>
       <c r="O18" t="n">
-        <v>26670.25</v>
+        <v>26666.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>25585.5</v>
+        <v>25530</v>
       </c>
       <c r="C19" t="n">
-        <v>26349</v>
+        <v>26027.75</v>
       </c>
       <c r="D19" t="n">
-        <v>25365.25</v>
+        <v>24239.75</v>
       </c>
       <c r="E19" t="n">
-        <v>25670</v>
+        <v>25163.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-68.25</v>
+        <v>-506.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0197</v>
       </c>
       <c r="H19" t="n">
-        <v>983.75</v>
+        <v>1788</v>
       </c>
       <c r="I19" t="n">
-        <v>24204.25</v>
+        <v>24381.5</v>
       </c>
       <c r="J19" t="n">
-        <v>25068.94</v>
+        <v>24592.69</v>
       </c>
       <c r="K19" t="n">
-        <v>25327.88</v>
+        <v>25178.12</v>
       </c>
       <c r="L19" t="n">
-        <v>25586.81</v>
+        <v>25763.56</v>
       </c>
       <c r="M19" t="n">
-        <v>26148.62</v>
+        <v>26161.88</v>
       </c>
       <c r="N19" t="n">
-        <v>26710.44</v>
+        <v>26560.19</v>
       </c>
       <c r="O19" t="n">
-        <v>26666.5</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>27332.75</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2132,83 +2136,77 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>25530</v>
+        <v>25153.75</v>
       </c>
       <c r="C20" t="n">
-        <v>26027.75</v>
+        <v>25465.25</v>
       </c>
       <c r="D20" t="n">
-        <v>24239.75</v>
+        <v>24578.75</v>
       </c>
       <c r="E20" t="n">
-        <v>25163.25</v>
+        <v>24803.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-506.75</v>
+        <v>-360</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0197</v>
+        <v>-0.0143</v>
       </c>
       <c r="H20" t="n">
-        <v>1788</v>
+        <v>886.5</v>
       </c>
       <c r="I20" t="n">
-        <v>24381.5</v>
+        <v>22451.75</v>
       </c>
       <c r="J20" t="n">
-        <v>24592.69</v>
+        <v>23390</v>
       </c>
       <c r="K20" t="n">
-        <v>25178.12</v>
+        <v>24269.25</v>
       </c>
       <c r="L20" t="n">
-        <v>25763.56</v>
+        <v>25148.5</v>
       </c>
       <c r="M20" t="n">
-        <v>26161.88</v>
+        <v>26057.25</v>
       </c>
       <c r="N20" t="n">
-        <v>26560.19</v>
+        <v>26966</v>
       </c>
       <c r="O20" t="n">
-        <v>27332.75</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>27815.75</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2220,64 +2218,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25153.75</v>
+        <v>24789.75</v>
       </c>
       <c r="C21" t="n">
-        <v>25465.25</v>
+        <v>25139.5</v>
       </c>
       <c r="D21" t="n">
-        <v>24578.75</v>
+        <v>24449.25</v>
       </c>
       <c r="E21" t="n">
-        <v>24803.25</v>
+        <v>25067.5</v>
       </c>
       <c r="F21" t="n">
-        <v>-360</v>
+        <v>264.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0143</v>
+        <v>0.0107</v>
       </c>
       <c r="H21" t="n">
-        <v>886.5</v>
+        <v>690.25</v>
       </c>
       <c r="I21" t="n">
-        <v>22451.75</v>
+        <v>23692.25</v>
       </c>
       <c r="J21" t="n">
-        <v>23390</v>
+        <v>23807.38</v>
       </c>
       <c r="K21" t="n">
-        <v>24269.25</v>
+        <v>24360</v>
       </c>
       <c r="L21" t="n">
-        <v>25148.5</v>
+        <v>24912.62</v>
       </c>
       <c r="M21" t="n">
-        <v>26057.25</v>
+        <v>25246.5</v>
       </c>
       <c r="N21" t="n">
-        <v>26966</v>
+        <v>25580.38</v>
       </c>
       <c r="O21" t="n">
-        <v>27815.75</v>
+        <v>26351.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2290,7 +2288,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2302,7 +2300,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2316,50 +2314,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24789.75</v>
+        <v>25033.75</v>
       </c>
       <c r="C22" t="n">
-        <v>25139.5</v>
+        <v>25494.75</v>
       </c>
       <c r="D22" t="n">
-        <v>24449.25</v>
+        <v>24668</v>
       </c>
       <c r="E22" t="n">
-        <v>25067.5</v>
+        <v>25004.75</v>
       </c>
       <c r="F22" t="n">
-        <v>264.25</v>
+        <v>-62.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0025</v>
       </c>
       <c r="H22" t="n">
-        <v>690.25</v>
+        <v>826.75</v>
       </c>
       <c r="I22" t="n">
-        <v>23692.25</v>
+        <v>23759</v>
       </c>
       <c r="J22" t="n">
-        <v>23807.38</v>
+        <v>24513.81</v>
       </c>
       <c r="K22" t="n">
-        <v>24360</v>
+        <v>24722.38</v>
       </c>
       <c r="L22" t="n">
-        <v>24912.62</v>
+        <v>24930.94</v>
       </c>
       <c r="M22" t="n">
-        <v>25246.5</v>
+        <v>25412.62</v>
       </c>
       <c r="N22" t="n">
-        <v>25580.38</v>
+        <v>25894.31</v>
       </c>
       <c r="O22" t="n">
-        <v>26351.75</v>
+        <v>25829.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,16 +2365,20 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2384,64 +2386,64 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25033.75</v>
+        <v>24682.5</v>
       </c>
       <c r="C23" t="n">
-        <v>25494.75</v>
+        <v>25250</v>
       </c>
       <c r="D23" t="n">
-        <v>24668</v>
+        <v>24352</v>
       </c>
       <c r="E23" t="n">
-        <v>25004.75</v>
+        <v>24670.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-62.75</v>
+        <v>-334.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0134</v>
       </c>
       <c r="H23" t="n">
-        <v>826.75</v>
+        <v>898</v>
       </c>
       <c r="I23" t="n">
-        <v>23759</v>
+        <v>23841.25</v>
       </c>
       <c r="J23" t="n">
-        <v>24513.81</v>
+        <v>24139.69</v>
       </c>
       <c r="K23" t="n">
-        <v>24722.38</v>
+        <v>24591.38</v>
       </c>
       <c r="L23" t="n">
-        <v>24930.94</v>
+        <v>25043.06</v>
       </c>
       <c r="M23" t="n">
-        <v>25412.62</v>
+        <v>25418.12</v>
       </c>
       <c r="N23" t="n">
-        <v>25894.31</v>
+        <v>25793.19</v>
       </c>
       <c r="O23" t="n">
-        <v>25829.75</v>
+        <v>26321.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,18 +2453,16 @@
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2470,64 +2470,64 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24682.5</v>
+        <v>24435.25</v>
       </c>
       <c r="C24" t="n">
-        <v>25250</v>
+        <v>25217.5</v>
       </c>
       <c r="D24" t="n">
-        <v>24352</v>
+        <v>24000</v>
       </c>
       <c r="E24" t="n">
-        <v>24670.25</v>
+        <v>24394.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-334.5</v>
+        <v>-276</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0134</v>
+        <v>-0.0112</v>
       </c>
       <c r="H24" t="n">
-        <v>898</v>
+        <v>1217.5</v>
       </c>
       <c r="I24" t="n">
-        <v>23841.25</v>
+        <v>23454</v>
       </c>
       <c r="J24" t="n">
-        <v>24139.69</v>
+        <v>23706.88</v>
       </c>
       <c r="K24" t="n">
-        <v>24591.38</v>
+        <v>24221.25</v>
       </c>
       <c r="L24" t="n">
-        <v>25043.06</v>
+        <v>24735.62</v>
       </c>
       <c r="M24" t="n">
-        <v>25418.12</v>
+        <v>25119.25</v>
       </c>
       <c r="N24" t="n">
-        <v>25793.19</v>
+        <v>25502.88</v>
       </c>
       <c r="O24" t="n">
-        <v>26321.5</v>
+        <v>26148</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,13 +2540,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2554,7 +2556,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2568,50 +2570,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>24435.25</v>
+        <v>24285</v>
       </c>
       <c r="C25" t="n">
-        <v>25217.5</v>
+        <v>24989</v>
       </c>
       <c r="D25" t="n">
-        <v>24000</v>
+        <v>24108.75</v>
       </c>
       <c r="E25" t="n">
-        <v>24394.25</v>
+        <v>24291.78</v>
       </c>
       <c r="F25" t="n">
-        <v>-276</v>
+        <v>-102.47</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0112</v>
+        <v>-0.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>1217.5</v>
+        <v>880.25</v>
       </c>
       <c r="I25" t="n">
-        <v>23454</v>
+        <v>22782.5</v>
       </c>
       <c r="J25" t="n">
-        <v>23706.88</v>
+        <v>23069.5</v>
       </c>
       <c r="K25" t="n">
-        <v>24221.25</v>
+        <v>23785.5</v>
       </c>
       <c r="L25" t="n">
-        <v>24735.62</v>
+        <v>24501.5</v>
       </c>
       <c r="M25" t="n">
-        <v>25119.25</v>
+        <v>25003</v>
       </c>
       <c r="N25" t="n">
-        <v>25502.88</v>
+        <v>25504.5</v>
       </c>
       <c r="O25" t="n">
-        <v>26148</v>
+        <v>26435</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,20 +2621,16 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2640,81 +2638,87 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>24285</v>
+        <v>23902</v>
       </c>
       <c r="C26" t="n">
-        <v>24989</v>
+        <v>24763</v>
       </c>
       <c r="D26" t="n">
-        <v>24108.75</v>
+        <v>23232.5</v>
       </c>
       <c r="E26" t="n">
-        <v>24291.78</v>
+        <v>23328.5</v>
       </c>
       <c r="F26" t="n">
-        <v>-102.47</v>
+        <v>-963.28</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0397</v>
       </c>
       <c r="H26" t="n">
-        <v>880.25</v>
+        <v>1530.5</v>
       </c>
       <c r="I26" t="n">
-        <v>22782.5</v>
+        <v>23228.5</v>
       </c>
       <c r="J26" t="n">
-        <v>23069.5</v>
+        <v>23282.98</v>
       </c>
       <c r="K26" t="n">
-        <v>23785.5</v>
+        <v>23851.65</v>
       </c>
       <c r="L26" t="n">
-        <v>24501.5</v>
+        <v>24420.33</v>
       </c>
       <c r="M26" t="n">
-        <v>25003</v>
+        <v>24731.9</v>
       </c>
       <c r="N26" t="n">
-        <v>25504.5</v>
+        <v>25043.48</v>
       </c>
       <c r="O26" t="n">
-        <v>26435</v>
+        <v>25869.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2722,152 +2726,148 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23902</v>
+        <v>23189.5</v>
       </c>
       <c r="C27" t="n">
-        <v>24763</v>
+        <v>24348.25</v>
       </c>
       <c r="D27" t="n">
-        <v>23232.5</v>
+        <v>22961.5</v>
       </c>
       <c r="E27" t="n">
-        <v>23328.5</v>
+        <v>24129.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-963.28</v>
+        <v>801.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0397</v>
+        <v>0.0343</v>
       </c>
       <c r="H27" t="n">
-        <v>1530.5</v>
+        <v>1386.75</v>
       </c>
       <c r="I27" t="n">
-        <v>23228.5</v>
+        <v>21702</v>
       </c>
       <c r="J27" t="n">
-        <v>23282.98</v>
+        <v>21463.38</v>
       </c>
       <c r="K27" t="n">
-        <v>23851.65</v>
+        <v>22563.25</v>
       </c>
       <c r="L27" t="n">
-        <v>24420.33</v>
+        <v>23663.12</v>
       </c>
       <c r="M27" t="n">
-        <v>24731.9</v>
+        <v>24093.75</v>
       </c>
       <c r="N27" t="n">
-        <v>25043.48</v>
+        <v>24524.38</v>
       </c>
       <c r="O27" t="n">
-        <v>25869.25</v>
+        <v>26293.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23189.5</v>
+        <v>24093.5</v>
       </c>
       <c r="C28" t="n">
-        <v>24348.25</v>
+        <v>25393</v>
       </c>
       <c r="D28" t="n">
-        <v>22961.5</v>
+        <v>23941.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24129.75</v>
+        <v>25281.25</v>
       </c>
       <c r="F28" t="n">
-        <v>801.25</v>
+        <v>1151.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0343</v>
+        <v>0.0477</v>
       </c>
       <c r="H28" t="n">
-        <v>1386.75</v>
+        <v>1451.5</v>
       </c>
       <c r="I28" t="n">
-        <v>21702</v>
+        <v>21574.75</v>
       </c>
       <c r="J28" t="n">
-        <v>21463.38</v>
+        <v>22980.44</v>
       </c>
       <c r="K28" t="n">
-        <v>22563.25</v>
+        <v>23436.38</v>
       </c>
       <c r="L28" t="n">
-        <v>23663.12</v>
+        <v>23892.31</v>
       </c>
       <c r="M28" t="n">
-        <v>24093.75</v>
+        <v>24823.12</v>
       </c>
       <c r="N28" t="n">
-        <v>24524.38</v>
+        <v>25753.94</v>
       </c>
       <c r="O28" t="n">
-        <v>26293.5</v>
+        <v>25735</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2878,80 +2878,78 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24093.5</v>
+        <v>24980</v>
       </c>
       <c r="C29" t="n">
-        <v>25393</v>
+        <v>26884.75</v>
       </c>
       <c r="D29" t="n">
-        <v>23941.5</v>
+        <v>24904.5</v>
       </c>
       <c r="E29" t="n">
-        <v>25281.25</v>
+        <v>26825.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1151.5</v>
+        <v>1544.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0477</v>
+        <v>0.0611</v>
       </c>
       <c r="H29" t="n">
-        <v>1451.5</v>
+        <v>1980.25</v>
       </c>
       <c r="I29" t="n">
-        <v>21574.75</v>
+        <v>22490</v>
       </c>
       <c r="J29" t="n">
-        <v>22980.44</v>
+        <v>24136.75</v>
       </c>
       <c r="K29" t="n">
-        <v>23436.38</v>
+        <v>24555.5</v>
       </c>
       <c r="L29" t="n">
-        <v>23892.31</v>
+        <v>24974.25</v>
       </c>
       <c r="M29" t="n">
-        <v>24823.12</v>
+        <v>26007</v>
       </c>
       <c r="N29" t="n">
-        <v>25753.94</v>
+        <v>27039.75</v>
       </c>
       <c r="O29" t="n">
-        <v>25735</v>
+        <v>26844.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2962,7 +2960,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2980,7 +2978,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2990,50 +2988,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>24980</v>
+        <v>26599.75</v>
       </c>
       <c r="C30" t="n">
-        <v>26884.75</v>
+        <v>27462.5</v>
       </c>
       <c r="D30" t="n">
-        <v>24904.5</v>
+        <v>26535</v>
       </c>
       <c r="E30" t="n">
-        <v>26825.5</v>
+        <v>27435</v>
       </c>
       <c r="F30" t="n">
-        <v>1544.25</v>
+        <v>609.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0611</v>
+        <v>0.0227</v>
       </c>
       <c r="H30" t="n">
-        <v>1980.25</v>
+        <v>927.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22490</v>
+        <v>22924.25</v>
       </c>
       <c r="J30" t="n">
-        <v>24136.75</v>
+        <v>25310.69</v>
       </c>
       <c r="K30" t="n">
-        <v>24555.5</v>
+        <v>25835.38</v>
       </c>
       <c r="L30" t="n">
-        <v>24974.25</v>
+        <v>26360.06</v>
       </c>
       <c r="M30" t="n">
-        <v>26007</v>
+        <v>27815.62</v>
       </c>
       <c r="N30" t="n">
-        <v>27039.75</v>
+        <v>29271.19</v>
       </c>
       <c r="O30" t="n">
-        <v>26844.5</v>
+        <v>28865</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3044,25 +3042,23 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3072,50 +3068,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>26599.75</v>
+        <v>27403.25</v>
       </c>
       <c r="C31" t="n">
-        <v>27462.5</v>
+        <v>27917</v>
       </c>
       <c r="D31" t="n">
-        <v>26535</v>
+        <v>27009.5</v>
       </c>
       <c r="E31" t="n">
-        <v>27435</v>
+        <v>27835.75</v>
       </c>
       <c r="F31" t="n">
-        <v>609.5</v>
+        <v>400.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0227</v>
+        <v>0.0146</v>
       </c>
       <c r="H31" t="n">
-        <v>927.5</v>
+        <v>907.5</v>
       </c>
       <c r="I31" t="n">
-        <v>22924.25</v>
+        <v>25607.5</v>
       </c>
       <c r="J31" t="n">
-        <v>25310.69</v>
+        <v>26725.62</v>
       </c>
       <c r="K31" t="n">
-        <v>25835.38</v>
+        <v>26971.25</v>
       </c>
       <c r="L31" t="n">
-        <v>26360.06</v>
+        <v>27216.88</v>
       </c>
       <c r="M31" t="n">
-        <v>27815.62</v>
+        <v>27898.75</v>
       </c>
       <c r="N31" t="n">
-        <v>29271.19</v>
+        <v>28580.62</v>
       </c>
       <c r="O31" t="n">
-        <v>28865</v>
+        <v>28390</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3126,7 +3122,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3142,7 +3138,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3152,50 +3148,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27403.25</v>
+        <v>27890</v>
       </c>
       <c r="C32" t="n">
-        <v>27917</v>
+        <v>29386.75</v>
       </c>
       <c r="D32" t="n">
-        <v>27009.5</v>
+        <v>27613</v>
       </c>
       <c r="E32" t="n">
-        <v>27835.75</v>
+        <v>29332.5</v>
       </c>
       <c r="F32" t="n">
-        <v>400.75</v>
+        <v>1496.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0146</v>
+        <v>0.0538</v>
       </c>
       <c r="H32" t="n">
-        <v>907.5</v>
+        <v>1773.75</v>
       </c>
       <c r="I32" t="n">
-        <v>25607.5</v>
+        <v>26102</v>
       </c>
       <c r="J32" t="n">
-        <v>26725.62</v>
+        <v>27114.5</v>
       </c>
       <c r="K32" t="n">
-        <v>26971.25</v>
+        <v>27382</v>
       </c>
       <c r="L32" t="n">
-        <v>27216.88</v>
+        <v>27649.5</v>
       </c>
       <c r="M32" t="n">
-        <v>27898.75</v>
+        <v>28289.5</v>
       </c>
       <c r="N32" t="n">
-        <v>28580.62</v>
+        <v>28929.5</v>
       </c>
       <c r="O32" t="n">
-        <v>28390</v>
+        <v>28824.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3206,23 +3202,27 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3232,50 +3232,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>27890</v>
+        <v>29294</v>
       </c>
       <c r="C33" t="n">
-        <v>29386.75</v>
+        <v>29782</v>
       </c>
       <c r="D33" t="n">
-        <v>27613</v>
+        <v>28742</v>
       </c>
       <c r="E33" t="n">
-        <v>29332.5</v>
+        <v>29231.75</v>
       </c>
       <c r="F33" t="n">
-        <v>1496.75</v>
+        <v>-100.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0034</v>
       </c>
       <c r="H33" t="n">
-        <v>1773.75</v>
+        <v>1040</v>
       </c>
       <c r="I33" t="n">
-        <v>26102</v>
+        <v>25839.25</v>
       </c>
       <c r="J33" t="n">
-        <v>27114.5</v>
+        <v>27975.06</v>
       </c>
       <c r="K33" t="n">
-        <v>27382</v>
+        <v>28445.62</v>
       </c>
       <c r="L33" t="n">
-        <v>27649.5</v>
+        <v>28916.19</v>
       </c>
       <c r="M33" t="n">
-        <v>28289.5</v>
+        <v>30219.38</v>
       </c>
       <c r="N33" t="n">
-        <v>28929.5</v>
+        <v>31522.56</v>
       </c>
       <c r="O33" t="n">
-        <v>28824.5</v>
+        <v>31160.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3286,80 +3286,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29294</v>
+        <v>29135</v>
       </c>
       <c r="C34" t="n">
-        <v>29782</v>
+        <v>29749</v>
       </c>
       <c r="D34" t="n">
-        <v>28742</v>
+        <v>28663</v>
       </c>
       <c r="E34" t="n">
-        <v>29231.75</v>
+        <v>29558.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-100.75</v>
+        <v>327</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0034</v>
+        <v>0.0112</v>
       </c>
       <c r="H34" t="n">
-        <v>1040</v>
+        <v>1086</v>
       </c>
       <c r="I34" t="n">
-        <v>25839.25</v>
+        <v>27702</v>
       </c>
       <c r="J34" t="n">
-        <v>27975.06</v>
+        <v>28176.62</v>
       </c>
       <c r="K34" t="n">
-        <v>28445.62</v>
+        <v>28711.75</v>
       </c>
       <c r="L34" t="n">
-        <v>28916.19</v>
+        <v>29246.88</v>
       </c>
       <c r="M34" t="n">
-        <v>30219.38</v>
+        <v>29751.75</v>
       </c>
       <c r="N34" t="n">
-        <v>31522.56</v>
+        <v>30256.62</v>
       </c>
       <c r="O34" t="n">
-        <v>31160.5</v>
+        <v>30822</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3367,16 +3365,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3384,64 +3386,64 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29135</v>
+        <v>29676.25</v>
       </c>
       <c r="C35" t="n">
-        <v>29749</v>
+        <v>30536</v>
       </c>
       <c r="D35" t="n">
-        <v>28663</v>
+        <v>29676.25</v>
       </c>
       <c r="E35" t="n">
-        <v>29558.75</v>
+        <v>30405.25</v>
       </c>
       <c r="F35" t="n">
-        <v>327</v>
+        <v>846.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0112</v>
+        <v>0.0286</v>
       </c>
       <c r="H35" t="n">
-        <v>1086</v>
+        <v>859.75</v>
       </c>
       <c r="I35" t="n">
-        <v>27702</v>
+        <v>27577</v>
       </c>
       <c r="J35" t="n">
-        <v>28176.62</v>
+        <v>28649.12</v>
       </c>
       <c r="K35" t="n">
-        <v>28711.75</v>
+        <v>29015.75</v>
       </c>
       <c r="L35" t="n">
-        <v>29246.88</v>
+        <v>29382.38</v>
       </c>
       <c r="M35" t="n">
-        <v>29751.75</v>
+        <v>30101.75</v>
       </c>
       <c r="N35" t="n">
-        <v>30256.62</v>
+        <v>30821.12</v>
       </c>
       <c r="O35" t="n">
-        <v>30822</v>
+        <v>30835</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,12 +3451,10 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3470,83 +3470,83 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29676.25</v>
+        <v>30415.5</v>
       </c>
       <c r="C36" t="n">
-        <v>30536</v>
+        <v>30807.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29676.25</v>
+        <v>28781.25</v>
       </c>
       <c r="E36" t="n">
-        <v>30405.25</v>
+        <v>29026.5</v>
       </c>
       <c r="F36" t="n">
-        <v>846.5</v>
+        <v>-1378.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0286</v>
+        <v>-0.0453</v>
       </c>
       <c r="H36" t="n">
-        <v>859.75</v>
+        <v>2026.5</v>
       </c>
       <c r="I36" t="n">
-        <v>27577</v>
+        <v>28816.5</v>
       </c>
       <c r="J36" t="n">
-        <v>28649.12</v>
+        <v>29695.06</v>
       </c>
       <c r="K36" t="n">
-        <v>29015.75</v>
+        <v>29975.38</v>
       </c>
       <c r="L36" t="n">
-        <v>29382.38</v>
+        <v>30255.69</v>
       </c>
       <c r="M36" t="n">
-        <v>30101.75</v>
+        <v>30835.12</v>
       </c>
       <c r="N36" t="n">
-        <v>30821.12</v>
+        <v>31414.56</v>
       </c>
       <c r="O36" t="n">
-        <v>30835</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>31395.75</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3556,77 +3556,75 @@
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30415.5</v>
+        <v>28844.5</v>
       </c>
       <c r="C37" t="n">
-        <v>30807.75</v>
+        <v>29848.25</v>
       </c>
       <c r="D37" t="n">
-        <v>28781.25</v>
+        <v>28227.75</v>
       </c>
       <c r="E37" t="n">
-        <v>29026.5</v>
+        <v>29662</v>
       </c>
       <c r="F37" t="n">
-        <v>-1378.75</v>
+        <v>635.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0453</v>
+        <v>0.0219</v>
       </c>
       <c r="H37" t="n">
-        <v>2026.5</v>
+        <v>1620.5</v>
       </c>
       <c r="I37" t="n">
-        <v>28816.5</v>
+        <v>26754.75</v>
       </c>
       <c r="J37" t="n">
-        <v>29695.06</v>
+        <v>26616</v>
       </c>
       <c r="K37" t="n">
-        <v>29975.38</v>
+        <v>28013.25</v>
       </c>
       <c r="L37" t="n">
-        <v>30255.69</v>
+        <v>29410.5</v>
       </c>
       <c r="M37" t="n">
-        <v>30835.12</v>
+        <v>30039.75</v>
       </c>
       <c r="N37" t="n">
-        <v>31414.56</v>
+        <v>30669</v>
       </c>
       <c r="O37" t="n">
-        <v>31395.75</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>32834.25</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3638,7 +3636,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3652,50 +3650,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28844.5</v>
+        <v>29907</v>
       </c>
       <c r="C38" t="n">
-        <v>29848.25</v>
+        <v>30770.75</v>
       </c>
       <c r="D38" t="n">
-        <v>28227.75</v>
+        <v>29616</v>
       </c>
       <c r="E38" t="n">
-        <v>29662</v>
+        <v>30647</v>
       </c>
       <c r="F38" t="n">
-        <v>635.5</v>
+        <v>985</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0219</v>
+        <v>0.0332</v>
       </c>
       <c r="H38" t="n">
-        <v>1620.5</v>
+        <v>1154.75</v>
       </c>
       <c r="I38" t="n">
-        <v>26754.75</v>
+        <v>26607.25</v>
       </c>
       <c r="J38" t="n">
-        <v>26616</v>
+        <v>28353.5</v>
       </c>
       <c r="K38" t="n">
-        <v>28013.25</v>
+        <v>28851.75</v>
       </c>
       <c r="L38" t="n">
-        <v>29410.5</v>
+        <v>29350</v>
       </c>
       <c r="M38" t="n">
-        <v>30039.75</v>
+        <v>30472.25</v>
       </c>
       <c r="N38" t="n">
-        <v>30669</v>
+        <v>31594.5</v>
       </c>
       <c r="O38" t="n">
-        <v>32834.25</v>
+        <v>31468.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3706,13 +3704,15 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3720,83 +3720,85 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29907</v>
+        <v>30577</v>
       </c>
       <c r="C39" t="n">
-        <v>30770.75</v>
+        <v>30968</v>
       </c>
       <c r="D39" t="n">
-        <v>29616</v>
+        <v>29160.5</v>
       </c>
       <c r="E39" t="n">
-        <v>30647</v>
+        <v>29368.25</v>
       </c>
       <c r="F39" t="n">
-        <v>985</v>
+        <v>-1278.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0332</v>
+        <v>-0.0417</v>
       </c>
       <c r="H39" t="n">
-        <v>1154.75</v>
+        <v>1807.5</v>
       </c>
       <c r="I39" t="n">
-        <v>26607.25</v>
+        <v>28461.25</v>
       </c>
       <c r="J39" t="n">
-        <v>28353.5</v>
+        <v>29719.06</v>
       </c>
       <c r="K39" t="n">
-        <v>28851.75</v>
+        <v>30069.62</v>
       </c>
       <c r="L39" t="n">
-        <v>29350</v>
+        <v>30420.19</v>
       </c>
       <c r="M39" t="n">
-        <v>30472.25</v>
+        <v>31224.38</v>
       </c>
       <c r="N39" t="n">
-        <v>31594.5</v>
+        <v>32028.56</v>
       </c>
       <c r="O39" t="n">
-        <v>31468.75</v>
+        <v>31925.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3804,150 +3806,148 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30577</v>
+        <v>29282.5</v>
       </c>
       <c r="C40" t="n">
-        <v>30968</v>
+        <v>30599.75</v>
       </c>
       <c r="D40" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E40" t="n">
-        <v>29368.25</v>
+        <v>29901.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-1278.75</v>
+        <v>533.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0417</v>
+        <v>0.0182</v>
       </c>
       <c r="H40" t="n">
-        <v>1807.5</v>
+        <v>1326</v>
       </c>
       <c r="I40" t="n">
-        <v>28461.25</v>
+        <v>27353</v>
       </c>
       <c r="J40" t="n">
-        <v>29719.06</v>
+        <v>27212.75</v>
       </c>
       <c r="K40" t="n">
-        <v>30069.62</v>
+        <v>28464.5</v>
       </c>
       <c r="L40" t="n">
-        <v>30420.19</v>
+        <v>29716.25</v>
       </c>
       <c r="M40" t="n">
-        <v>31224.38</v>
+        <v>30272</v>
       </c>
       <c r="N40" t="n">
-        <v>32028.56</v>
+        <v>30827.75</v>
       </c>
       <c r="O40" t="n">
-        <v>31925.5</v>
+        <v>32775.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29282.5</v>
+        <v>29930.25</v>
       </c>
       <c r="C41" t="n">
-        <v>30599.75</v>
+        <v>30094</v>
       </c>
       <c r="D41" t="n">
-        <v>29273.75</v>
+        <v>28909.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29901.75</v>
+        <v>30032.25</v>
       </c>
       <c r="F41" t="n">
-        <v>533.5</v>
+        <v>130.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0182</v>
+        <v>0.0044</v>
       </c>
       <c r="H41" t="n">
-        <v>1326</v>
+        <v>1184.25</v>
       </c>
       <c r="I41" t="n">
-        <v>27353</v>
+        <v>27947.75</v>
       </c>
       <c r="J41" t="n">
-        <v>27212.75</v>
+        <v>28558.25</v>
       </c>
       <c r="K41" t="n">
-        <v>28464.5</v>
+        <v>29238.75</v>
       </c>
       <c r="L41" t="n">
-        <v>29716.25</v>
+        <v>29919.25</v>
       </c>
       <c r="M41" t="n">
-        <v>30272</v>
+        <v>30564.75</v>
       </c>
       <c r="N41" t="n">
-        <v>30827.75</v>
+        <v>31210.25</v>
       </c>
       <c r="O41" t="n">
-        <v>32775.5</v>
+        <v>31925.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,18 +3955,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3974,70 +3974,72 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29930.25</v>
+        <v>29952</v>
       </c>
       <c r="C42" t="n">
-        <v>30094</v>
+        <v>30062.5</v>
       </c>
       <c r="D42" t="n">
-        <v>28909.75</v>
+        <v>28408.25</v>
       </c>
       <c r="E42" t="n">
-        <v>30032.25</v>
+        <v>28773.25</v>
       </c>
       <c r="F42" t="n">
-        <v>130.5</v>
+        <v>-1259</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0419</v>
       </c>
       <c r="H42" t="n">
-        <v>1184.25</v>
+        <v>1654.25</v>
       </c>
       <c r="I42" t="n">
-        <v>27947.75</v>
+        <v>27725.5</v>
       </c>
       <c r="J42" t="n">
-        <v>28558.25</v>
+        <v>29113.19</v>
       </c>
       <c r="K42" t="n">
-        <v>29238.75</v>
+        <v>29440.12</v>
       </c>
       <c r="L42" t="n">
-        <v>29919.25</v>
+        <v>29767.06</v>
       </c>
       <c r="M42" t="n">
-        <v>30564.75</v>
+        <v>30624.38</v>
       </c>
       <c r="N42" t="n">
-        <v>31210.25</v>
+        <v>31481.69</v>
       </c>
       <c r="O42" t="n">
-        <v>31925.75</v>
+        <v>31278.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4046,7 +4048,7 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4058,79 +4060,73 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29952</v>
+        <v>28747.75</v>
       </c>
       <c r="C43" t="n">
-        <v>30062.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D43" t="n">
-        <v>28408.25</v>
+        <v>28212.5</v>
       </c>
       <c r="E43" t="n">
-        <v>28773.25</v>
+        <v>28282.25</v>
       </c>
       <c r="F43" t="n">
-        <v>-1259</v>
+        <v>-491</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0419</v>
+        <v>-0.0171</v>
       </c>
       <c r="H43" t="n">
-        <v>1654.25</v>
+        <v>1152.25</v>
       </c>
       <c r="I43" t="n">
-        <v>27725.5</v>
+        <v>26754</v>
       </c>
       <c r="J43" t="n">
-        <v>29113.19</v>
+        <v>26887.94</v>
       </c>
       <c r="K43" t="n">
-        <v>29440.12</v>
+        <v>27946.12</v>
       </c>
       <c r="L43" t="n">
-        <v>29767.06</v>
+        <v>29004.31</v>
       </c>
       <c r="M43" t="n">
-        <v>30624.38</v>
+        <v>29600.38</v>
       </c>
       <c r="N43" t="n">
-        <v>31481.69</v>
+        <v>30196.44</v>
       </c>
       <c r="O43" t="n">
-        <v>31278.25</v>
+        <v>31716.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4144,7 +4140,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4154,50 +4150,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28747.75</v>
+        <v>28500</v>
       </c>
       <c r="C44" t="n">
-        <v>29364.75</v>
+        <v>28763.25</v>
       </c>
       <c r="D44" t="n">
-        <v>28212.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E44" t="n">
-        <v>28282.25</v>
+        <v>28404.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-491</v>
+        <v>122</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0171</v>
+        <v>0.0043</v>
       </c>
       <c r="H44" t="n">
-        <v>1152.25</v>
+        <v>1561.75</v>
       </c>
       <c r="I44" t="n">
-        <v>26754</v>
+        <v>27060.25</v>
       </c>
       <c r="J44" t="n">
-        <v>26887.94</v>
+        <v>26876.81</v>
       </c>
       <c r="K44" t="n">
-        <v>27946.12</v>
+        <v>27706.12</v>
       </c>
       <c r="L44" t="n">
-        <v>29004.31</v>
+        <v>28535.44</v>
       </c>
       <c r="M44" t="n">
-        <v>29600.38</v>
+        <v>28858.38</v>
       </c>
       <c r="N44" t="n">
-        <v>30196.44</v>
+        <v>29181.31</v>
       </c>
       <c r="O44" t="n">
-        <v>31716.75</v>
+        <v>30517</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4207,12 +4203,12 @@
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4224,60 +4220,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28500</v>
+        <v>28565</v>
       </c>
       <c r="C45" t="n">
-        <v>28763.25</v>
+        <v>30074</v>
       </c>
       <c r="D45" t="n">
-        <v>27201.5</v>
+        <v>28313.5</v>
       </c>
       <c r="E45" t="n">
-        <v>28404.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F45" t="n">
-        <v>122</v>
+        <v>1430.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0504</v>
       </c>
       <c r="H45" t="n">
-        <v>1561.75</v>
+        <v>1760.5</v>
       </c>
       <c r="I45" t="n">
-        <v>27060.25</v>
+        <v>25639.75</v>
       </c>
       <c r="J45" t="n">
-        <v>26876.81</v>
+        <v>27053.44</v>
       </c>
       <c r="K45" t="n">
-        <v>27706.12</v>
+        <v>27623.38</v>
       </c>
       <c r="L45" t="n">
-        <v>28535.44</v>
+        <v>28193.31</v>
       </c>
       <c r="M45" t="n">
-        <v>28858.38</v>
+        <v>29185.12</v>
       </c>
       <c r="N45" t="n">
-        <v>29181.31</v>
+        <v>30176.94</v>
       </c>
       <c r="O45" t="n">
-        <v>30517</v>
+        <v>30325</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4285,83 +4285,85 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28565</v>
+        <v>29851.25</v>
       </c>
       <c r="C46" t="n">
-        <v>30074</v>
+        <v>30283</v>
       </c>
       <c r="D46" t="n">
-        <v>28313.5</v>
+        <v>29533.5</v>
       </c>
       <c r="E46" t="n">
-        <v>29834.75</v>
+        <v>30141.75</v>
       </c>
       <c r="F46" t="n">
-        <v>1430.5</v>
+        <v>307</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0504</v>
+        <v>0.0103</v>
       </c>
       <c r="H46" t="n">
-        <v>1760.5</v>
+        <v>749.5</v>
       </c>
       <c r="I46" t="n">
-        <v>25639.75</v>
+        <v>26553</v>
       </c>
       <c r="J46" t="n">
-        <v>27053.44</v>
+        <v>28394.75</v>
       </c>
       <c r="K46" t="n">
-        <v>27623.38</v>
+        <v>28954.5</v>
       </c>
       <c r="L46" t="n">
-        <v>28193.31</v>
+        <v>29514.25</v>
       </c>
       <c r="M46" t="n">
-        <v>29185.12</v>
+        <v>30715</v>
       </c>
       <c r="N46" t="n">
-        <v>30176.94</v>
+        <v>31915.75</v>
       </c>
       <c r="O46" t="n">
-        <v>30325</v>
+        <v>31834.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4372,25 +4374,23 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4404,69 +4404,71 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29851.25</v>
+        <v>30170</v>
       </c>
       <c r="C47" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D47" t="n">
-        <v>29533.5</v>
+        <v>29202.75</v>
       </c>
       <c r="E47" t="n">
-        <v>30141.75</v>
+        <v>29387.75</v>
       </c>
       <c r="F47" t="n">
-        <v>307</v>
+        <v>-754</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.025</v>
       </c>
       <c r="H47" t="n">
-        <v>749.5</v>
+        <v>1140.25</v>
       </c>
       <c r="I47" t="n">
-        <v>26553</v>
+        <v>28784</v>
       </c>
       <c r="J47" t="n">
-        <v>28394.75</v>
+        <v>29509</v>
       </c>
       <c r="K47" t="n">
-        <v>28954.5</v>
+        <v>29767</v>
       </c>
       <c r="L47" t="n">
-        <v>29514.25</v>
+        <v>30025</v>
       </c>
       <c r="M47" t="n">
-        <v>30715</v>
+        <v>30516.5</v>
       </c>
       <c r="N47" t="n">
-        <v>31915.75</v>
+        <v>31008</v>
       </c>
       <c r="O47" t="n">
-        <v>31834.5</v>
+        <v>31032.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4474,81 +4476,77 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>30170</v>
+        <v>29392.25</v>
       </c>
       <c r="C48" t="n">
-        <v>30343</v>
+        <v>29811.5</v>
       </c>
       <c r="D48" t="n">
-        <v>29202.75</v>
+        <v>28946.75</v>
       </c>
       <c r="E48" t="n">
-        <v>29387.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F48" t="n">
-        <v>-754</v>
+        <v>104</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.025</v>
+        <v>0.0035</v>
       </c>
       <c r="H48" t="n">
-        <v>1140.25</v>
+        <v>864.75</v>
       </c>
       <c r="I48" t="n">
-        <v>28784</v>
+        <v>28062.5</v>
       </c>
       <c r="J48" t="n">
-        <v>29509</v>
+        <v>28054.94</v>
       </c>
       <c r="K48" t="n">
-        <v>29767</v>
+        <v>28817.62</v>
       </c>
       <c r="L48" t="n">
-        <v>30025</v>
+        <v>29580.31</v>
       </c>
       <c r="M48" t="n">
-        <v>30516.5</v>
+        <v>29957.88</v>
       </c>
       <c r="N48" t="n">
-        <v>31008</v>
+        <v>30335.44</v>
       </c>
       <c r="O48" t="n">
-        <v>31032.5</v>
+        <v>31483.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4560,7 +4558,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4574,50 +4572,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29392.25</v>
+        <v>29540</v>
       </c>
       <c r="C49" t="n">
-        <v>29811.5</v>
+        <v>29704.5</v>
       </c>
       <c r="D49" t="n">
-        <v>28946.75</v>
+        <v>28927.25</v>
       </c>
       <c r="E49" t="n">
-        <v>29491.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F49" t="n">
-        <v>104</v>
+        <v>73.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0025</v>
       </c>
       <c r="H49" t="n">
-        <v>864.75</v>
+        <v>777.25</v>
       </c>
       <c r="I49" t="n">
-        <v>28062.5</v>
+        <v>28082</v>
       </c>
       <c r="J49" t="n">
-        <v>28054.94</v>
+        <v>28683.31</v>
       </c>
       <c r="K49" t="n">
-        <v>28817.62</v>
+        <v>29059.38</v>
       </c>
       <c r="L49" t="n">
-        <v>29580.31</v>
+        <v>29435.44</v>
       </c>
       <c r="M49" t="n">
-        <v>29957.88</v>
+        <v>29924.12</v>
       </c>
       <c r="N49" t="n">
-        <v>30335.44</v>
+        <v>30412.81</v>
       </c>
       <c r="O49" t="n">
-        <v>31483.25</v>
+        <v>30676.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4625,12 +4623,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4642,7 +4642,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4656,50 +4656,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29540</v>
+        <v>29535.25</v>
       </c>
       <c r="C50" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D50" t="n">
-        <v>28927.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E50" t="n">
-        <v>29565.25</v>
+        <v>29387</v>
       </c>
       <c r="F50" t="n">
-        <v>73.5</v>
+        <v>-178.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.006</v>
       </c>
       <c r="H50" t="n">
-        <v>777.25</v>
+        <v>724.25</v>
       </c>
       <c r="I50" t="n">
-        <v>28082</v>
+        <v>28150</v>
       </c>
       <c r="J50" t="n">
-        <v>28683.31</v>
+        <v>28912.69</v>
       </c>
       <c r="K50" t="n">
-        <v>29059.38</v>
+        <v>29176.62</v>
       </c>
       <c r="L50" t="n">
-        <v>29435.44</v>
+        <v>29440.56</v>
       </c>
       <c r="M50" t="n">
-        <v>29924.12</v>
+        <v>29953.88</v>
       </c>
       <c r="N50" t="n">
-        <v>30412.81</v>
+        <v>30467.19</v>
       </c>
       <c r="O50" t="n">
-        <v>30676.25</v>
+        <v>30481.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4726,64 +4726,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29535.25</v>
+        <v>28997.75</v>
       </c>
       <c r="C51" t="n">
-        <v>29764.75</v>
+        <v>29665.25</v>
       </c>
       <c r="D51" t="n">
-        <v>29040.5</v>
+        <v>28763.75</v>
       </c>
       <c r="E51" t="n">
-        <v>29387</v>
+        <v>29613.68</v>
       </c>
       <c r="F51" t="n">
-        <v>-178.25</v>
+        <v>226.68</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.006</v>
+        <v>0.0077</v>
       </c>
       <c r="H51" t="n">
-        <v>724.25</v>
+        <v>901.5</v>
       </c>
       <c r="I51" t="n">
-        <v>28150</v>
+        <v>28316.25</v>
       </c>
       <c r="J51" t="n">
-        <v>28912.69</v>
+        <v>28654.94</v>
       </c>
       <c r="K51" t="n">
-        <v>29176.62</v>
+        <v>29024.88</v>
       </c>
       <c r="L51" t="n">
-        <v>29440.56</v>
+        <v>29394.81</v>
       </c>
       <c r="M51" t="n">
-        <v>29953.88</v>
+        <v>29749.12</v>
       </c>
       <c r="N51" t="n">
-        <v>30467.19</v>
+        <v>30103.44</v>
       </c>
       <c r="O51" t="n">
-        <v>30481.75</v>
+        <v>30489</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4798,11 +4798,13 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4810,64 +4812,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28997.75</v>
+        <v>29938</v>
       </c>
       <c r="C52" t="n">
-        <v>29665.25</v>
+        <v>31094.75</v>
       </c>
       <c r="D52" t="n">
-        <v>28763.75</v>
+        <v>29904</v>
       </c>
       <c r="E52" t="n">
-        <v>29613.68</v>
+        <v>30889.25</v>
       </c>
       <c r="F52" t="n">
-        <v>226.68</v>
+        <v>1275.57</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0431</v>
       </c>
       <c r="H52" t="n">
-        <v>901.5</v>
+        <v>1190.75</v>
       </c>
       <c r="I52" t="n">
-        <v>28316.25</v>
+        <v>27862.25</v>
       </c>
       <c r="J52" t="n">
-        <v>28654.94</v>
+        <v>28911.77</v>
       </c>
       <c r="K52" t="n">
-        <v>29024.88</v>
+        <v>29162.93</v>
       </c>
       <c r="L52" t="n">
-        <v>29394.81</v>
+        <v>29414.09</v>
       </c>
       <c r="M52" t="n">
-        <v>29749.12</v>
+        <v>30064.43</v>
       </c>
       <c r="N52" t="n">
-        <v>30103.44</v>
+        <v>30714.77</v>
       </c>
       <c r="O52" t="n">
-        <v>30489</v>
+        <v>30566.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4875,85 +4877,83 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29938</v>
+        <v>30870</v>
       </c>
       <c r="C53" t="n">
-        <v>31094.75</v>
+        <v>31282.5</v>
       </c>
       <c r="D53" t="n">
-        <v>29904</v>
+        <v>30356.75</v>
       </c>
       <c r="E53" t="n">
-        <v>30889.25</v>
+        <v>31061.75</v>
       </c>
       <c r="F53" t="n">
-        <v>1275.57</v>
+        <v>172.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0431</v>
+        <v>0.0056</v>
       </c>
       <c r="H53" t="n">
-        <v>1190.75</v>
+        <v>925.75</v>
       </c>
       <c r="I53" t="n">
-        <v>27862.25</v>
+        <v>28713.25</v>
       </c>
       <c r="J53" t="n">
-        <v>28911.77</v>
+        <v>29893.44</v>
       </c>
       <c r="K53" t="n">
-        <v>29162.93</v>
+        <v>30293.88</v>
       </c>
       <c r="L53" t="n">
-        <v>29414.09</v>
+        <v>30694.31</v>
       </c>
       <c r="M53" t="n">
-        <v>30064.43</v>
+        <v>31484.62</v>
       </c>
       <c r="N53" t="n">
-        <v>30714.77</v>
+        <v>32274.94</v>
       </c>
       <c r="O53" t="n">
-        <v>30566.75</v>
+        <v>32285.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4964,27 +4964,21 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4994,50 +4988,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30870</v>
+        <v>31059</v>
       </c>
       <c r="C54" t="n">
-        <v>31282.5</v>
+        <v>31616.5</v>
       </c>
       <c r="D54" t="n">
-        <v>30356.75</v>
+        <v>30792</v>
       </c>
       <c r="E54" t="n">
-        <v>31061.75</v>
+        <v>31108.75</v>
       </c>
       <c r="F54" t="n">
-        <v>172.5</v>
+        <v>47</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0056</v>
+        <v>0.0015</v>
       </c>
       <c r="H54" t="n">
-        <v>925.75</v>
+        <v>824.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28713.25</v>
+        <v>29431</v>
       </c>
       <c r="J54" t="n">
-        <v>29893.44</v>
+        <v>30257.06</v>
       </c>
       <c r="K54" t="n">
-        <v>30293.88</v>
+        <v>30598.88</v>
       </c>
       <c r="L54" t="n">
-        <v>30694.31</v>
+        <v>30940.69</v>
       </c>
       <c r="M54" t="n">
-        <v>31484.62</v>
+        <v>31524.62</v>
       </c>
       <c r="N54" t="n">
-        <v>32274.94</v>
+        <v>32108.56</v>
       </c>
       <c r="O54" t="n">
-        <v>32285.5</v>
+        <v>32208.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5048,13 +5042,15 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5062,7 +5058,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5072,69 +5068,73 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>31059</v>
+        <v>31145.5</v>
       </c>
       <c r="C55" t="n">
-        <v>31616.5</v>
+        <v>31289.25</v>
       </c>
       <c r="D55" t="n">
-        <v>30792</v>
+        <v>29268.75</v>
       </c>
       <c r="E55" t="n">
-        <v>31108.75</v>
+        <v>29391.5</v>
       </c>
       <c r="F55" t="n">
-        <v>47</v>
+        <v>-1717.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0552</v>
       </c>
       <c r="H55" t="n">
-        <v>824.5</v>
+        <v>2020.5</v>
       </c>
       <c r="I55" t="n">
-        <v>29431</v>
+        <v>29967.5</v>
       </c>
       <c r="J55" t="n">
-        <v>30257.06</v>
+        <v>30236.5</v>
       </c>
       <c r="K55" t="n">
-        <v>30598.88</v>
+        <v>30696.5</v>
       </c>
       <c r="L55" t="n">
-        <v>30940.69</v>
+        <v>31156.5</v>
       </c>
       <c r="M55" t="n">
-        <v>31524.62</v>
+        <v>31521</v>
       </c>
       <c r="N55" t="n">
-        <v>32108.56</v>
+        <v>31885.5</v>
       </c>
       <c r="O55" t="n">
-        <v>32208.25</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>32441</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5152,69 +5152,63 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>31145.5</v>
+        <v>29227</v>
       </c>
       <c r="C56" t="n">
-        <v>31289.25</v>
+        <v>30113</v>
       </c>
       <c r="D56" t="n">
-        <v>29268.75</v>
+        <v>28987</v>
       </c>
       <c r="E56" t="n">
-        <v>29391.5</v>
+        <v>29117.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-1717.25</v>
+        <v>-273.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0552</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>2020.5</v>
+        <v>1126</v>
       </c>
       <c r="I56" t="n">
-        <v>29967.5</v>
+        <v>27248.25</v>
       </c>
       <c r="J56" t="n">
-        <v>30236.5</v>
+        <v>26927.25</v>
       </c>
       <c r="K56" t="n">
-        <v>30696.5</v>
+        <v>28381.25</v>
       </c>
       <c r="L56" t="n">
-        <v>31156.5</v>
+        <v>29835.25</v>
       </c>
       <c r="M56" t="n">
-        <v>31521</v>
+        <v>30401.75</v>
       </c>
       <c r="N56" t="n">
-        <v>31885.5</v>
+        <v>30968.25</v>
       </c>
       <c r="O56" t="n">
-        <v>32441</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>33309.75</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5226,7 +5220,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5236,50 +5230,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29227</v>
+        <v>29268</v>
       </c>
       <c r="C57" t="n">
-        <v>30113</v>
+        <v>30178</v>
       </c>
       <c r="D57" t="n">
-        <v>28987</v>
+        <v>28232.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29117.75</v>
+        <v>28543</v>
       </c>
       <c r="F57" t="n">
-        <v>-273.75</v>
+        <v>-574.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0197</v>
       </c>
       <c r="H57" t="n">
-        <v>1126</v>
+        <v>1945.25</v>
       </c>
       <c r="I57" t="n">
-        <v>27248.25</v>
+        <v>27861</v>
       </c>
       <c r="J57" t="n">
-        <v>26927.25</v>
+        <v>27775.62</v>
       </c>
       <c r="K57" t="n">
-        <v>28381.25</v>
+        <v>28554.75</v>
       </c>
       <c r="L57" t="n">
-        <v>29835.25</v>
+        <v>29333.88</v>
       </c>
       <c r="M57" t="n">
-        <v>30401.75</v>
+        <v>29680.75</v>
       </c>
       <c r="N57" t="n">
-        <v>30968.25</v>
+        <v>30027.62</v>
       </c>
       <c r="O57" t="n">
-        <v>33309.75</v>
+        <v>31239</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5287,113 +5281,35 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>29268</v>
-      </c>
-      <c r="C58" t="n">
-        <v>30178</v>
-      </c>
-      <c r="D58" t="n">
-        <v>28822.25</v>
-      </c>
-      <c r="E58" t="n">
-        <v>28877.5</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-240.25</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0083</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1355.75</v>
-      </c>
-      <c r="I58" t="n">
-        <v>27861</v>
-      </c>
-      <c r="J58" t="n">
-        <v>27775.62</v>
-      </c>
-      <c r="K58" t="n">
-        <v>28554.75</v>
-      </c>
-      <c r="L58" t="n">
-        <v>29333.88</v>
-      </c>
-      <c r="M58" t="n">
-        <v>29680.75</v>
-      </c>
-      <c r="N58" t="n">
-        <v>30027.62</v>
-      </c>
-      <c r="O58" t="n">
-        <v>31239</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>
